--- a/reports/diebold-birth-dates.xlsx
+++ b/reports/diebold-birth-dates.xlsx
@@ -1102,17 +1102,27 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="7" t="n"/>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>1999</v>
+      </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="inlineStr"/>
+          <t>Approximate</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>Shady Side Academy senior in fall 2017</t>
+        </is>
+      </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
       </c>
     </row>
@@ -5792,17 +5802,27 @@
           <t>2013–2018</t>
         </is>
       </c>
-      <c r="D155" s="6" t="inlineStr"/>
-      <c r="E155" s="7" t="n"/>
+      <c r="D155" s="6" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="E155" s="7" t="n">
+        <v>1997</v>
+      </c>
       <c r="F155" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="G155" s="8" t="inlineStr"/>
+          <t>Approximate</t>
+        </is>
+      </c>
+      <c r="G155" s="8" t="inlineStr">
+        <is>
+          <t>Pittsburgh entrant in 2014 U.S. Junior Amateur qualifying (under 19); uncertain by a year or two</t>
+        </is>
+      </c>
       <c r="H155" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
       </c>
     </row>
@@ -6132,17 +6152,27 @@
           <t>2014–2015</t>
         </is>
       </c>
-      <c r="D166" s="6" t="inlineStr"/>
-      <c r="E166" s="7" t="n"/>
+      <c r="D166" s="6" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="E166" s="7" t="n">
+        <v>1994</v>
+      </c>
       <c r="F166" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="G166" s="8" t="inlineStr"/>
+          <t>Approximate</t>
+        </is>
+      </c>
+      <c r="G166" s="8" t="inlineStr">
+        <is>
+          <t>Shady Side Academy; senior on the South Carolina golf roster 2015-16</t>
+        </is>
+      </c>
       <c r="H166" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
       </c>
     </row>
@@ -6162,17 +6192,27 @@
           <t>2022–2023</t>
         </is>
       </c>
-      <c r="D167" s="6" t="inlineStr"/>
-      <c r="E167" s="7" t="n"/>
+      <c r="D167" s="6" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="E167" s="7" t="n">
+        <v>2000</v>
+      </c>
       <c r="F167" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="G167" s="8" t="inlineStr"/>
+          <t>Approximate</t>
+        </is>
+      </c>
+      <c r="G167" s="8" t="inlineStr">
+        <is>
+          <t>Shaler graduate; Findlay golf, senior in 2023; uncertain by a year or two</t>
+        </is>
+      </c>
       <c r="H167" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
       </c>
     </row>
@@ -6252,17 +6292,27 @@
           <t>2021–2025</t>
         </is>
       </c>
-      <c r="D170" s="6" t="inlineStr"/>
-      <c r="E170" s="7" t="n"/>
+      <c r="D170" s="6" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="E170" s="7" t="n">
+        <v>1990</v>
+      </c>
       <c r="F170" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="G170" s="8" t="inlineStr"/>
+          <t>Approximate</t>
+        </is>
+      </c>
+      <c r="G170" s="8" t="inlineStr">
+        <is>
+          <t>Deer Lakes; Penn State Behrend golf 2009-11</t>
+        </is>
+      </c>
       <c r="H170" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
       </c>
     </row>
@@ -6372,17 +6422,27 @@
           <t>2019–2025</t>
         </is>
       </c>
-      <c r="D174" s="6" t="inlineStr"/>
-      <c r="E174" s="7" t="n"/>
+      <c r="D174" s="6" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="E174" s="7" t="n">
+        <v>2003</v>
+      </c>
       <c r="F174" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="G174" s="8" t="inlineStr"/>
+          <t>Approximate</t>
+        </is>
+      </c>
+      <c r="G174" s="8" t="inlineStr">
+        <is>
+          <t>Fox Chapel HS junior in fall 2019 (WPIAL 3A, T3)</t>
+        </is>
+      </c>
       <c r="H174" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
       </c>
     </row>
@@ -6432,17 +6492,27 @@
           <t>2009–2013</t>
         </is>
       </c>
-      <c r="D176" s="6" t="inlineStr"/>
-      <c r="E176" s="7" t="n"/>
+      <c r="D176" s="6" t="inlineStr">
+        <is>
+          <t>1986</t>
+        </is>
+      </c>
+      <c r="E176" s="7" t="n">
+        <v>1986</v>
+      </c>
       <c r="F176" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="G176" s="8" t="inlineStr"/>
+          <t>Approximate</t>
+        </is>
+      </c>
+      <c r="G176" s="8" t="inlineStr">
+        <is>
+          <t>Serra Catholic; senior on the Marshall golf roster 2007-08</t>
+        </is>
+      </c>
       <c r="H176" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
       </c>
     </row>
@@ -6462,17 +6532,27 @@
           <t>2009–2014</t>
         </is>
       </c>
-      <c r="D177" s="6" t="inlineStr"/>
-      <c r="E177" s="7" t="n"/>
+      <c r="D177" s="6" t="inlineStr">
+        <is>
+          <t>1983</t>
+        </is>
+      </c>
+      <c r="E177" s="7" t="n">
+        <v>1983</v>
+      </c>
       <c r="F177" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="G177" s="8" t="inlineStr"/>
+          <t>Approximate</t>
+        </is>
+      </c>
+      <c r="G177" s="8" t="inlineStr">
+        <is>
+          <t>Allegheny College class of 2005 (athletics hall of fame)</t>
+        </is>
+      </c>
       <c r="H177" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
       </c>
     </row>
@@ -6552,17 +6632,27 @@
           <t>2020–2025</t>
         </is>
       </c>
-      <c r="D180" s="6" t="inlineStr"/>
-      <c r="E180" s="7" t="n"/>
+      <c r="D180" s="6" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="E180" s="7" t="n">
+        <v>2003</v>
+      </c>
       <c r="F180" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="G180" s="8" t="inlineStr"/>
+          <t>Approximate</t>
+        </is>
+      </c>
+      <c r="G180" s="8" t="inlineStr">
+        <is>
+          <t>Shady Side Academy sophomore in fall 2018 (IPSL medalist)</t>
+        </is>
+      </c>
       <c r="H180" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
       </c>
     </row>
@@ -6732,17 +6822,27 @@
           <t>2023–2025</t>
         </is>
       </c>
-      <c r="D186" s="6" t="inlineStr"/>
-      <c r="E186" s="7" t="n"/>
+      <c r="D186" s="6" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="E186" s="7" t="n">
+        <v>2001</v>
+      </c>
       <c r="F186" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="G186" s="8" t="inlineStr"/>
+          <t>Approximate</t>
+        </is>
+      </c>
+      <c r="G186" s="8" t="inlineStr">
+        <is>
+          <t>Pine-Richland golfer at the 2018 PIAA championship; class year not found, uncertain</t>
+        </is>
+      </c>
       <c r="H186" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
       </c>
     </row>
@@ -6762,17 +6862,27 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D187" s="6" t="inlineStr"/>
-      <c r="E187" s="7" t="n"/>
+      <c r="D187" s="6" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="E187" s="7" t="n">
+        <v>2004</v>
+      </c>
       <c r="F187" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="G187" s="8" t="inlineStr"/>
+          <t>Approximate</t>
+        </is>
+      </c>
+      <c r="G187" s="8" t="inlineStr">
+        <is>
+          <t>Fox Chapel HS junior in fall 2020</t>
+        </is>
+      </c>
       <c r="H187" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
       </c>
     </row>
@@ -6851,13 +6961,13 @@
         <v>34</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -6917,13 +7027,13 @@
         <v>0</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E7" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
@@ -6939,13 +7049,13 @@
         <v>90</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>3</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" ht="45" customHeight="1">

--- a/reports/diebold-birth-dates.xlsx
+++ b/reports/diebold-birth-dates.xlsx
@@ -584,7 +584,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Ryan Banks</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -592,17 +592,27 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr"/>
-      <c r="E6" s="7" t="n"/>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>1990</v>
+      </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr"/>
+          <t>Approximate</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>Age 36 in Oct 2026 (Tommy Leech)</t>
+        </is>
+      </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
       </c>
     </row>
@@ -762,7 +772,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Jun 1983</t>
+          <t>15 Jun 1983</t>
         </is>
       </c>
       <c r="E11" s="7" t="n">
@@ -775,7 +785,7 @@
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>Field Club age roster, Aug 2025 (month and year only)</t>
+          <t>Field Club age roster, Aug 2025; full date from Tommy Leech, Oct 2026</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr"/>
@@ -860,7 +870,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Dunlap</t>
+          <t>Matt Dunlap</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -868,19 +878,25 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="7" t="n"/>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>7 Dec 1993</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>1993</v>
+      </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="G14" s="8" t="inlineStr"/>
-      <c r="H14" s="8" t="inlineStr">
-        <is>
-          <t>Please add</t>
-        </is>
-      </c>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>Tommy Leech, Oct 2026</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -970,19 +986,25 @@
           <t>2024–2025</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr"/>
-      <c r="E17" s="7" t="n"/>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>24 May 1993</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>1993</v>
+      </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="inlineStr"/>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>Please add</t>
-        </is>
-      </c>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>Tommy Leech, Oct 2026</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -1036,17 +1058,27 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="7" t="n"/>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>2007</v>
+      </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="G19" s="8" t="inlineStr"/>
+          <t>Approximate</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>High school class of 2025 (Tommy Leech)</t>
+        </is>
+      </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
       </c>
     </row>
@@ -1322,17 +1354,27 @@
           <t>2014–2015</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr"/>
-      <c r="E27" s="7" t="n"/>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="n">
+        <v>1994</v>
+      </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="G27" s="8" t="inlineStr"/>
+          <t>Approximate</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>High school class of 2012 (Tommy Leech)</t>
+        </is>
+      </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
       </c>
     </row>
@@ -6958,16 +7000,16 @@
         <v>41</v>
       </c>
       <c r="C4" s="11" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E4" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -7046,16 +7088,16 @@
         <v>182</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>3</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" ht="45" customHeight="1">

--- a/reports/diebold-birth-dates.xlsx
+++ b/reports/diebold-birth-dates.xlsx
@@ -2304,17 +2304,27 @@
           <t>2015</t>
         </is>
       </c>
-      <c r="D54" s="6" t="inlineStr"/>
-      <c r="E54" s="7" t="n"/>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>1977</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="n">
+        <v>1977</v>
+      </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="G54" s="8" t="inlineStr"/>
+          <t>Approximate</t>
+        </is>
+      </c>
+      <c r="G54" s="8" t="inlineStr">
+        <is>
+          <t>Probably Jimmy Brahm, PGA, former Fox Chapel assistant pro: Slippery Rock graduate who entered the golf business in 2000; identity and year both uncertain</t>
+        </is>
+      </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
       </c>
     </row>
@@ -3466,17 +3476,27 @@
           <t>2007–2021</t>
         </is>
       </c>
-      <c r="D87" s="6" t="inlineStr"/>
-      <c r="E87" s="7" t="n"/>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>1970</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="n">
+        <v>1970</v>
+      </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="G87" s="8" t="inlineStr"/>
+          <t>Approximate</t>
+        </is>
+      </c>
+      <c r="G87" s="8" t="inlineStr">
+        <is>
+          <t>Gus Schroeder Jr., Schroeder Industries president since 2005; rough estimate, father (also Gus, b. c. 1940) died c. 2000</t>
+        </is>
+      </c>
       <c r="H87" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
       </c>
     </row>
@@ -5694,17 +5714,27 @@
           <t>2008–2025</t>
         </is>
       </c>
-      <c r="D150" s="6" t="inlineStr"/>
-      <c r="E150" s="7" t="n"/>
+      <c r="D150" s="6" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="E150" s="7" t="n">
+        <v>1994</v>
+      </c>
       <c r="F150" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="G150" s="8" t="inlineStr"/>
+          <t>Approximate</t>
+        </is>
+      </c>
+      <c r="G150" s="8" t="inlineStr">
+        <is>
+          <t>A William Betts of Leechburg was a Hartford golf senior in 2015-16; if the same man he was 14 at his 2008 debut, so uncertain</t>
+        </is>
+      </c>
       <c r="H150" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
       </c>
     </row>
@@ -7025,13 +7055,13 @@
         <v>16</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E5" s="11" t="n">
         <v>3</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
@@ -7069,13 +7099,13 @@
         <v>0</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E7" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8">
@@ -7091,13 +7121,13 @@
         <v>92</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>3</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" ht="45" customHeight="1">

--- a/reports/diebold-birth-dates.xlsx
+++ b/reports/diebold-birth-dates.xlsx
@@ -5716,11 +5716,11 @@
       </c>
       <c r="D150" s="6" t="inlineStr">
         <is>
-          <t>1994</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="E150" s="7" t="n">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="F150" s="5" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G150" s="8" t="inlineStr">
         <is>
-          <t>A William Betts of Leechburg was a Hartford golf senior in 2015-16; if the same man he was 14 at his 2008 debut, so uncertain</t>
+          <t>Fox Chapel HS freshman in 2007, then prep school, class of 2011/12 (Tommy Leech); Hartford golf senior 2015-16</t>
         </is>
       </c>
       <c r="H150" s="8" t="inlineStr">

--- a/reports/diebold-birth-dates.xlsx
+++ b/reports/diebold-birth-dates.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Birth dates'!$A$5:$H$187</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Birth dates'!$A$5:$I$187</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H187"/>
+  <dimension ref="A1:I187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -508,9 +508,10 @@
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="48" customWidth="1" min="7" max="7"/>
-    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="48" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -562,15 +563,20 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
+          <t>Age band (2026)</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>Where it came from</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>Notes for the club</t>
         </is>
@@ -602,15 +608,20 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
+          <t>30–39</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
           <t>Approximate</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>Age 36 in Oct 2026 (Tommy Leech)</t>
         </is>
       </c>
-      <c r="H6" s="8" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
@@ -642,15 +653,20 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
+          <t>40–49</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>Field Club age roster, Aug 2025 (month and year only)</t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr"/>
+      <c r="I7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -678,15 +694,20 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
+          <t>30–39</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>Field Club age roster, Aug 2025 (month and year only)</t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr"/>
+      <c r="I8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -714,15 +735,20 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
+          <t>30–39</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>Field Club age roster, Aug 2025 (month and year only)</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr"/>
+      <c r="I9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -742,13 +768,14 @@
       </c>
       <c r="D10" s="6" t="inlineStr"/>
       <c r="E10" s="7" t="n"/>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="G10" s="8" t="inlineStr"/>
-      <c r="H10" s="8" t="inlineStr">
+      <c r="H10" s="8" t="inlineStr"/>
+      <c r="I10" s="8" t="inlineStr">
         <is>
           <t>Please add</t>
         </is>
@@ -780,15 +807,20 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
+          <t>40–49</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
         <is>
           <t>Field Club age roster, Aug 2025; full date from Tommy Leech, Oct 2026</t>
         </is>
       </c>
-      <c r="H11" s="8" t="inlineStr"/>
+      <c r="I11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -816,15 +848,20 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>Field Club age roster, Aug 2025 (month and year only)</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr"/>
+      <c r="I12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -852,15 +889,20 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
+          <t>30–39</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>Field Club age roster, Aug 2025 (month and year only)</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr"/>
+      <c r="I13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -888,15 +930,20 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
+          <t>30–39</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
         <is>
           <t>Tommy Leech, Oct 2026</t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr"/>
+      <c r="I14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -924,15 +971,20 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
+          <t>40–49</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
         <is>
           <t>Field Club age roster, Aug 2025 (month and year only)</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr"/>
+      <c r="I15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -960,15 +1012,20 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G16" s="8" t="inlineStr">
+          <t>30–39</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
         <is>
           <t>Field Club age roster, Aug 2025 (month and year only)</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr"/>
+      <c r="I16" s="8" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -996,15 +1053,20 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
+          <t>30–39</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
         <is>
           <t>Tommy Leech, Oct 2026</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr"/>
+      <c r="I17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -1032,15 +1094,20 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G18" s="8" t="inlineStr">
+          <t>30–39</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
         <is>
           <t>Field Club age roster, Aug 2025 (month and year only)</t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr"/>
+      <c r="I18" s="8" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -1068,15 +1135,20 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
+          <t>Under 25</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
           <t>Approximate</t>
         </is>
       </c>
-      <c r="G19" s="8" t="inlineStr">
+      <c r="H19" s="8" t="inlineStr">
         <is>
           <t>High school class of 2025 (Tommy Leech)</t>
         </is>
       </c>
-      <c r="H19" s="8" t="inlineStr">
+      <c r="I19" s="8" t="inlineStr">
         <is>
           <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
@@ -1108,15 +1180,20 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G20" s="8" t="inlineStr">
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="inlineStr">
         <is>
           <t>Field Club age roster, Aug 2025 (month and year only)</t>
         </is>
       </c>
-      <c r="H20" s="8" t="inlineStr"/>
+      <c r="I20" s="8" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -1144,15 +1221,20 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
+          <t>25–29</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
           <t>Approximate</t>
         </is>
       </c>
-      <c r="G21" s="8" t="inlineStr">
+      <c r="H21" s="8" t="inlineStr">
         <is>
           <t>Shady Side Academy senior in fall 2017</t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr">
+      <c r="I21" s="8" t="inlineStr">
         <is>
           <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
@@ -1184,15 +1266,20 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G22" s="8" t="inlineStr">
+          <t>25–29</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>Field Club age roster, Aug 2025 (month and year only)</t>
         </is>
       </c>
-      <c r="H22" s="8" t="inlineStr"/>
+      <c r="I22" s="8" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -1220,15 +1307,20 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G23" s="8" t="inlineStr">
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
         <is>
           <t>Field Club age roster, Aug 2025 (month and year only)</t>
         </is>
       </c>
-      <c r="H23" s="8" t="inlineStr"/>
+      <c r="I23" s="8" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -1256,15 +1348,20 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G24" s="8" t="inlineStr">
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
         <is>
           <t>Field Club age roster, Aug 2025 (month and year only)</t>
         </is>
       </c>
-      <c r="H24" s="8" t="inlineStr"/>
+      <c r="I24" s="8" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -1292,15 +1389,20 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G25" s="8" t="inlineStr">
+          <t>25–29</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
         <is>
           <t>Field Club age roster, Aug 2025 (month and year only)</t>
         </is>
       </c>
-      <c r="H25" s="8" t="inlineStr"/>
+      <c r="I25" s="8" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -1328,15 +1430,20 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G26" s="8" t="inlineStr">
+          <t>30–39</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>Field Club age roster, Aug 2025 (month and year only)</t>
         </is>
       </c>
-      <c r="H26" s="8" t="inlineStr"/>
+      <c r="I26" s="8" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -1364,15 +1471,20 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
+          <t>30–39</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
           <t>Approximate</t>
         </is>
       </c>
-      <c r="G27" s="8" t="inlineStr">
+      <c r="H27" s="8" t="inlineStr">
         <is>
           <t>High school class of 2012 (Tommy Leech)</t>
         </is>
       </c>
-      <c r="H27" s="8" t="inlineStr">
+      <c r="I27" s="8" t="inlineStr">
         <is>
           <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
@@ -1404,15 +1516,20 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G28" s="8" t="inlineStr">
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
         <is>
           <t>Field Club age roster, Aug 2025 (month and year only)</t>
         </is>
       </c>
-      <c r="H28" s="8" t="inlineStr"/>
+      <c r="I28" s="8" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -1440,15 +1557,20 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G29" s="8" t="inlineStr">
+          <t>Under 25</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="inlineStr">
         <is>
           <t>Field Club age roster, Aug 2025 (month and year only)</t>
         </is>
       </c>
-      <c r="H29" s="8" t="inlineStr"/>
+      <c r="I29" s="8" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -1476,15 +1598,20 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G30" s="8" t="inlineStr">
+          <t>25–29</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="inlineStr">
         <is>
           <t>Field Club age roster, Aug 2025 (month and year only)</t>
         </is>
       </c>
-      <c r="H30" s="8" t="inlineStr"/>
+      <c r="I30" s="8" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -1512,15 +1639,20 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G31" s="8" t="inlineStr">
+          <t>30–39</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H31" s="8" t="inlineStr">
         <is>
           <t>Field Club age roster, Aug 2025 (month and year only)</t>
         </is>
       </c>
-      <c r="H31" s="8" t="inlineStr"/>
+      <c r="I31" s="8" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -1548,15 +1680,20 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G32" s="8" t="inlineStr">
+          <t>25–29</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="inlineStr">
         <is>
           <t>Field Club age roster, Aug 2025 (month and year only)</t>
         </is>
       </c>
-      <c r="H32" s="8" t="inlineStr"/>
+      <c r="I32" s="8" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -1584,15 +1721,20 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G33" s="8" t="inlineStr">
+          <t>40–49</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="inlineStr">
         <is>
           <t>Field Club age roster, Aug 2025 (month and year only)</t>
         </is>
       </c>
-      <c r="H33" s="8" t="inlineStr"/>
+      <c r="I33" s="8" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -1620,15 +1762,20 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G34" s="8" t="inlineStr">
+          <t>30–39</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H34" s="8" t="inlineStr">
         <is>
           <t>Field Club age roster, Aug 2025 (month and year only)</t>
         </is>
       </c>
-      <c r="H34" s="8" t="inlineStr"/>
+      <c r="I34" s="8" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -1656,15 +1803,20 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G35" s="8" t="inlineStr">
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H35" s="8" t="inlineStr">
         <is>
           <t>Field Club age roster, Aug 2025 (month and year only)</t>
         </is>
       </c>
-      <c r="H35" s="8" t="inlineStr"/>
+      <c r="I35" s="8" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -1692,15 +1844,20 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G36" s="8" t="inlineStr">
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H36" s="8" t="inlineStr">
         <is>
           <t>Field Club age roster, Aug 2025 (month and year only)</t>
         </is>
       </c>
-      <c r="H36" s="8" t="inlineStr"/>
+      <c r="I36" s="8" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -1728,15 +1885,20 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G37" s="8" t="inlineStr">
+          <t>40–49</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="inlineStr">
         <is>
           <t>Field Club age roster, Aug 2025 (month and year only)</t>
         </is>
       </c>
-      <c r="H37" s="8" t="inlineStr"/>
+      <c r="I37" s="8" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -1764,15 +1926,20 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G38" s="8" t="inlineStr">
+          <t>40–49</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="inlineStr">
         <is>
           <t>Field Club age roster, Aug 2025 (month and year only)</t>
         </is>
       </c>
-      <c r="H38" s="8" t="inlineStr"/>
+      <c r="I38" s="8" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -1800,15 +1967,20 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G39" s="8" t="inlineStr">
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="inlineStr">
         <is>
           <t>Field Club age roster, Aug 2025 (month and year only)</t>
         </is>
       </c>
-      <c r="H39" s="8" t="inlineStr"/>
+      <c r="I39" s="8" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -1836,15 +2008,20 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G40" s="8" t="inlineStr">
+          <t>Under 25</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H40" s="8" t="inlineStr">
         <is>
           <t>Field Club age roster, Aug 2025 (month and year only)</t>
         </is>
       </c>
-      <c r="H40" s="8" t="inlineStr"/>
+      <c r="I40" s="8" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -1872,15 +2049,20 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G41" s="8" t="inlineStr">
+          <t>40–49</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H41" s="8" t="inlineStr">
         <is>
           <t>Field Club age roster, Aug 2025 (month and year only)</t>
         </is>
       </c>
-      <c r="H41" s="8" t="inlineStr"/>
+      <c r="I41" s="8" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -1908,15 +2090,20 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G42" s="8" t="inlineStr">
+          <t>40–49</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H42" s="8" t="inlineStr">
         <is>
           <t>Field Club age roster, Aug 2025 (month and year only)</t>
         </is>
       </c>
-      <c r="H42" s="8" t="inlineStr"/>
+      <c r="I42" s="8" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -1944,15 +2131,20 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G43" s="8" t="inlineStr">
+          <t>30–39</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H43" s="8" t="inlineStr">
         <is>
           <t>Field Club age roster, Aug 2025 (month and year only)</t>
         </is>
       </c>
-      <c r="H43" s="8" t="inlineStr"/>
+      <c r="I43" s="8" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -1980,15 +2172,20 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G44" s="8" t="inlineStr">
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H44" s="8" t="inlineStr">
         <is>
           <t>Field Club age roster, Aug 2025 (month and year only)</t>
         </is>
       </c>
-      <c r="H44" s="8" t="inlineStr"/>
+      <c r="I44" s="8" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -2016,15 +2213,20 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G45" s="8" t="inlineStr">
+          <t>Under 25</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H45" s="8" t="inlineStr">
         <is>
           <t>Field Club age roster, Aug 2025 (month and year only)</t>
         </is>
       </c>
-      <c r="H45" s="8" t="inlineStr"/>
+      <c r="I45" s="8" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -2052,15 +2254,20 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G46" s="8" t="inlineStr">
+          <t>40–49</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H46" s="8" t="inlineStr">
         <is>
           <t>Field Club age roster, Aug 2025 (month and year only)</t>
         </is>
       </c>
-      <c r="H46" s="8" t="inlineStr"/>
+      <c r="I46" s="8" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -2080,13 +2287,14 @@
       </c>
       <c r="D47" s="6" t="inlineStr"/>
       <c r="E47" s="7" t="n"/>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="F47" s="5" t="inlineStr"/>
+      <c r="G47" s="5" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="G47" s="8" t="inlineStr"/>
-      <c r="H47" s="8" t="inlineStr">
+      <c r="H47" s="8" t="inlineStr"/>
+      <c r="I47" s="8" t="inlineStr">
         <is>
           <t>Please add</t>
         </is>
@@ -2110,13 +2318,14 @@
       </c>
       <c r="D48" s="6" t="inlineStr"/>
       <c r="E48" s="7" t="n"/>
-      <c r="F48" s="5" t="inlineStr">
+      <c r="F48" s="5" t="inlineStr"/>
+      <c r="G48" s="5" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="G48" s="8" t="inlineStr"/>
-      <c r="H48" s="8" t="inlineStr">
+      <c r="H48" s="8" t="inlineStr"/>
+      <c r="I48" s="8" t="inlineStr">
         <is>
           <t>Please add</t>
         </is>
@@ -2140,13 +2349,14 @@
       </c>
       <c r="D49" s="6" t="inlineStr"/>
       <c r="E49" s="7" t="n"/>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="F49" s="5" t="inlineStr"/>
+      <c r="G49" s="5" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="G49" s="8" t="inlineStr"/>
-      <c r="H49" s="8" t="inlineStr">
+      <c r="H49" s="8" t="inlineStr"/>
+      <c r="I49" s="8" t="inlineStr">
         <is>
           <t>Please add</t>
         </is>
@@ -2170,13 +2380,14 @@
       </c>
       <c r="D50" s="6" t="inlineStr"/>
       <c r="E50" s="7" t="n"/>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="F50" s="5" t="inlineStr"/>
+      <c r="G50" s="5" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="G50" s="8" t="inlineStr"/>
-      <c r="H50" s="8" t="inlineStr">
+      <c r="H50" s="8" t="inlineStr"/>
+      <c r="I50" s="8" t="inlineStr">
         <is>
           <t>Please add</t>
         </is>
@@ -2200,13 +2411,14 @@
       </c>
       <c r="D51" s="6" t="inlineStr"/>
       <c r="E51" s="7" t="n"/>
-      <c r="F51" s="5" t="inlineStr">
+      <c r="F51" s="5" t="inlineStr"/>
+      <c r="G51" s="5" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="G51" s="8" t="inlineStr"/>
-      <c r="H51" s="8" t="inlineStr">
+      <c r="H51" s="8" t="inlineStr"/>
+      <c r="I51" s="8" t="inlineStr">
         <is>
           <t>Please add</t>
         </is>
@@ -2238,15 +2450,20 @@
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
+          <t>Under 25</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
           <t>Approximate</t>
         </is>
       </c>
-      <c r="G52" s="8" t="inlineStr">
+      <c r="H52" s="8" t="inlineStr">
         <is>
           <t>Fox Chapel HS class of 2028 (MaxPreps); Tri-State PGA junior boys 11-14 in 2024</t>
         </is>
       </c>
-      <c r="H52" s="8" t="inlineStr">
+      <c r="I52" s="8" t="inlineStr">
         <is>
           <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
@@ -2278,15 +2495,20 @@
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G53" s="8" t="inlineStr">
+          <t>25–29</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H53" s="8" t="inlineStr">
         <is>
           <t>Fox Chapel age roster, Aug 2025</t>
         </is>
       </c>
-      <c r="H53" s="8" t="inlineStr"/>
+      <c r="I53" s="8" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
@@ -2314,15 +2536,20 @@
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
+          <t>40–49</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
           <t>Approximate</t>
         </is>
       </c>
-      <c r="G54" s="8" t="inlineStr">
+      <c r="H54" s="8" t="inlineStr">
         <is>
           <t>Probably Jimmy Brahm, PGA, former Fox Chapel assistant pro: Slippery Rock graduate who entered the golf business in 2000; identity and year both uncertain</t>
         </is>
       </c>
-      <c r="H54" s="8" t="inlineStr">
+      <c r="I54" s="8" t="inlineStr">
         <is>
           <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
@@ -2354,15 +2581,20 @@
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
+          <t>Under 25</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
           <t>Approximate</t>
         </is>
       </c>
-      <c r="G55" s="8" t="inlineStr">
+      <c r="H55" s="8" t="inlineStr">
         <is>
           <t>SMU sophomore in spring 2025</t>
         </is>
       </c>
-      <c r="H55" s="8" t="inlineStr">
+      <c r="I55" s="8" t="inlineStr">
         <is>
           <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
@@ -2392,17 +2624,22 @@
       <c r="E56" s="7" t="n">
         <v>1981</v>
       </c>
-      <c r="F56" s="6" t="inlineStr">
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>40–49</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
         <is>
           <t>Please confirm</t>
         </is>
       </c>
-      <c r="G56" s="8" t="inlineStr">
+      <c r="H56" s="8" t="inlineStr">
         <is>
           <t>Fox Chapel age roster, Aug 2025 shows 1981-07-06, identical to Eric Hellberg; one of the two is probably a copy error, so both are approximate until Fox Chapel confirms</t>
         </is>
       </c>
-      <c r="H56" s="8" t="inlineStr">
+      <c r="I56" s="8" t="inlineStr">
         <is>
           <t>The roster gives this player the same full date as another player – please check which is right</t>
         </is>
@@ -2426,13 +2663,14 @@
       </c>
       <c r="D57" s="6" t="inlineStr"/>
       <c r="E57" s="7" t="n"/>
-      <c r="F57" s="5" t="inlineStr">
+      <c r="F57" s="5" t="inlineStr"/>
+      <c r="G57" s="5" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="G57" s="8" t="inlineStr"/>
-      <c r="H57" s="8" t="inlineStr">
+      <c r="H57" s="8" t="inlineStr"/>
+      <c r="I57" s="8" t="inlineStr">
         <is>
           <t>Please add</t>
         </is>
@@ -2464,15 +2702,20 @@
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
+          <t>40–49</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
           <t>Approximate</t>
         </is>
       </c>
-      <c r="G58" s="8" t="inlineStr">
+      <c r="H58" s="8" t="inlineStr">
         <is>
           <t>Shady Side Academy and GWU graduate, first job 2007; uncertain</t>
         </is>
       </c>
-      <c r="H58" s="8" t="inlineStr">
+      <c r="I58" s="8" t="inlineStr">
         <is>
           <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
@@ -2504,15 +2747,20 @@
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G59" s="8" t="inlineStr">
+          <t>25–29</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H59" s="8" t="inlineStr">
         <is>
           <t>Fox Chapel age roster, Aug 2025</t>
         </is>
       </c>
-      <c r="H59" s="8" t="inlineStr"/>
+      <c r="I59" s="8" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
@@ -2540,15 +2788,20 @@
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G60" s="8" t="inlineStr">
+          <t>Under 25</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H60" s="8" t="inlineStr">
         <is>
           <t>Fox Chapel age roster, Aug 2025</t>
         </is>
       </c>
-      <c r="H60" s="8" t="inlineStr"/>
+      <c r="I60" s="8" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
@@ -2576,15 +2829,20 @@
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
+          <t>40–49</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
           <t>Approximate</t>
         </is>
       </c>
-      <c r="G61" s="8" t="inlineStr">
+      <c r="H61" s="8" t="inlineStr">
         <is>
           <t>Age 45 in Poets &amp; Quants profile, 2025</t>
         </is>
       </c>
-      <c r="H61" s="8" t="inlineStr">
+      <c r="I61" s="8" t="inlineStr">
         <is>
           <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
@@ -2608,13 +2866,14 @@
       </c>
       <c r="D62" s="6" t="inlineStr"/>
       <c r="E62" s="7" t="n"/>
-      <c r="F62" s="5" t="inlineStr">
+      <c r="F62" s="5" t="inlineStr"/>
+      <c r="G62" s="5" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="G62" s="8" t="inlineStr"/>
-      <c r="H62" s="8" t="inlineStr">
+      <c r="H62" s="8" t="inlineStr"/>
+      <c r="I62" s="8" t="inlineStr">
         <is>
           <t>Please add</t>
         </is>
@@ -2638,13 +2897,14 @@
       </c>
       <c r="D63" s="6" t="inlineStr"/>
       <c r="E63" s="7" t="n"/>
-      <c r="F63" s="5" t="inlineStr">
+      <c r="F63" s="5" t="inlineStr"/>
+      <c r="G63" s="5" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="G63" s="8" t="inlineStr"/>
-      <c r="H63" s="8" t="inlineStr">
+      <c r="H63" s="8" t="inlineStr"/>
+      <c r="I63" s="8" t="inlineStr">
         <is>
           <t>Please add</t>
         </is>
@@ -2676,15 +2936,20 @@
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G64" s="8" t="inlineStr">
+          <t>30–39</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H64" s="8" t="inlineStr">
         <is>
           <t>Fox Chapel age roster, Aug 2025</t>
         </is>
       </c>
-      <c r="H64" s="8" t="inlineStr"/>
+      <c r="I64" s="8" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
@@ -2712,15 +2977,20 @@
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
           <t>Approximate</t>
         </is>
       </c>
-      <c r="G65" s="8" t="inlineStr">
+      <c r="H65" s="8" t="inlineStr">
         <is>
           <t>Fox Chapel age roster: 49 in Oct 2023</t>
         </is>
       </c>
-      <c r="H65" s="8" t="inlineStr">
+      <c r="I65" s="8" t="inlineStr">
         <is>
           <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
@@ -2752,15 +3022,20 @@
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G66" s="8" t="inlineStr">
+          <t>Under 25</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H66" s="8" t="inlineStr">
         <is>
           <t>Fox Chapel age roster, Aug 2025</t>
         </is>
       </c>
-      <c r="H66" s="8" t="inlineStr"/>
+      <c r="I66" s="8" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
@@ -2788,15 +3063,20 @@
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G67" s="8" t="inlineStr">
+          <t>30–39</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H67" s="8" t="inlineStr">
         <is>
           <t>Fox Chapel age roster, Aug 2025</t>
         </is>
       </c>
-      <c r="H67" s="8" t="inlineStr"/>
+      <c r="I67" s="8" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
@@ -2822,17 +3102,22 @@
       <c r="E68" s="7" t="n">
         <v>1972</v>
       </c>
-      <c r="F68" s="6" t="inlineStr">
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
         <is>
           <t>Please confirm</t>
         </is>
       </c>
-      <c r="G68" s="8" t="inlineStr">
+      <c r="H68" s="8" t="inlineStr">
         <is>
           <t>Fox Chapel age roster, Aug 2025 shows 1972-12-15, identical to Tom Delaney (Oakmont) and probably pasted; year kept as approximate until Fox Chapel confirms</t>
         </is>
       </c>
-      <c r="H68" s="8" t="inlineStr">
+      <c r="I68" s="8" t="inlineStr">
         <is>
           <t>The roster gives this player the same full date as another player – please check which is right</t>
         </is>
@@ -2856,13 +3141,14 @@
       </c>
       <c r="D69" s="6" t="inlineStr"/>
       <c r="E69" s="7" t="n"/>
-      <c r="F69" s="5" t="inlineStr">
+      <c r="F69" s="5" t="inlineStr"/>
+      <c r="G69" s="5" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="G69" s="8" t="inlineStr"/>
-      <c r="H69" s="8" t="inlineStr">
+      <c r="H69" s="8" t="inlineStr"/>
+      <c r="I69" s="8" t="inlineStr">
         <is>
           <t>Please add</t>
         </is>
@@ -2892,17 +3178,22 @@
       <c r="E70" s="7" t="n">
         <v>1981</v>
       </c>
-      <c r="F70" s="6" t="inlineStr">
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>40–49</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
         <is>
           <t>Please confirm</t>
         </is>
       </c>
-      <c r="G70" s="8" t="inlineStr">
+      <c r="H70" s="8" t="inlineStr">
         <is>
           <t>Fox Chapel age roster, Aug 2025 shows 1981-07-06, identical to Michael Carlin; one of the two is probably a copy error, so both are approximate until Fox Chapel confirms</t>
         </is>
       </c>
-      <c r="H70" s="8" t="inlineStr">
+      <c r="I70" s="8" t="inlineStr">
         <is>
           <t>The roster gives this player the same full date as another player – please check which is right</t>
         </is>
@@ -2934,15 +3225,20 @@
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G71" s="8" t="inlineStr">
+          <t>30–39</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H71" s="8" t="inlineStr">
         <is>
           <t>Fox Chapel age roster, Aug 2025</t>
         </is>
       </c>
-      <c r="H71" s="8" t="inlineStr"/>
+      <c r="I71" s="8" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
@@ -2970,15 +3266,20 @@
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G72" s="8" t="inlineStr">
+          <t>30–39</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H72" s="8" t="inlineStr">
         <is>
           <t>Fox Chapel age roster, Aug 2025</t>
         </is>
       </c>
-      <c r="H72" s="8" t="inlineStr"/>
+      <c r="I72" s="8" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
@@ -3006,15 +3307,20 @@
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G73" s="8" t="inlineStr">
+          <t>40–49</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H73" s="8" t="inlineStr">
         <is>
           <t>Fox Chapel age roster, Aug 2025</t>
         </is>
       </c>
-      <c r="H73" s="8" t="inlineStr"/>
+      <c r="I73" s="8" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
@@ -3034,13 +3340,14 @@
       </c>
       <c r="D74" s="6" t="inlineStr"/>
       <c r="E74" s="7" t="n"/>
-      <c r="F74" s="5" t="inlineStr">
+      <c r="F74" s="5" t="inlineStr"/>
+      <c r="G74" s="5" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="G74" s="8" t="inlineStr"/>
-      <c r="H74" s="8" t="inlineStr">
+      <c r="H74" s="8" t="inlineStr"/>
+      <c r="I74" s="8" t="inlineStr">
         <is>
           <t>Please add</t>
         </is>
@@ -3072,15 +3379,20 @@
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
+          <t>Under 25</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
           <t>Approximate</t>
         </is>
       </c>
-      <c r="G75" s="8" t="inlineStr">
+      <c r="H75" s="8" t="inlineStr">
         <is>
           <t>Shady Side Academy junior in fall 2019; WPIAL 3A runner-up 2020</t>
         </is>
       </c>
-      <c r="H75" s="8" t="inlineStr">
+      <c r="I75" s="8" t="inlineStr">
         <is>
           <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
@@ -3112,15 +3424,20 @@
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G76" s="8" t="inlineStr">
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H76" s="8" t="inlineStr">
         <is>
           <t>Fox Chapel age roster, Aug 2025</t>
         </is>
       </c>
-      <c r="H76" s="8" t="inlineStr"/>
+      <c r="I76" s="8" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
@@ -3148,15 +3465,20 @@
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G77" s="8" t="inlineStr">
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H77" s="8" t="inlineStr">
         <is>
           <t>Fox Chapel age roster, Aug 2025</t>
         </is>
       </c>
-      <c r="H77" s="8" t="inlineStr"/>
+      <c r="I77" s="8" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
@@ -3184,15 +3506,20 @@
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G78" s="8" t="inlineStr">
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="G78" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H78" s="8" t="inlineStr">
         <is>
           <t>Fox Chapel age roster, Aug 2025</t>
         </is>
       </c>
-      <c r="H78" s="8" t="inlineStr"/>
+      <c r="I78" s="8" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
@@ -3212,13 +3539,14 @@
       </c>
       <c r="D79" s="6" t="inlineStr"/>
       <c r="E79" s="7" t="n"/>
-      <c r="F79" s="5" t="inlineStr">
+      <c r="F79" s="5" t="inlineStr"/>
+      <c r="G79" s="5" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="G79" s="8" t="inlineStr"/>
-      <c r="H79" s="8" t="inlineStr">
+      <c r="H79" s="8" t="inlineStr"/>
+      <c r="I79" s="8" t="inlineStr">
         <is>
           <t>Please add</t>
         </is>
@@ -3242,13 +3570,14 @@
       </c>
       <c r="D80" s="6" t="inlineStr"/>
       <c r="E80" s="7" t="n"/>
-      <c r="F80" s="5" t="inlineStr">
+      <c r="F80" s="5" t="inlineStr"/>
+      <c r="G80" s="5" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="G80" s="8" t="inlineStr"/>
-      <c r="H80" s="8" t="inlineStr">
+      <c r="H80" s="8" t="inlineStr"/>
+      <c r="I80" s="8" t="inlineStr">
         <is>
           <t>Please add</t>
         </is>
@@ -3280,15 +3609,20 @@
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
+          <t>30–39</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
           <t>Approximate</t>
         </is>
       </c>
-      <c r="G81" s="8" t="inlineStr">
+      <c r="H81" s="8" t="inlineStr">
         <is>
           <t>Peters Township class of 2012; Saint Francis golf 2012-16</t>
         </is>
       </c>
-      <c r="H81" s="8" t="inlineStr">
+      <c r="I81" s="8" t="inlineStr">
         <is>
           <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
@@ -3312,13 +3646,14 @@
       </c>
       <c r="D82" s="6" t="inlineStr"/>
       <c r="E82" s="7" t="n"/>
-      <c r="F82" s="5" t="inlineStr">
+      <c r="F82" s="5" t="inlineStr"/>
+      <c r="G82" s="5" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="G82" s="8" t="inlineStr"/>
-      <c r="H82" s="8" t="inlineStr">
+      <c r="H82" s="8" t="inlineStr"/>
+      <c r="I82" s="8" t="inlineStr">
         <is>
           <t>Please add</t>
         </is>
@@ -3350,15 +3685,20 @@
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G83" s="8" t="inlineStr">
+          <t>30–39</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H83" s="8" t="inlineStr">
         <is>
           <t>Georgetown men's golf roster</t>
         </is>
       </c>
-      <c r="H83" s="8" t="inlineStr"/>
+      <c r="I83" s="8" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
@@ -3386,15 +3726,20 @@
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="G84" s="5" t="inlineStr">
+        <is>
           <t>Approximate</t>
         </is>
       </c>
-      <c r="G84" s="8" t="inlineStr">
+      <c r="H84" s="8" t="inlineStr">
         <is>
           <t>Fox Chapel age roster: 60 in Oct 2023</t>
         </is>
       </c>
-      <c r="H84" s="8" t="inlineStr">
+      <c r="I84" s="8" t="inlineStr">
         <is>
           <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
@@ -3418,13 +3763,14 @@
       </c>
       <c r="D85" s="6" t="inlineStr"/>
       <c r="E85" s="7" t="n"/>
-      <c r="F85" s="5" t="inlineStr">
+      <c r="F85" s="5" t="inlineStr"/>
+      <c r="G85" s="5" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="G85" s="8" t="inlineStr"/>
-      <c r="H85" s="8" t="inlineStr">
+      <c r="H85" s="8" t="inlineStr"/>
+      <c r="I85" s="8" t="inlineStr">
         <is>
           <t>Please add</t>
         </is>
@@ -3448,13 +3794,14 @@
       </c>
       <c r="D86" s="6" t="inlineStr"/>
       <c r="E86" s="7" t="n"/>
-      <c r="F86" s="5" t="inlineStr">
+      <c r="F86" s="5" t="inlineStr"/>
+      <c r="G86" s="5" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="G86" s="8" t="inlineStr"/>
-      <c r="H86" s="8" t="inlineStr">
+      <c r="H86" s="8" t="inlineStr"/>
+      <c r="I86" s="8" t="inlineStr">
         <is>
           <t>Please add</t>
         </is>
@@ -3486,15 +3833,20 @@
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="G87" s="5" t="inlineStr">
+        <is>
           <t>Approximate</t>
         </is>
       </c>
-      <c r="G87" s="8" t="inlineStr">
+      <c r="H87" s="8" t="inlineStr">
         <is>
           <t>Gus Schroeder Jr., Schroeder Industries president since 2005; rough estimate, father (also Gus, b. c. 1940) died c. 2000</t>
         </is>
       </c>
-      <c r="H87" s="8" t="inlineStr">
+      <c r="I87" s="8" t="inlineStr">
         <is>
           <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
@@ -3518,13 +3870,14 @@
       </c>
       <c r="D88" s="6" t="inlineStr"/>
       <c r="E88" s="7" t="n"/>
-      <c r="F88" s="5" t="inlineStr">
+      <c r="F88" s="5" t="inlineStr"/>
+      <c r="G88" s="5" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="G88" s="8" t="inlineStr"/>
-      <c r="H88" s="8" t="inlineStr">
+      <c r="H88" s="8" t="inlineStr"/>
+      <c r="I88" s="8" t="inlineStr">
         <is>
           <t>Please add</t>
         </is>
@@ -3556,15 +3909,20 @@
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G89" s="8" t="inlineStr">
+          <t>40–49</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H89" s="8" t="inlineStr">
         <is>
           <t>Fox Chapel age roster, Aug 2025</t>
         </is>
       </c>
-      <c r="H89" s="8" t="inlineStr"/>
+      <c r="I89" s="8" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
@@ -3584,13 +3942,14 @@
       </c>
       <c r="D90" s="6" t="inlineStr"/>
       <c r="E90" s="7" t="n"/>
-      <c r="F90" s="5" t="inlineStr">
+      <c r="F90" s="5" t="inlineStr"/>
+      <c r="G90" s="5" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="G90" s="8" t="inlineStr"/>
-      <c r="H90" s="8" t="inlineStr">
+      <c r="H90" s="8" t="inlineStr"/>
+      <c r="I90" s="8" t="inlineStr">
         <is>
           <t>Please add</t>
         </is>
@@ -3622,15 +3981,20 @@
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G91" s="8" t="inlineStr">
+          <t>40–49</t>
+        </is>
+      </c>
+      <c r="G91" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H91" s="8" t="inlineStr">
         <is>
           <t>Fox Chapel age roster, Aug 2025</t>
         </is>
       </c>
-      <c r="H91" s="8" t="inlineStr"/>
+      <c r="I91" s="8" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
@@ -3658,15 +4022,20 @@
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
+          <t>30–39</t>
+        </is>
+      </c>
+      <c r="G92" s="5" t="inlineStr">
+        <is>
           <t>Approximate</t>
         </is>
       </c>
-      <c r="G92" s="8" t="inlineStr">
+      <c r="H92" s="8" t="inlineStr">
         <is>
           <t>Peters Township HS golf 2010 alongside Tommy Nettles; uncertain, same name only</t>
         </is>
       </c>
-      <c r="H92" s="8" t="inlineStr">
+      <c r="I92" s="8" t="inlineStr">
         <is>
           <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
@@ -3690,13 +4059,14 @@
       </c>
       <c r="D93" s="6" t="inlineStr"/>
       <c r="E93" s="7" t="n"/>
-      <c r="F93" s="5" t="inlineStr">
+      <c r="F93" s="5" t="inlineStr"/>
+      <c r="G93" s="5" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="G93" s="8" t="inlineStr"/>
-      <c r="H93" s="8" t="inlineStr">
+      <c r="H93" s="8" t="inlineStr"/>
+      <c r="I93" s="8" t="inlineStr">
         <is>
           <t>Please add</t>
         </is>
@@ -3720,13 +4090,14 @@
       </c>
       <c r="D94" s="6" t="inlineStr"/>
       <c r="E94" s="7" t="n"/>
-      <c r="F94" s="5" t="inlineStr">
+      <c r="F94" s="5" t="inlineStr"/>
+      <c r="G94" s="5" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="G94" s="8" t="inlineStr"/>
-      <c r="H94" s="8" t="inlineStr">
+      <c r="H94" s="8" t="inlineStr"/>
+      <c r="I94" s="8" t="inlineStr">
         <is>
           <t>Please add</t>
         </is>
@@ -3750,13 +4121,14 @@
       </c>
       <c r="D95" s="6" t="inlineStr"/>
       <c r="E95" s="7" t="n"/>
-      <c r="F95" s="5" t="inlineStr">
+      <c r="F95" s="5" t="inlineStr"/>
+      <c r="G95" s="5" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="G95" s="8" t="inlineStr"/>
-      <c r="H95" s="8" t="inlineStr">
+      <c r="H95" s="8" t="inlineStr"/>
+      <c r="I95" s="8" t="inlineStr">
         <is>
           <t>Please add</t>
         </is>
@@ -3780,13 +4152,14 @@
       </c>
       <c r="D96" s="6" t="inlineStr"/>
       <c r="E96" s="7" t="n"/>
-      <c r="F96" s="5" t="inlineStr">
+      <c r="F96" s="5" t="inlineStr"/>
+      <c r="G96" s="5" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="G96" s="8" t="inlineStr"/>
-      <c r="H96" s="8" t="inlineStr">
+      <c r="H96" s="8" t="inlineStr"/>
+      <c r="I96" s="8" t="inlineStr">
         <is>
           <t>Please add</t>
         </is>
@@ -3810,13 +4183,14 @@
       </c>
       <c r="D97" s="6" t="inlineStr"/>
       <c r="E97" s="7" t="n"/>
-      <c r="F97" s="5" t="inlineStr">
+      <c r="F97" s="5" t="inlineStr"/>
+      <c r="G97" s="5" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="G97" s="8" t="inlineStr"/>
-      <c r="H97" s="8" t="inlineStr">
+      <c r="H97" s="8" t="inlineStr"/>
+      <c r="I97" s="8" t="inlineStr">
         <is>
           <t>Please add</t>
         </is>
@@ -3848,15 +4222,20 @@
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G98" s="8" t="inlineStr">
+          <t>40–49</t>
+        </is>
+      </c>
+      <c r="G98" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H98" s="8" t="inlineStr">
         <is>
           <t>Fox Chapel age roster, Aug 2025</t>
         </is>
       </c>
-      <c r="H98" s="8" t="inlineStr"/>
+      <c r="I98" s="8" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
@@ -3884,15 +4263,20 @@
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G99" s="8" t="inlineStr">
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="G99" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H99" s="8" t="inlineStr">
         <is>
           <t>Oakmont age roster, Aug 2025</t>
         </is>
       </c>
-      <c r="H99" s="8" t="inlineStr"/>
+      <c r="I99" s="8" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
@@ -3920,15 +4304,20 @@
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G100" s="8" t="inlineStr">
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="G100" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H100" s="8" t="inlineStr">
         <is>
           <t>Oakmont age roster, Aug 2025</t>
         </is>
       </c>
-      <c r="H100" s="8" t="inlineStr"/>
+      <c r="I100" s="8" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
@@ -3948,13 +4337,14 @@
       </c>
       <c r="D101" s="6" t="inlineStr"/>
       <c r="E101" s="7" t="n"/>
-      <c r="F101" s="5" t="inlineStr">
+      <c r="F101" s="5" t="inlineStr"/>
+      <c r="G101" s="5" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="G101" s="8" t="inlineStr"/>
-      <c r="H101" s="8" t="inlineStr">
+      <c r="H101" s="8" t="inlineStr"/>
+      <c r="I101" s="8" t="inlineStr">
         <is>
           <t>Please add</t>
         </is>
@@ -3986,15 +4376,20 @@
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G102" s="8" t="inlineStr">
+          <t>40–49</t>
+        </is>
+      </c>
+      <c r="G102" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H102" s="8" t="inlineStr">
         <is>
           <t>Oakmont age roster, Aug 2025</t>
         </is>
       </c>
-      <c r="H102" s="8" t="inlineStr"/>
+      <c r="I102" s="8" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
@@ -4022,15 +4417,20 @@
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G103" s="8" t="inlineStr">
+          <t>40–49</t>
+        </is>
+      </c>
+      <c r="G103" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H103" s="8" t="inlineStr">
         <is>
           <t>Oakmont age roster, Aug 2025</t>
         </is>
       </c>
-      <c r="H103" s="8" t="inlineStr"/>
+      <c r="I103" s="8" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
@@ -4058,15 +4458,20 @@
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G104" s="8" t="inlineStr">
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="G104" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H104" s="8" t="inlineStr">
         <is>
           <t>Oakmont age roster, Aug 2025</t>
         </is>
       </c>
-      <c r="H104" s="8" t="inlineStr"/>
+      <c r="I104" s="8" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
@@ -4094,15 +4499,20 @@
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G105" s="8" t="inlineStr">
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="G105" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H105" s="8" t="inlineStr">
         <is>
           <t>Oakmont age roster, Aug 2025</t>
         </is>
       </c>
-      <c r="H105" s="8" t="inlineStr"/>
+      <c r="I105" s="8" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
@@ -4130,15 +4540,20 @@
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G106" s="8" t="inlineStr">
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="G106" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H106" s="8" t="inlineStr">
         <is>
           <t>Oakmont age roster, Aug 2025</t>
         </is>
       </c>
-      <c r="H106" s="8" t="inlineStr"/>
+      <c r="I106" s="8" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
@@ -4166,15 +4581,20 @@
       </c>
       <c r="F107" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G107" s="8" t="inlineStr">
+          <t>30–39</t>
+        </is>
+      </c>
+      <c r="G107" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H107" s="8" t="inlineStr">
         <is>
           <t>Oakmont age roster, Aug 2025</t>
         </is>
       </c>
-      <c r="H107" s="8" t="inlineStr"/>
+      <c r="I107" s="8" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
@@ -4202,15 +4622,20 @@
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G108" s="8" t="inlineStr">
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="G108" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H108" s="8" t="inlineStr">
         <is>
           <t>Oakmont age roster, Aug 2025</t>
         </is>
       </c>
-      <c r="H108" s="8" t="inlineStr"/>
+      <c r="I108" s="8" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
@@ -4238,15 +4663,20 @@
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G109" s="8" t="inlineStr">
+          <t>30–39</t>
+        </is>
+      </c>
+      <c r="G109" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H109" s="8" t="inlineStr">
         <is>
           <t>Oakmont age roster, Aug 2025</t>
         </is>
       </c>
-      <c r="H109" s="8" t="inlineStr"/>
+      <c r="I109" s="8" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
@@ -4274,15 +4704,20 @@
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G110" s="8" t="inlineStr">
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="G110" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H110" s="8" t="inlineStr">
         <is>
           <t>Oakmont age roster, Aug 2025</t>
         </is>
       </c>
-      <c r="H110" s="8" t="inlineStr"/>
+      <c r="I110" s="8" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
@@ -4310,15 +4745,20 @@
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G111" s="8" t="inlineStr">
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="G111" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H111" s="8" t="inlineStr">
         <is>
           <t>Oakmont age roster, Aug 2025; the roster's own age column (50 in Oct 2023) agrees. Clint Guyaux (Fox Chapel) carries the same date, probably pasted from this row</t>
         </is>
       </c>
-      <c r="H111" s="8" t="inlineStr"/>
+      <c r="I111" s="8" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
@@ -4346,15 +4786,20 @@
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G112" s="8" t="inlineStr">
+          <t>30–39</t>
+        </is>
+      </c>
+      <c r="G112" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H112" s="8" t="inlineStr">
         <is>
           <t>Oakmont age roster, Aug 2025</t>
         </is>
       </c>
-      <c r="H112" s="8" t="inlineStr"/>
+      <c r="I112" s="8" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
@@ -4382,15 +4827,20 @@
       </c>
       <c r="F113" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G113" s="8" t="inlineStr">
+          <t>40–49</t>
+        </is>
+      </c>
+      <c r="G113" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H113" s="8" t="inlineStr">
         <is>
           <t>Oakmont age roster, Aug 2025</t>
         </is>
       </c>
-      <c r="H113" s="8" t="inlineStr"/>
+      <c r="I113" s="8" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
@@ -4418,15 +4868,20 @@
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G114" s="8" t="inlineStr">
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="G114" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H114" s="8" t="inlineStr">
         <is>
           <t>Oakmont age roster, Aug 2025</t>
         </is>
       </c>
-      <c r="H114" s="8" t="inlineStr"/>
+      <c r="I114" s="8" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
@@ -4446,13 +4901,14 @@
       </c>
       <c r="D115" s="6" t="inlineStr"/>
       <c r="E115" s="7" t="n"/>
-      <c r="F115" s="5" t="inlineStr">
+      <c r="F115" s="5" t="inlineStr"/>
+      <c r="G115" s="5" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="G115" s="8" t="inlineStr"/>
-      <c r="H115" s="8" t="inlineStr">
+      <c r="H115" s="8" t="inlineStr"/>
+      <c r="I115" s="8" t="inlineStr">
         <is>
           <t>Please add</t>
         </is>
@@ -4484,15 +4940,20 @@
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G116" s="8" t="inlineStr">
+          <t>25–29</t>
+        </is>
+      </c>
+      <c r="G116" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H116" s="8" t="inlineStr">
         <is>
           <t>Oakmont age roster, Aug 2025</t>
         </is>
       </c>
-      <c r="H116" s="8" t="inlineStr"/>
+      <c r="I116" s="8" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
@@ -4520,15 +4981,20 @@
       </c>
       <c r="F117" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G117" s="8" t="inlineStr">
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="G117" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H117" s="8" t="inlineStr">
         <is>
           <t>Oakmont age roster, Aug 2025</t>
         </is>
       </c>
-      <c r="H117" s="8" t="inlineStr"/>
+      <c r="I117" s="8" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
@@ -4556,15 +5022,20 @@
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
+          <t>30–39</t>
+        </is>
+      </c>
+      <c r="G118" s="5" t="inlineStr">
+        <is>
           <t>Approximate</t>
         </is>
       </c>
-      <c r="G118" s="8" t="inlineStr">
+      <c r="H118" s="8" t="inlineStr">
         <is>
           <t>Oakmont age roster: 28 in Oct 2023; Emory golf 2014-18 agrees</t>
         </is>
       </c>
-      <c r="H118" s="8" t="inlineStr">
+      <c r="I118" s="8" t="inlineStr">
         <is>
           <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
@@ -4596,15 +5067,20 @@
       </c>
       <c r="F119" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G119" s="8" t="inlineStr">
+          <t>30–39</t>
+        </is>
+      </c>
+      <c r="G119" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H119" s="8" t="inlineStr">
         <is>
           <t>Oakmont age roster, Aug 2025</t>
         </is>
       </c>
-      <c r="H119" s="8" t="inlineStr"/>
+      <c r="I119" s="8" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
@@ -4632,15 +5108,20 @@
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G120" s="8" t="inlineStr">
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="G120" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H120" s="8" t="inlineStr">
         <is>
           <t>Oakmont age roster, Aug 2025</t>
         </is>
       </c>
-      <c r="H120" s="8" t="inlineStr"/>
+      <c r="I120" s="8" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
@@ -4668,15 +5149,20 @@
       </c>
       <c r="F121" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G121" s="8" t="inlineStr">
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="G121" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H121" s="8" t="inlineStr">
         <is>
           <t>Oakmont age roster, Aug 2025</t>
         </is>
       </c>
-      <c r="H121" s="8" t="inlineStr"/>
+      <c r="I121" s="8" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
@@ -4704,15 +5190,20 @@
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
+          <t>30–39</t>
+        </is>
+      </c>
+      <c r="G122" s="5" t="inlineStr">
+        <is>
           <t>Approximate</t>
         </is>
       </c>
-      <c r="G122" s="8" t="inlineStr">
+      <c r="H122" s="8" t="inlineStr">
         <is>
           <t>Oakmont age roster: 30 in Oct 2023</t>
         </is>
       </c>
-      <c r="H122" s="8" t="inlineStr">
+      <c r="I122" s="8" t="inlineStr">
         <is>
           <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
@@ -4744,15 +5235,20 @@
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G123" s="8" t="inlineStr">
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="G123" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H123" s="8" t="inlineStr">
         <is>
           <t>Oakmont age roster, Aug 2025</t>
         </is>
       </c>
-      <c r="H123" s="8" t="inlineStr"/>
+      <c r="I123" s="8" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
@@ -4780,15 +5276,20 @@
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
+          <t>Under 25</t>
+        </is>
+      </c>
+      <c r="G124" s="5" t="inlineStr">
+        <is>
           <t>Approximate</t>
         </is>
       </c>
-      <c r="G124" s="8" t="inlineStr">
+      <c r="H124" s="8" t="inlineStr">
         <is>
           <t>Oakmont age roster: 20 in Oct 2023</t>
         </is>
       </c>
-      <c r="H124" s="8" t="inlineStr">
+      <c r="I124" s="8" t="inlineStr">
         <is>
           <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
@@ -4820,15 +5321,20 @@
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G125" s="8" t="inlineStr">
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="G125" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H125" s="8" t="inlineStr">
         <is>
           <t>Oakmont age roster, Aug 2025</t>
         </is>
       </c>
-      <c r="H125" s="8" t="inlineStr"/>
+      <c r="I125" s="8" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
@@ -4856,15 +5362,20 @@
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G126" s="8" t="inlineStr">
+          <t>30–39</t>
+        </is>
+      </c>
+      <c r="G126" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H126" s="8" t="inlineStr">
         <is>
           <t>Oakmont age roster, Aug 2025</t>
         </is>
       </c>
-      <c r="H126" s="8" t="inlineStr"/>
+      <c r="I126" s="8" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
@@ -4892,15 +5403,20 @@
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G127" s="8" t="inlineStr">
+          <t>30–39</t>
+        </is>
+      </c>
+      <c r="G127" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H127" s="8" t="inlineStr">
         <is>
           <t>Oakmont age roster, Aug 2025</t>
         </is>
       </c>
-      <c r="H127" s="8" t="inlineStr"/>
+      <c r="I127" s="8" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
@@ -4928,15 +5444,20 @@
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G128" s="8" t="inlineStr">
+          <t>30–39</t>
+        </is>
+      </c>
+      <c r="G128" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H128" s="8" t="inlineStr">
         <is>
           <t>Oakmont age roster, Aug 2025</t>
         </is>
       </c>
-      <c r="H128" s="8" t="inlineStr"/>
+      <c r="I128" s="8" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
@@ -4964,15 +5485,20 @@
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G129" s="8" t="inlineStr">
+          <t>25–29</t>
+        </is>
+      </c>
+      <c r="G129" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H129" s="8" t="inlineStr">
         <is>
           <t>Oakmont age roster, Aug 2025</t>
         </is>
       </c>
-      <c r="H129" s="8" t="inlineStr"/>
+      <c r="I129" s="8" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
@@ -5000,15 +5526,20 @@
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G130" s="8" t="inlineStr">
+          <t>30–39</t>
+        </is>
+      </c>
+      <c r="G130" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H130" s="8" t="inlineStr">
         <is>
           <t>Oakmont age roster, Aug 2025</t>
         </is>
       </c>
-      <c r="H130" s="8" t="inlineStr"/>
+      <c r="I130" s="8" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
@@ -5036,15 +5567,20 @@
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G131" s="8" t="inlineStr">
+          <t>30–39</t>
+        </is>
+      </c>
+      <c r="G131" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H131" s="8" t="inlineStr">
         <is>
           <t>Oakmont age roster, Aug 2025</t>
         </is>
       </c>
-      <c r="H131" s="8" t="inlineStr"/>
+      <c r="I131" s="8" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
@@ -5072,15 +5608,20 @@
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G132" s="8" t="inlineStr">
+          <t>30–39</t>
+        </is>
+      </c>
+      <c r="G132" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H132" s="8" t="inlineStr">
         <is>
           <t>PGA Tour player bio (Tom Nettles, McMurray PA)</t>
         </is>
       </c>
-      <c r="H132" s="8" t="inlineStr"/>
+      <c r="I132" s="8" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
@@ -5108,15 +5649,20 @@
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G133" s="8" t="inlineStr">
+          <t>Under 25</t>
+        </is>
+      </c>
+      <c r="G133" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H133" s="8" t="inlineStr">
         <is>
           <t>Oakmont age roster, Aug 2025</t>
         </is>
       </c>
-      <c r="H133" s="8" t="inlineStr"/>
+      <c r="I133" s="8" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
@@ -5144,15 +5690,20 @@
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G134" s="8" t="inlineStr">
+          <t>Under 25</t>
+        </is>
+      </c>
+      <c r="G134" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H134" s="8" t="inlineStr">
         <is>
           <t>High Point University men's golf roster</t>
         </is>
       </c>
-      <c r="H134" s="8" t="inlineStr"/>
+      <c r="I134" s="8" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
@@ -5180,15 +5731,20 @@
       </c>
       <c r="F135" s="5" t="inlineStr">
         <is>
+          <t>Under 25</t>
+        </is>
+      </c>
+      <c r="G135" s="5" t="inlineStr">
+        <is>
           <t>Approximate</t>
         </is>
       </c>
-      <c r="G135" s="8" t="inlineStr">
+      <c r="H135" s="8" t="inlineStr">
         <is>
           <t>Central Catholic class of 2023, Notre Dame class of 2027; 18 on the Oakmont roster in Oct 2023</t>
         </is>
       </c>
-      <c r="H135" s="8" t="inlineStr">
+      <c r="I135" s="8" t="inlineStr">
         <is>
           <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
@@ -5220,15 +5776,20 @@
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
+          <t>Under 25</t>
+        </is>
+      </c>
+      <c r="G136" s="5" t="inlineStr">
+        <is>
           <t>Approximate</t>
         </is>
       </c>
-      <c r="G136" s="8" t="inlineStr">
+      <c r="H136" s="8" t="inlineStr">
         <is>
           <t>Franklin Regional class of 2023; signed with Youngstown State for 2023-24</t>
         </is>
       </c>
-      <c r="H136" s="8" t="inlineStr">
+      <c r="I136" s="8" t="inlineStr">
         <is>
           <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
@@ -5260,15 +5821,20 @@
       </c>
       <c r="F137" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G137" s="8" t="inlineStr">
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="G137" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H137" s="8" t="inlineStr">
         <is>
           <t>Oakmont age roster, Aug 2025</t>
         </is>
       </c>
-      <c r="H137" s="8" t="inlineStr"/>
+      <c r="I137" s="8" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
@@ -5296,15 +5862,20 @@
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G138" s="8" t="inlineStr">
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="G138" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H138" s="8" t="inlineStr">
         <is>
           <t>Oakmont age roster, Aug 2025</t>
         </is>
       </c>
-      <c r="H138" s="8" t="inlineStr"/>
+      <c r="I138" s="8" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
@@ -5332,15 +5903,20 @@
       </c>
       <c r="F139" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G139" s="8" t="inlineStr">
+          <t>40–49</t>
+        </is>
+      </c>
+      <c r="G139" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H139" s="8" t="inlineStr">
         <is>
           <t>Oakmont age roster, Aug 2025</t>
         </is>
       </c>
-      <c r="H139" s="8" t="inlineStr"/>
+      <c r="I139" s="8" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
@@ -5368,15 +5944,20 @@
       </c>
       <c r="F140" s="5" t="inlineStr">
         <is>
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="G140" s="5" t="inlineStr">
+        <is>
           <t>Approximate</t>
         </is>
       </c>
-      <c r="G140" s="8" t="inlineStr">
+      <c r="H140" s="8" t="inlineStr">
         <is>
           <t>Oakmont age roster: 56 in Oct 2023</t>
         </is>
       </c>
-      <c r="H140" s="8" t="inlineStr">
+      <c r="I140" s="8" t="inlineStr">
         <is>
           <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
@@ -5408,15 +5989,20 @@
       </c>
       <c r="F141" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G141" s="8" t="inlineStr">
+          <t>30–39</t>
+        </is>
+      </c>
+      <c r="G141" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H141" s="8" t="inlineStr">
         <is>
           <t>Oakmont age roster, Aug 2025</t>
         </is>
       </c>
-      <c r="H141" s="8" t="inlineStr"/>
+      <c r="I141" s="8" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
@@ -5444,15 +6030,20 @@
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G142" s="8" t="inlineStr">
+          <t>30–39</t>
+        </is>
+      </c>
+      <c r="G142" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H142" s="8" t="inlineStr">
         <is>
           <t>Oakmont age roster, Aug 2025</t>
         </is>
       </c>
-      <c r="H142" s="8" t="inlineStr"/>
+      <c r="I142" s="8" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
@@ -5480,15 +6071,20 @@
       </c>
       <c r="F143" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G143" s="8" t="inlineStr">
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="G143" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H143" s="8" t="inlineStr">
         <is>
           <t>Oakmont age roster, Aug 2025</t>
         </is>
       </c>
-      <c r="H143" s="8" t="inlineStr"/>
+      <c r="I143" s="8" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
@@ -5516,15 +6112,20 @@
       </c>
       <c r="F144" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G144" s="8" t="inlineStr">
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="G144" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H144" s="8" t="inlineStr">
         <is>
           <t>Oakmont age roster, Aug 2025</t>
         </is>
       </c>
-      <c r="H144" s="8" t="inlineStr"/>
+      <c r="I144" s="8" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
@@ -5552,15 +6153,20 @@
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G145" s="8" t="inlineStr">
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="G145" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H145" s="8" t="inlineStr">
         <is>
           <t>Oakmont age roster, Aug 2025</t>
         </is>
       </c>
-      <c r="H145" s="8" t="inlineStr"/>
+      <c r="I145" s="8" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
@@ -5588,15 +6194,20 @@
       </c>
       <c r="F146" s="5" t="inlineStr">
         <is>
+          <t>30–39</t>
+        </is>
+      </c>
+      <c r="G146" s="5" t="inlineStr">
+        <is>
           <t>Approximate</t>
         </is>
       </c>
-      <c r="G146" s="8" t="inlineStr">
+      <c r="H146" s="8" t="inlineStr">
         <is>
           <t>Oakmont age roster: 30 in Oct 2023</t>
         </is>
       </c>
-      <c r="H146" s="8" t="inlineStr">
+      <c r="I146" s="8" t="inlineStr">
         <is>
           <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
@@ -5628,15 +6239,20 @@
       </c>
       <c r="F147" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="G147" s="8" t="inlineStr">
+          <t>30–39</t>
+        </is>
+      </c>
+      <c r="G147" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H147" s="8" t="inlineStr">
         <is>
           <t>Oakmont age roster, Aug 2025</t>
         </is>
       </c>
-      <c r="H147" s="8" t="inlineStr"/>
+      <c r="I147" s="8" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
@@ -5656,13 +6272,14 @@
       </c>
       <c r="D148" s="6" t="inlineStr"/>
       <c r="E148" s="7" t="n"/>
-      <c r="F148" s="5" t="inlineStr">
+      <c r="F148" s="5" t="inlineStr"/>
+      <c r="G148" s="5" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="G148" s="8" t="inlineStr"/>
-      <c r="H148" s="8" t="inlineStr">
+      <c r="H148" s="8" t="inlineStr"/>
+      <c r="I148" s="8" t="inlineStr">
         <is>
           <t>Please add</t>
         </is>
@@ -5686,13 +6303,14 @@
       </c>
       <c r="D149" s="6" t="inlineStr"/>
       <c r="E149" s="7" t="n"/>
-      <c r="F149" s="5" t="inlineStr">
+      <c r="F149" s="5" t="inlineStr"/>
+      <c r="G149" s="5" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="G149" s="8" t="inlineStr"/>
-      <c r="H149" s="8" t="inlineStr">
+      <c r="H149" s="8" t="inlineStr"/>
+      <c r="I149" s="8" t="inlineStr">
         <is>
           <t>Please add</t>
         </is>
@@ -5724,15 +6342,20 @@
       </c>
       <c r="F150" s="5" t="inlineStr">
         <is>
+          <t>30–39</t>
+        </is>
+      </c>
+      <c r="G150" s="5" t="inlineStr">
+        <is>
           <t>Approximate</t>
         </is>
       </c>
-      <c r="G150" s="8" t="inlineStr">
+      <c r="H150" s="8" t="inlineStr">
         <is>
           <t>Fox Chapel HS freshman in 2007, then prep school, class of 2011/12 (Tommy Leech); Hartford golf senior 2015-16</t>
         </is>
       </c>
-      <c r="H150" s="8" t="inlineStr">
+      <c r="I150" s="8" t="inlineStr">
         <is>
           <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
@@ -5756,13 +6379,14 @@
       </c>
       <c r="D151" s="6" t="inlineStr"/>
       <c r="E151" s="7" t="n"/>
-      <c r="F151" s="5" t="inlineStr">
+      <c r="F151" s="5" t="inlineStr"/>
+      <c r="G151" s="5" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="G151" s="8" t="inlineStr"/>
-      <c r="H151" s="8" t="inlineStr">
+      <c r="H151" s="8" t="inlineStr"/>
+      <c r="I151" s="8" t="inlineStr">
         <is>
           <t>Please add</t>
         </is>
@@ -5786,13 +6410,14 @@
       </c>
       <c r="D152" s="6" t="inlineStr"/>
       <c r="E152" s="7" t="n"/>
-      <c r="F152" s="5" t="inlineStr">
+      <c r="F152" s="5" t="inlineStr"/>
+      <c r="G152" s="5" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="G152" s="8" t="inlineStr"/>
-      <c r="H152" s="8" t="inlineStr">
+      <c r="H152" s="8" t="inlineStr"/>
+      <c r="I152" s="8" t="inlineStr">
         <is>
           <t>Please add</t>
         </is>
@@ -5818,13 +6443,22 @@
       <c r="E153" s="7" t="n"/>
       <c r="F153" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="G153" s="8" t="inlineStr"/>
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="G153" s="5" t="inlineStr">
+        <is>
+          <t>Band only</t>
+        </is>
+      </c>
       <c r="H153" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Tommy Leech, Oct 2026</t>
+        </is>
+      </c>
+      <c r="I153" s="8" t="inlineStr">
+        <is>
+          <t>Only an age band is known – a year would be better</t>
         </is>
       </c>
     </row>
@@ -5846,13 +6480,14 @@
       </c>
       <c r="D154" s="6" t="inlineStr"/>
       <c r="E154" s="7" t="n"/>
-      <c r="F154" s="5" t="inlineStr">
+      <c r="F154" s="5" t="inlineStr"/>
+      <c r="G154" s="5" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="G154" s="8" t="inlineStr"/>
-      <c r="H154" s="8" t="inlineStr">
+      <c r="H154" s="8" t="inlineStr"/>
+      <c r="I154" s="8" t="inlineStr">
         <is>
           <t>Please add</t>
         </is>
@@ -5884,15 +6519,20 @@
       </c>
       <c r="F155" s="5" t="inlineStr">
         <is>
+          <t>25–29</t>
+        </is>
+      </c>
+      <c r="G155" s="5" t="inlineStr">
+        <is>
           <t>Approximate</t>
         </is>
       </c>
-      <c r="G155" s="8" t="inlineStr">
+      <c r="H155" s="8" t="inlineStr">
         <is>
           <t>Pittsburgh entrant in 2014 U.S. Junior Amateur qualifying (under 19); uncertain by a year or two</t>
         </is>
       </c>
-      <c r="H155" s="8" t="inlineStr">
+      <c r="I155" s="8" t="inlineStr">
         <is>
           <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
@@ -5916,13 +6556,14 @@
       </c>
       <c r="D156" s="6" t="inlineStr"/>
       <c r="E156" s="7" t="n"/>
-      <c r="F156" s="5" t="inlineStr">
+      <c r="F156" s="5" t="inlineStr"/>
+      <c r="G156" s="5" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="G156" s="8" t="inlineStr"/>
-      <c r="H156" s="8" t="inlineStr">
+      <c r="H156" s="8" t="inlineStr"/>
+      <c r="I156" s="8" t="inlineStr">
         <is>
           <t>Please add</t>
         </is>
@@ -5948,13 +6589,22 @@
       <c r="E157" s="7" t="n"/>
       <c r="F157" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="G157" s="8" t="inlineStr"/>
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="G157" s="5" t="inlineStr">
+        <is>
+          <t>Band only</t>
+        </is>
+      </c>
       <c r="H157" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Tommy Leech, Oct 2026</t>
+        </is>
+      </c>
+      <c r="I157" s="8" t="inlineStr">
+        <is>
+          <t>Only an age band is known – a year would be better</t>
         </is>
       </c>
     </row>
@@ -5976,13 +6626,14 @@
       </c>
       <c r="D158" s="6" t="inlineStr"/>
       <c r="E158" s="7" t="n"/>
-      <c r="F158" s="5" t="inlineStr">
+      <c r="F158" s="5" t="inlineStr"/>
+      <c r="G158" s="5" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="G158" s="8" t="inlineStr"/>
-      <c r="H158" s="8" t="inlineStr">
+      <c r="H158" s="8" t="inlineStr"/>
+      <c r="I158" s="8" t="inlineStr">
         <is>
           <t>Please add</t>
         </is>
@@ -6014,15 +6665,20 @@
       </c>
       <c r="F159" s="5" t="inlineStr">
         <is>
+          <t>40–49</t>
+        </is>
+      </c>
+      <c r="G159" s="5" t="inlineStr">
+        <is>
           <t>Approximate</t>
         </is>
       </c>
-      <c r="G159" s="8" t="inlineStr">
+      <c r="H159" s="8" t="inlineStr">
         <is>
           <t>Age 45 in Poets &amp; Quants profile, 2025</t>
         </is>
       </c>
-      <c r="H159" s="8" t="inlineStr">
+      <c r="I159" s="8" t="inlineStr">
         <is>
           <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
@@ -6046,13 +6702,14 @@
       </c>
       <c r="D160" s="6" t="inlineStr"/>
       <c r="E160" s="7" t="n"/>
-      <c r="F160" s="5" t="inlineStr">
+      <c r="F160" s="5" t="inlineStr"/>
+      <c r="G160" s="5" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="G160" s="8" t="inlineStr"/>
-      <c r="H160" s="8" t="inlineStr">
+      <c r="H160" s="8" t="inlineStr"/>
+      <c r="I160" s="8" t="inlineStr">
         <is>
           <t>Please add</t>
         </is>
@@ -6076,13 +6733,14 @@
       </c>
       <c r="D161" s="6" t="inlineStr"/>
       <c r="E161" s="7" t="n"/>
-      <c r="F161" s="5" t="inlineStr">
+      <c r="F161" s="5" t="inlineStr"/>
+      <c r="G161" s="5" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="G161" s="8" t="inlineStr"/>
-      <c r="H161" s="8" t="inlineStr">
+      <c r="H161" s="8" t="inlineStr"/>
+      <c r="I161" s="8" t="inlineStr">
         <is>
           <t>Please add</t>
         </is>
@@ -6106,13 +6764,14 @@
       </c>
       <c r="D162" s="6" t="inlineStr"/>
       <c r="E162" s="7" t="n"/>
-      <c r="F162" s="5" t="inlineStr">
+      <c r="F162" s="5" t="inlineStr"/>
+      <c r="G162" s="5" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="G162" s="8" t="inlineStr"/>
-      <c r="H162" s="8" t="inlineStr">
+      <c r="H162" s="8" t="inlineStr"/>
+      <c r="I162" s="8" t="inlineStr">
         <is>
           <t>Please add</t>
         </is>
@@ -6136,13 +6795,14 @@
       </c>
       <c r="D163" s="6" t="inlineStr"/>
       <c r="E163" s="7" t="n"/>
-      <c r="F163" s="5" t="inlineStr">
+      <c r="F163" s="5" t="inlineStr"/>
+      <c r="G163" s="5" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="G163" s="8" t="inlineStr"/>
-      <c r="H163" s="8" t="inlineStr">
+      <c r="H163" s="8" t="inlineStr"/>
+      <c r="I163" s="8" t="inlineStr">
         <is>
           <t>Please add</t>
         </is>
@@ -6166,13 +6826,14 @@
       </c>
       <c r="D164" s="6" t="inlineStr"/>
       <c r="E164" s="7" t="n"/>
-      <c r="F164" s="5" t="inlineStr">
+      <c r="F164" s="5" t="inlineStr"/>
+      <c r="G164" s="5" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="G164" s="8" t="inlineStr"/>
-      <c r="H164" s="8" t="inlineStr">
+      <c r="H164" s="8" t="inlineStr"/>
+      <c r="I164" s="8" t="inlineStr">
         <is>
           <t>Please add</t>
         </is>
@@ -6196,13 +6857,14 @@
       </c>
       <c r="D165" s="6" t="inlineStr"/>
       <c r="E165" s="7" t="n"/>
-      <c r="F165" s="5" t="inlineStr">
+      <c r="F165" s="5" t="inlineStr"/>
+      <c r="G165" s="5" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="G165" s="8" t="inlineStr"/>
-      <c r="H165" s="8" t="inlineStr">
+      <c r="H165" s="8" t="inlineStr"/>
+      <c r="I165" s="8" t="inlineStr">
         <is>
           <t>Please add</t>
         </is>
@@ -6234,15 +6896,20 @@
       </c>
       <c r="F166" s="5" t="inlineStr">
         <is>
+          <t>30–39</t>
+        </is>
+      </c>
+      <c r="G166" s="5" t="inlineStr">
+        <is>
           <t>Approximate</t>
         </is>
       </c>
-      <c r="G166" s="8" t="inlineStr">
+      <c r="H166" s="8" t="inlineStr">
         <is>
           <t>Shady Side Academy; senior on the South Carolina golf roster 2015-16</t>
         </is>
       </c>
-      <c r="H166" s="8" t="inlineStr">
+      <c r="I166" s="8" t="inlineStr">
         <is>
           <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
@@ -6274,15 +6941,20 @@
       </c>
       <c r="F167" s="5" t="inlineStr">
         <is>
+          <t>25–29</t>
+        </is>
+      </c>
+      <c r="G167" s="5" t="inlineStr">
+        <is>
           <t>Approximate</t>
         </is>
       </c>
-      <c r="G167" s="8" t="inlineStr">
+      <c r="H167" s="8" t="inlineStr">
         <is>
           <t>Shaler graduate; Findlay golf, senior in 2023; uncertain by a year or two</t>
         </is>
       </c>
-      <c r="H167" s="8" t="inlineStr">
+      <c r="I167" s="8" t="inlineStr">
         <is>
           <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
@@ -6304,17 +6976,32 @@
           <t>2012–2023</t>
         </is>
       </c>
-      <c r="D168" s="6" t="inlineStr"/>
-      <c r="E168" s="7" t="n"/>
+      <c r="D168" s="6" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="E168" s="7" t="n">
+        <v>1984</v>
+      </c>
       <c r="F168" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="G168" s="8" t="inlineStr"/>
+          <t>40–49</t>
+        </is>
+      </c>
+      <c r="G168" s="5" t="inlineStr">
+        <is>
+          <t>Approximate</t>
+        </is>
+      </c>
       <c r="H168" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>About 42 in Oct 2026 (Tommy Leech)</t>
+        </is>
+      </c>
+      <c r="I168" s="8" t="inlineStr">
+        <is>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
       </c>
     </row>
@@ -6334,17 +7021,32 @@
           <t>2015–2025</t>
         </is>
       </c>
-      <c r="D169" s="6" t="inlineStr"/>
-      <c r="E169" s="7" t="n"/>
+      <c r="D169" s="6" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="E169" s="7" t="n">
+        <v>1990</v>
+      </c>
       <c r="F169" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="G169" s="8" t="inlineStr"/>
+          <t>30–39</t>
+        </is>
+      </c>
+      <c r="G169" s="5" t="inlineStr">
+        <is>
+          <t>Approximate</t>
+        </is>
+      </c>
       <c r="H169" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>About 36 in Oct 2026 (Tommy Leech)</t>
+        </is>
+      </c>
+      <c r="I169" s="8" t="inlineStr">
+        <is>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
       </c>
     </row>
@@ -6374,15 +7076,20 @@
       </c>
       <c r="F170" s="5" t="inlineStr">
         <is>
+          <t>30–39</t>
+        </is>
+      </c>
+      <c r="G170" s="5" t="inlineStr">
+        <is>
           <t>Approximate</t>
         </is>
       </c>
-      <c r="G170" s="8" t="inlineStr">
+      <c r="H170" s="8" t="inlineStr">
         <is>
           <t>Deer Lakes; Penn State Behrend golf 2009-11</t>
         </is>
       </c>
-      <c r="H170" s="8" t="inlineStr">
+      <c r="I170" s="8" t="inlineStr">
         <is>
           <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
@@ -6406,13 +7113,14 @@
       </c>
       <c r="D171" s="6" t="inlineStr"/>
       <c r="E171" s="7" t="n"/>
-      <c r="F171" s="5" t="inlineStr">
+      <c r="F171" s="5" t="inlineStr"/>
+      <c r="G171" s="5" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="G171" s="8" t="inlineStr"/>
-      <c r="H171" s="8" t="inlineStr">
+      <c r="H171" s="8" t="inlineStr"/>
+      <c r="I171" s="8" t="inlineStr">
         <is>
           <t>Please add</t>
         </is>
@@ -6436,13 +7144,14 @@
       </c>
       <c r="D172" s="6" t="inlineStr"/>
       <c r="E172" s="7" t="n"/>
-      <c r="F172" s="5" t="inlineStr">
+      <c r="F172" s="5" t="inlineStr"/>
+      <c r="G172" s="5" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="G172" s="8" t="inlineStr"/>
-      <c r="H172" s="8" t="inlineStr">
+      <c r="H172" s="8" t="inlineStr"/>
+      <c r="I172" s="8" t="inlineStr">
         <is>
           <t>Please add</t>
         </is>
@@ -6468,13 +7177,22 @@
       <c r="E173" s="7" t="n"/>
       <c r="F173" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="G173" s="8" t="inlineStr"/>
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="G173" s="5" t="inlineStr">
+        <is>
+          <t>Band only</t>
+        </is>
+      </c>
       <c r="H173" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Tommy Leech, Oct 2026</t>
+        </is>
+      </c>
+      <c r="I173" s="8" t="inlineStr">
+        <is>
+          <t>Only an age band is known – a year would be better</t>
         </is>
       </c>
     </row>
@@ -6504,15 +7222,20 @@
       </c>
       <c r="F174" s="5" t="inlineStr">
         <is>
+          <t>Under 25</t>
+        </is>
+      </c>
+      <c r="G174" s="5" t="inlineStr">
+        <is>
           <t>Approximate</t>
         </is>
       </c>
-      <c r="G174" s="8" t="inlineStr">
+      <c r="H174" s="8" t="inlineStr">
         <is>
           <t>Fox Chapel HS junior in fall 2019 (WPIAL 3A, T3)</t>
         </is>
       </c>
-      <c r="H174" s="8" t="inlineStr">
+      <c r="I174" s="8" t="inlineStr">
         <is>
           <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
@@ -6536,13 +7259,14 @@
       </c>
       <c r="D175" s="6" t="inlineStr"/>
       <c r="E175" s="7" t="n"/>
-      <c r="F175" s="5" t="inlineStr">
+      <c r="F175" s="5" t="inlineStr"/>
+      <c r="G175" s="5" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="G175" s="8" t="inlineStr"/>
-      <c r="H175" s="8" t="inlineStr">
+      <c r="H175" s="8" t="inlineStr"/>
+      <c r="I175" s="8" t="inlineStr">
         <is>
           <t>Please add</t>
         </is>
@@ -6574,15 +7298,20 @@
       </c>
       <c r="F176" s="5" t="inlineStr">
         <is>
+          <t>40–49</t>
+        </is>
+      </c>
+      <c r="G176" s="5" t="inlineStr">
+        <is>
           <t>Approximate</t>
         </is>
       </c>
-      <c r="G176" s="8" t="inlineStr">
+      <c r="H176" s="8" t="inlineStr">
         <is>
           <t>Serra Catholic; senior on the Marshall golf roster 2007-08</t>
         </is>
       </c>
-      <c r="H176" s="8" t="inlineStr">
+      <c r="I176" s="8" t="inlineStr">
         <is>
           <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
@@ -6614,15 +7343,20 @@
       </c>
       <c r="F177" s="5" t="inlineStr">
         <is>
+          <t>40–49</t>
+        </is>
+      </c>
+      <c r="G177" s="5" t="inlineStr">
+        <is>
           <t>Approximate</t>
         </is>
       </c>
-      <c r="G177" s="8" t="inlineStr">
+      <c r="H177" s="8" t="inlineStr">
         <is>
           <t>Allegheny College class of 2005 (athletics hall of fame)</t>
         </is>
       </c>
-      <c r="H177" s="8" t="inlineStr">
+      <c r="I177" s="8" t="inlineStr">
         <is>
           <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
@@ -6646,13 +7380,14 @@
       </c>
       <c r="D178" s="6" t="inlineStr"/>
       <c r="E178" s="7" t="n"/>
-      <c r="F178" s="5" t="inlineStr">
+      <c r="F178" s="5" t="inlineStr"/>
+      <c r="G178" s="5" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="G178" s="8" t="inlineStr"/>
-      <c r="H178" s="8" t="inlineStr">
+      <c r="H178" s="8" t="inlineStr"/>
+      <c r="I178" s="8" t="inlineStr">
         <is>
           <t>Please add</t>
         </is>
@@ -6676,13 +7411,14 @@
       </c>
       <c r="D179" s="6" t="inlineStr"/>
       <c r="E179" s="7" t="n"/>
-      <c r="F179" s="5" t="inlineStr">
+      <c r="F179" s="5" t="inlineStr"/>
+      <c r="G179" s="5" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="G179" s="8" t="inlineStr"/>
-      <c r="H179" s="8" t="inlineStr">
+      <c r="H179" s="8" t="inlineStr"/>
+      <c r="I179" s="8" t="inlineStr">
         <is>
           <t>Please add</t>
         </is>
@@ -6714,15 +7450,20 @@
       </c>
       <c r="F180" s="5" t="inlineStr">
         <is>
+          <t>Under 25</t>
+        </is>
+      </c>
+      <c r="G180" s="5" t="inlineStr">
+        <is>
           <t>Approximate</t>
         </is>
       </c>
-      <c r="G180" s="8" t="inlineStr">
+      <c r="H180" s="8" t="inlineStr">
         <is>
           <t>Shady Side Academy sophomore in fall 2018 (IPSL medalist)</t>
         </is>
       </c>
-      <c r="H180" s="8" t="inlineStr">
+      <c r="I180" s="8" t="inlineStr">
         <is>
           <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
@@ -6746,13 +7487,14 @@
       </c>
       <c r="D181" s="6" t="inlineStr"/>
       <c r="E181" s="7" t="n"/>
-      <c r="F181" s="5" t="inlineStr">
+      <c r="F181" s="5" t="inlineStr"/>
+      <c r="G181" s="5" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="G181" s="8" t="inlineStr"/>
-      <c r="H181" s="8" t="inlineStr">
+      <c r="H181" s="8" t="inlineStr"/>
+      <c r="I181" s="8" t="inlineStr">
         <is>
           <t>Please add</t>
         </is>
@@ -6776,13 +7518,14 @@
       </c>
       <c r="D182" s="6" t="inlineStr"/>
       <c r="E182" s="7" t="n"/>
-      <c r="F182" s="5" t="inlineStr">
+      <c r="F182" s="5" t="inlineStr"/>
+      <c r="G182" s="5" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="G182" s="8" t="inlineStr"/>
-      <c r="H182" s="8" t="inlineStr">
+      <c r="H182" s="8" t="inlineStr"/>
+      <c r="I182" s="8" t="inlineStr">
         <is>
           <t>Please add</t>
         </is>
@@ -6806,13 +7549,14 @@
       </c>
       <c r="D183" s="6" t="inlineStr"/>
       <c r="E183" s="7" t="n"/>
-      <c r="F183" s="5" t="inlineStr">
+      <c r="F183" s="5" t="inlineStr"/>
+      <c r="G183" s="5" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="G183" s="8" t="inlineStr"/>
-      <c r="H183" s="8" t="inlineStr">
+      <c r="H183" s="8" t="inlineStr"/>
+      <c r="I183" s="8" t="inlineStr">
         <is>
           <t>Please add</t>
         </is>
@@ -6836,13 +7580,14 @@
       </c>
       <c r="D184" s="6" t="inlineStr"/>
       <c r="E184" s="7" t="n"/>
-      <c r="F184" s="5" t="inlineStr">
+      <c r="F184" s="5" t="inlineStr"/>
+      <c r="G184" s="5" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="G184" s="8" t="inlineStr"/>
-      <c r="H184" s="8" t="inlineStr">
+      <c r="H184" s="8" t="inlineStr"/>
+      <c r="I184" s="8" t="inlineStr">
         <is>
           <t>Please add</t>
         </is>
@@ -6866,13 +7611,14 @@
       </c>
       <c r="D185" s="6" t="inlineStr"/>
       <c r="E185" s="7" t="n"/>
-      <c r="F185" s="5" t="inlineStr">
+      <c r="F185" s="5" t="inlineStr"/>
+      <c r="G185" s="5" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="G185" s="8" t="inlineStr"/>
-      <c r="H185" s="8" t="inlineStr">
+      <c r="H185" s="8" t="inlineStr"/>
+      <c r="I185" s="8" t="inlineStr">
         <is>
           <t>Please add</t>
         </is>
@@ -6904,15 +7650,20 @@
       </c>
       <c r="F186" s="5" t="inlineStr">
         <is>
+          <t>25–29</t>
+        </is>
+      </c>
+      <c r="G186" s="5" t="inlineStr">
+        <is>
           <t>Approximate</t>
         </is>
       </c>
-      <c r="G186" s="8" t="inlineStr">
+      <c r="H186" s="8" t="inlineStr">
         <is>
           <t>Pine-Richland golfer at the 2018 PIAA championship; class year not found, uncertain</t>
         </is>
       </c>
-      <c r="H186" s="8" t="inlineStr">
+      <c r="I186" s="8" t="inlineStr">
         <is>
           <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
@@ -6944,22 +7695,27 @@
       </c>
       <c r="F187" s="5" t="inlineStr">
         <is>
+          <t>Under 25</t>
+        </is>
+      </c>
+      <c r="G187" s="5" t="inlineStr">
+        <is>
           <t>Approximate</t>
         </is>
       </c>
-      <c r="G187" s="8" t="inlineStr">
+      <c r="H187" s="8" t="inlineStr">
         <is>
           <t>Fox Chapel HS junior in fall 2020</t>
         </is>
       </c>
-      <c r="H187" s="8" t="inlineStr">
+      <c r="I187" s="8" t="inlineStr">
         <is>
           <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:H187"/>
+  <autoFilter ref="A5:I187"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6970,7 +7726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6978,7 +7734,8 @@
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7016,6 +7773,11 @@
       </c>
       <c r="F3" s="10" t="inlineStr">
         <is>
+          <t>Band only</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
           <t>Missing</t>
         </is>
       </c>
@@ -7039,6 +7801,9 @@
         <v>0</v>
       </c>
       <c r="F4" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7061,6 +7826,9 @@
         <v>3</v>
       </c>
       <c r="F5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="11" t="n">
         <v>22</v>
       </c>
     </row>
@@ -7083,6 +7851,9 @@
         <v>0</v>
       </c>
       <c r="F6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="11" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7099,13 +7870,16 @@
         <v>0</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E7" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>28</v>
+        <v>3</v>
+      </c>
+      <c r="G7" s="11" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="8">
@@ -7121,25 +7895,28 @@
         <v>92</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>3</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>53</v>
+        <v>3</v>
+      </c>
+      <c r="G8" s="12" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="10" ht="45" customHeight="1">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>Status key: Recorded = full or month date from a roster or public record. Approximate = year inferred from an age or school class. Please confirm = roster date duplicated between two players. Missing = nothing on file.</t>
+          <t>Status key: Recorded = full or month date from a roster or public record. Approximate = year inferred from an age or school class. Please confirm = roster date duplicated between two players. Band only = an age band but no year. Missing = nothing on file.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A10:G10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/diebold-birth-dates.xlsx
+++ b/reports/diebold-birth-dates.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Birth dates'!$A$5:$I$187</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Birth dates'!$A$5:$I$186</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I187"/>
+  <dimension ref="A1:I186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -758,28 +758,38 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Damon Claus</t>
+          <t>DJ Claus</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr"/>
-      <c r="E10" s="7" t="n"/>
-      <c r="F10" s="5" t="inlineStr"/>
+          <t>2017–2024</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>15 Jun 1983</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>1983</v>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>40–49</t>
+        </is>
+      </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="inlineStr"/>
-      <c r="I10" s="8" t="inlineStr">
-        <is>
-          <t>Please add</t>
-        </is>
-      </c>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>Field Club age roster, Aug 2025; full date from Tommy Leech, Oct 2026</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -789,25 +799,25 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>DJ Claus</t>
+          <t>Paul Curry</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>2017–2020</t>
+          <t>2000–2015</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>15 Jun 1983</t>
+          <t>Sep 1960</t>
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1983</v>
+        <v>1960</v>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>40–49</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -817,7 +827,7 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>Field Club age roster, Aug 2025; full date from Tommy Leech, Oct 2026</t>
+          <t>Field Club age roster, Aug 2025 (month and year only)</t>
         </is>
       </c>
       <c r="I11" s="8" t="inlineStr"/>
@@ -830,25 +840,25 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Paul Curry</t>
+          <t>Tim Dodson</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>2000–2015</t>
+          <t>2008–2023</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Sep 1960</t>
+          <t>Sep 1987</t>
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>1960</v>
+        <v>1987</v>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>30–39</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -871,21 +881,21 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Tim Dodson</t>
+          <t>Matt Dunlap</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>2008–2023</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Sep 1987</t>
+          <t>7 Dec 1993</t>
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>1987</v>
+        <v>1993</v>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
@@ -899,7 +909,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>Field Club age roster, Aug 2025 (month and year only)</t>
+          <t>Tommy Leech, Oct 2026</t>
         </is>
       </c>
       <c r="I13" s="8" t="inlineStr"/>
@@ -912,25 +922,25 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Matt Dunlap</t>
+          <t>Jordan Dunsmore</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2016–2021</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>7 Dec 1993</t>
+          <t>Oct 1984</t>
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>1993</v>
+        <v>1984</v>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>30–39</t>
+          <t>40–49</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -940,7 +950,7 @@
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>Tommy Leech, Oct 2026</t>
+          <t>Field Club age roster, Aug 2025 (month and year only)</t>
         </is>
       </c>
       <c r="I14" s="8" t="inlineStr"/>
@@ -953,25 +963,25 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Jordan Dunsmore</t>
+          <t>Brendan Eisenbrandt</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>2016–2021</t>
+          <t>2007–2014</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Oct 1984</t>
+          <t>Sep 1989</t>
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>1984</v>
+        <v>1989</v>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>40–49</t>
+          <t>30–39</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
@@ -994,21 +1004,21 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Brendan Eisenbrandt</t>
+          <t>Dom Fazio</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>2007–2014</t>
+          <t>2024–2025</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Sep 1989</t>
+          <t>24 May 1993</t>
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>1989</v>
+        <v>1993</v>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
@@ -1022,7 +1032,7 @@
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>Field Club age roster, Aug 2025 (month and year only)</t>
+          <t>Tommy Leech, Oct 2026</t>
         </is>
       </c>
       <c r="I16" s="8" t="inlineStr"/>
@@ -1035,21 +1045,21 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Dom Fazio</t>
+          <t>Graham Friday</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>2024–2025</t>
+          <t>2018–2024</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>24 May 1993</t>
+          <t>May 1994</t>
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
@@ -1063,7 +1073,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>Tommy Leech, Oct 2026</t>
+          <t>Field Club age roster, Aug 2025 (month and year only)</t>
         </is>
       </c>
       <c r="I17" s="8" t="inlineStr"/>
@@ -1076,38 +1086,42 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Graham Friday</t>
+          <t>R. Frohlich</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>2018–2024</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>May 1994</t>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>2007</t>
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>1994</v>
+        <v>2007</v>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>30–39</t>
+          <t>Under 25</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Approximate</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>Field Club age roster, Aug 2025 (month and year only)</t>
-        </is>
-      </c>
-      <c r="I18" s="8" t="inlineStr"/>
+          <t>High school class of 2025 (Tommy Leech)</t>
+        </is>
+      </c>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -1117,42 +1131,38 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>R. Frohlich</t>
+          <t>Frank Fuhrer III</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>2007</t>
+          <t>2000–2025</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Dec 1958</t>
         </is>
       </c>
       <c r="E19" s="7" t="n">
-        <v>2007</v>
+        <v>1958</v>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Under 25</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Approximate</t>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>High school class of 2025 (Tommy Leech)</t>
-        </is>
-      </c>
-      <c r="I19" s="8" t="inlineStr">
-        <is>
-          <t>Year only, worked out from an age or school year – a real date would be better</t>
-        </is>
-      </c>
+          <t>Field Club age roster, Aug 2025 (month and year only)</t>
+        </is>
+      </c>
+      <c r="I19" s="8" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -1162,38 +1172,42 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Frank Fuhrer III</t>
+          <t>Frank Fuhrer IV</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>2000–2025</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>Dec 1958</t>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>1999</t>
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>1958</v>
+        <v>1999</v>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>25–29</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Approximate</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>Field Club age roster, Aug 2025 (month and year only)</t>
-        </is>
-      </c>
-      <c r="I20" s="8" t="inlineStr"/>
+          <t>Shady Side Academy senior in fall 2017</t>
+        </is>
+      </c>
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -1203,21 +1217,21 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Frank Fuhrer IV</t>
+          <t>Jas Fuhrer</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>1999</t>
+          <t>2019–2025</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Nov 2000</t>
         </is>
       </c>
       <c r="E21" s="7" t="n">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
@@ -1226,19 +1240,15 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Approximate</t>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>Shady Side Academy senior in fall 2017</t>
-        </is>
-      </c>
-      <c r="I21" s="8" t="inlineStr">
-        <is>
-          <t>Year only, worked out from an age or school year – a real date would be better</t>
-        </is>
-      </c>
+          <t>Field Club age roster, Aug 2025 (month and year only)</t>
+        </is>
+      </c>
+      <c r="I21" s="8" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -1248,25 +1258,25 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Jas Fuhrer</t>
+          <t>John Ifft</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>2019–2025</t>
+          <t>2003–2013</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Nov 2000</t>
+          <t>Jan 1973</t>
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>2000</v>
+        <v>1973</v>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>25–29</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -1289,21 +1299,21 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>John Ifft</t>
+          <t>Greg Jacobs</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>2003–2013</t>
+          <t>2013–2018</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Jan 1973</t>
+          <t>Jul 1963</t>
         </is>
       </c>
       <c r="E23" s="7" t="n">
-        <v>1973</v>
+        <v>1963</v>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
@@ -1330,25 +1340,25 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Greg Jacobs</t>
+          <t>Jack Katarincic</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>2013–2018</t>
+          <t>2014–2023</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Jul 1963</t>
+          <t>Apr 1998</t>
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>1963</v>
+        <v>1998</v>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>25–29</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
@@ -1371,25 +1381,25 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Jack Katarincic</t>
+          <t>Tommy Leech</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>2014–2023</t>
+          <t>2010–2025</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Apr 1998</t>
+          <t>Dec 1992</t>
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>1998</v>
+        <v>1992</v>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>25–29</t>
+          <t>30–39</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
@@ -1412,21 +1422,21 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Tommy Leech</t>
+          <t>Will Maher</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>2010–2025</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>Dec 1992</t>
+          <t>2014–2015</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>1994</t>
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>1992</v>
+        <v>1994</v>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
@@ -1435,15 +1445,19 @@
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Approximate</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>Field Club age roster, Aug 2025 (month and year only)</t>
-        </is>
-      </c>
-      <c r="I26" s="8" t="inlineStr"/>
+          <t>High school class of 2012 (Tommy Leech)</t>
+        </is>
+      </c>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -1453,42 +1467,38 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Will Maher</t>
+          <t>John Marous III</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>2014–2015</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>1994</t>
+          <t>2003–2025</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Sep 1959</t>
         </is>
       </c>
       <c r="E27" s="7" t="n">
-        <v>1994</v>
+        <v>1959</v>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>30–39</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>Approximate</t>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>High school class of 2012 (Tommy Leech)</t>
-        </is>
-      </c>
-      <c r="I27" s="8" t="inlineStr">
-        <is>
-          <t>Year only, worked out from an age or school year – a real date would be better</t>
-        </is>
-      </c>
+          <t>Field Club age roster, Aug 2025 (month and year only)</t>
+        </is>
+      </c>
+      <c r="I27" s="8" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -1498,25 +1508,25 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>John Marous III</t>
+          <t>Matt Mattioli</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>2003–2025</t>
+          <t>2020–2025</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Sep 1959</t>
+          <t>Jun 2002</t>
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>1959</v>
+        <v>2002</v>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Under 25</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
@@ -1539,25 +1549,25 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Matt Mattioli</t>
+          <t>S. McInerney</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>2020–2025</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Jun 2002</t>
+          <t>Oct 1997</t>
         </is>
       </c>
       <c r="E29" s="7" t="n">
-        <v>2002</v>
+        <v>1997</v>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>Under 25</t>
+          <t>25–29</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -1580,25 +1590,25 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>S. McInerney</t>
+          <t>K. McKamish</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Oct 1997</t>
+          <t>Dec 1991</t>
         </is>
       </c>
       <c r="E30" s="7" t="n">
-        <v>1997</v>
+        <v>1991</v>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>25–29</t>
+          <t>30–39</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
@@ -1621,25 +1631,25 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>K. McKamish</t>
+          <t>Will McMahon</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2015–2025</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Dec 1991</t>
+          <t>Sep 1997</t>
         </is>
       </c>
       <c r="E31" s="7" t="n">
-        <v>1991</v>
+        <v>1997</v>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>30–39</t>
+          <t>25–29</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -1662,25 +1672,25 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Will McMahon</t>
+          <t>Derek Mousseau</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>2015–2025</t>
+          <t>2016–2025</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Sep 1997</t>
+          <t>Oct 1983</t>
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>1997</v>
+        <v>1983</v>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>25–29</t>
+          <t>40–49</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
@@ -1703,25 +1713,25 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Derek Mousseau</t>
+          <t>Kevin O'Brien</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>2016–2025</t>
+          <t>2023–2025</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Oct 1983</t>
+          <t>Apr 1995</t>
         </is>
       </c>
       <c r="E33" s="7" t="n">
-        <v>1983</v>
+        <v>1995</v>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>40–49</t>
+          <t>30–39</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -1744,25 +1754,25 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Kevin O'Brien</t>
+          <t>Gordy Opitz</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>2023–2025</t>
+          <t>2000–2020</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Apr 1995</t>
+          <t>Sep 1957</t>
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>1995</v>
+        <v>1957</v>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>30–39</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
@@ -1785,21 +1795,21 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Gordy Opitz</t>
+          <t>Ron Richards</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>2000–2020</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Sep 1957</t>
+          <t>Feb 1963</t>
         </is>
       </c>
       <c r="E35" s="7" t="n">
-        <v>1957</v>
+        <v>1963</v>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
@@ -1826,25 +1836,25 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Ron Richards</t>
+          <t>JM Ruscetti</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2001–2025</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Feb 1963</t>
+          <t>Jun 1983</t>
         </is>
       </c>
       <c r="E36" s="7" t="n">
-        <v>1963</v>
+        <v>1983</v>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>40–49</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
@@ -1867,21 +1877,21 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>JM Ruscetti</t>
+          <t>Patrick Sherry</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>2001–2025</t>
+          <t>2022–2025</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Jun 1983</t>
+          <t>Aug 1986</t>
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>1983</v>
+        <v>1986</v>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
@@ -1908,25 +1918,25 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Patrick Sherry</t>
+          <t>Pat Smith</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>2022–2025</t>
+          <t>2008–2024</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Aug 1986</t>
+          <t>May 1967</t>
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>1986</v>
+        <v>1967</v>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>40–49</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
@@ -1949,25 +1959,25 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Pat Smith</t>
+          <t>G. Thiele</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>2008–2024</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>May 1967</t>
+          <t>Feb 2002</t>
         </is>
       </c>
       <c r="E39" s="7" t="n">
-        <v>1967</v>
+        <v>2002</v>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Under 25</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -1990,25 +2000,25 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>G. Thiele</t>
+          <t>Jon Thomas</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2000–2024</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Feb 2002</t>
+          <t>Aug 1982</t>
         </is>
       </c>
       <c r="E40" s="7" t="n">
-        <v>2002</v>
+        <v>1982</v>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Under 25</t>
+          <t>40–49</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
@@ -2031,21 +2041,21 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Jon Thomas</t>
+          <t>Tucker Veenis</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>2000–2024</t>
+          <t>2003–2017</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Aug 1982</t>
+          <t>May 1981</t>
         </is>
       </c>
       <c r="E41" s="7" t="n">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
@@ -2072,25 +2082,25 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Tucker Veenis</t>
+          <t>Andrew Wallisch</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>2003–2017</t>
+          <t>2007–2025</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>May 1981</t>
+          <t>Jan 1989</t>
         </is>
       </c>
       <c r="E42" s="7" t="n">
-        <v>1981</v>
+        <v>1989</v>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>40–49</t>
+          <t>30–39</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
@@ -2113,25 +2123,25 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Andrew Wallisch</t>
+          <t>J. Wallisch</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>2007–2025</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Jan 1989</t>
+          <t>Jul 1957</t>
         </is>
       </c>
       <c r="E43" s="7" t="n">
-        <v>1989</v>
+        <v>1957</v>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>30–39</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -2154,25 +2164,25 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>J. Wallisch</t>
+          <t>Wes Warden</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2020–2023</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Jul 1957</t>
+          <t>Aug 2002</t>
         </is>
       </c>
       <c r="E44" s="7" t="n">
-        <v>1957</v>
+        <v>2002</v>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Under 25</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
@@ -2195,25 +2205,25 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Wes Warden</t>
+          <t>Dave Weber</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>2020–2023</t>
+          <t>2009–2023</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Aug 2002</t>
+          <t>Feb 1981</t>
         </is>
       </c>
       <c r="E45" s="7" t="n">
-        <v>2002</v>
+        <v>1981</v>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Under 25</t>
+          <t>40–49</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -2231,43 +2241,33 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>Field Club</t>
+          <t>Fox Chapel</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Dave Weber</t>
+          <t>L. Astorino</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>2009–2023</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>Feb 1981</t>
-        </is>
-      </c>
-      <c r="E46" s="7" t="n">
-        <v>1981</v>
-      </c>
-      <c r="F46" s="5" t="inlineStr">
-        <is>
-          <t>40–49</t>
-        </is>
-      </c>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr"/>
+      <c r="E46" s="7" t="n"/>
+      <c r="F46" s="5" t="inlineStr"/>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="H46" s="8" t="inlineStr">
-        <is>
-          <t>Field Club age roster, Aug 2025 (month and year only)</t>
-        </is>
-      </c>
-      <c r="I46" s="8" t="inlineStr"/>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="H46" s="8" t="inlineStr"/>
+      <c r="I46" s="8" t="inlineStr">
+        <is>
+          <t>Please add</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>L. Astorino</t>
+          <t>W. Barker</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2018–2019</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr"/>
@@ -2308,26 +2308,34 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>W. Barker</t>
+          <t>Phil Beard</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>2018–2019</t>
+          <t>2001–2014</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr"/>
       <c r="E48" s="7" t="n"/>
-      <c r="F48" s="5" t="inlineStr"/>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>50+</t>
+        </is>
+      </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="H48" s="8" t="inlineStr"/>
+          <t>Band only</t>
+        </is>
+      </c>
+      <c r="H48" s="8" t="inlineStr">
+        <is>
+          <t>Tommy Leech, Oct 2026</t>
+        </is>
+      </c>
       <c r="I48" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Only an age band is known – a year would be better</t>
         </is>
       </c>
     </row>
@@ -2339,12 +2347,12 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Phil Beard</t>
+          <t>Andrew Begg</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>2001–2014</t>
+          <t>2013–2015</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr"/>
@@ -2370,26 +2378,34 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Andrew Begg</t>
+          <t>Todd Berglund</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>2013–2015</t>
+          <t>2012–2013</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr"/>
       <c r="E50" s="7" t="n"/>
-      <c r="F50" s="5" t="inlineStr"/>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>50+</t>
+        </is>
+      </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="H50" s="8" t="inlineStr"/>
+          <t>Band only</t>
+        </is>
+      </c>
+      <c r="H50" s="8" t="inlineStr">
+        <is>
+          <t>Tommy Leech, Oct 2026</t>
+        </is>
+      </c>
       <c r="I50" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Only an age band is known – a year would be better</t>
         </is>
       </c>
     </row>
@@ -2401,26 +2417,40 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Todd Berglund</t>
+          <t>Barron Bitar</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>2012–2013</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr"/>
-      <c r="E51" s="7" t="n"/>
-      <c r="F51" s="5" t="inlineStr"/>
+          <t>2024–2025</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="n">
+        <v>2010</v>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>Under 25</t>
+        </is>
+      </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="H51" s="8" t="inlineStr"/>
+          <t>Approximate</t>
+        </is>
+      </c>
+      <c r="H51" s="8" t="inlineStr">
+        <is>
+          <t>Fox Chapel HS class of 2028 (MaxPreps); Tri-State PGA junior boys 11-14 in 2024</t>
+        </is>
+      </c>
       <c r="I51" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
       </c>
     </row>
@@ -2432,42 +2462,38 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>Barron Bitar</t>
+          <t>Scott Bitar II</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>2024–2025</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>2010</t>
+          <t>2017–2025</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>30 May 2001</t>
         </is>
       </c>
       <c r="E52" s="7" t="n">
-        <v>2010</v>
+        <v>2001</v>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>Under 25</t>
+          <t>25–29</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>Approximate</t>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>Fox Chapel HS class of 2028 (MaxPreps); Tri-State PGA junior boys 11-14 in 2024</t>
-        </is>
-      </c>
-      <c r="I52" s="8" t="inlineStr">
-        <is>
-          <t>Year only, worked out from an age or school year – a real date would be better</t>
-        </is>
-      </c>
+          <t>Fox Chapel age roster, Aug 2025</t>
+        </is>
+      </c>
+      <c r="I52" s="8" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
@@ -2477,38 +2503,42 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Scott Bitar II</t>
+          <t>James Braham</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>2017–2025</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>30 May 2001</t>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>1977</t>
         </is>
       </c>
       <c r="E53" s="7" t="n">
-        <v>2001</v>
+        <v>1977</v>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>25–29</t>
+          <t>40–49</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Approximate</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>Fox Chapel age roster, Aug 2025</t>
-        </is>
-      </c>
-      <c r="I53" s="8" t="inlineStr"/>
+          <t>Probably Jimmy Brahm, PGA, former Fox Chapel assistant pro: Slippery Rock graduate who entered the golf business in 2000; identity and year both uncertain</t>
+        </is>
+      </c>
+      <c r="I53" s="8" t="inlineStr">
+        <is>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
@@ -2518,25 +2548,25 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>James Braham</t>
+          <t>Aidan Burchianti</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2022–2024</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="E54" s="7" t="n">
-        <v>1977</v>
+        <v>2004</v>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>40–49</t>
+          <t>Under 25</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
@@ -2546,7 +2576,7 @@
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>Probably Jimmy Brahm, PGA, former Fox Chapel assistant pro: Slippery Rock graduate who entered the golf business in 2000; identity and year both uncertain</t>
+          <t>SMU sophomore in spring 2025</t>
         </is>
       </c>
       <c r="I54" s="8" t="inlineStr">
@@ -2563,40 +2593,40 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Aidan Burchianti</t>
+          <t>Mike Carlin</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>2022–2024</t>
+          <t>2012–2023</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>1981</t>
         </is>
       </c>
       <c r="E55" s="7" t="n">
-        <v>2004</v>
+        <v>1981</v>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>Under 25</t>
-        </is>
-      </c>
-      <c r="G55" s="5" t="inlineStr">
-        <is>
-          <t>Approximate</t>
+          <t>40–49</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>Please confirm</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>SMU sophomore in spring 2025</t>
+          <t>Fox Chapel age roster, Aug 2025 shows 1981-07-06, identical to Eric Hellberg; one of the two is probably a copy error, so both are approximate until Fox Chapel confirms</t>
         </is>
       </c>
       <c r="I55" s="8" t="inlineStr">
         <is>
-          <t>Year only, worked out from an age or school year – a real date would be better</t>
+          <t>The roster gives this player the same full date as another player – please check which is right</t>
         </is>
       </c>
     </row>
@@ -2608,40 +2638,40 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>Mike Carlin</t>
+          <t>TJ Cleveland</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>2012–2023</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>1981</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="E56" s="7" t="n">
-        <v>1981</v>
+        <v>1992</v>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>40–49</t>
-        </is>
-      </c>
-      <c r="G56" s="6" t="inlineStr">
-        <is>
-          <t>Please confirm</t>
+          <t>30–39</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>Approximate</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>Fox Chapel age roster, Aug 2025 shows 1981-07-06, identical to Eric Hellberg; one of the two is probably a copy error, so both are approximate until Fox Chapel confirms</t>
+          <t>Same age as Tommy Leech (Tommy, Oct 2026)</t>
         </is>
       </c>
       <c r="I56" s="8" t="inlineStr">
         <is>
-          <t>The roster gives this player the same full date as another player – please check which is right</t>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
       </c>
     </row>
@@ -2653,26 +2683,40 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>TJ Cleveland</t>
+          <t>Jesse Coslov</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="inlineStr"/>
-      <c r="E57" s="7" t="n"/>
-      <c r="F57" s="5" t="inlineStr"/>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>1985</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="n">
+        <v>1985</v>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>40–49</t>
+        </is>
+      </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="H57" s="8" t="inlineStr"/>
+          <t>Approximate</t>
+        </is>
+      </c>
+      <c r="H57" s="8" t="inlineStr">
+        <is>
+          <t>Shady Side Academy and GWU graduate, first job 2007; uncertain</t>
+        </is>
+      </c>
       <c r="I57" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
       </c>
     </row>
@@ -2684,42 +2728,38 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>Jesse Coslov</t>
+          <t>Brice Delaney</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>1985</t>
+          <t>2016–2025</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>21 Sep 2001</t>
         </is>
       </c>
       <c r="E58" s="7" t="n">
-        <v>1985</v>
+        <v>2001</v>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>40–49</t>
+          <t>25–29</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>Approximate</t>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>Shady Side Academy and GWU graduate, first job 2007; uncertain</t>
-        </is>
-      </c>
-      <c r="I58" s="8" t="inlineStr">
-        <is>
-          <t>Year only, worked out from an age or school year – a real date would be better</t>
-        </is>
-      </c>
+          <t>Fox Chapel age roster, Aug 2025</t>
+        </is>
+      </c>
+      <c r="I58" s="8" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
@@ -2729,25 +2769,25 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Brice Delaney</t>
+          <t>O. Delaney</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>2016–2025</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2001</t>
+          <t>13 Mar 2004</t>
         </is>
       </c>
       <c r="E59" s="7" t="n">
-        <v>2001</v>
+        <v>2004</v>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>25–29</t>
+          <t>Under 25</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
@@ -2770,38 +2810,42 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>O. Delaney</t>
+          <t>Tim Derdenger</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D60" s="5" t="inlineStr">
-        <is>
-          <t>13 Mar 2004</t>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>1980</t>
         </is>
       </c>
       <c r="E60" s="7" t="n">
-        <v>2004</v>
+        <v>1980</v>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>Under 25</t>
+          <t>40–49</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Approximate</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>Fox Chapel age roster, Aug 2025</t>
-        </is>
-      </c>
-      <c r="I60" s="8" t="inlineStr"/>
+          <t>Age 45 in Poets &amp; Quants profile, 2025</t>
+        </is>
+      </c>
+      <c r="I60" s="8" t="inlineStr">
+        <is>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
@@ -2811,40 +2855,26 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Tim Derdenger</t>
+          <t>Rob Ellsworth</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D61" s="6" t="inlineStr">
-        <is>
-          <t>1980</t>
-        </is>
-      </c>
-      <c r="E61" s="7" t="n">
-        <v>1980</v>
-      </c>
-      <c r="F61" s="5" t="inlineStr">
-        <is>
-          <t>40–49</t>
-        </is>
-      </c>
+          <t>2024–2025</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr"/>
+      <c r="E61" s="7" t="n"/>
+      <c r="F61" s="5" t="inlineStr"/>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Approximate</t>
-        </is>
-      </c>
-      <c r="H61" s="8" t="inlineStr">
-        <is>
-          <t>Age 45 in Poets &amp; Quants profile, 2025</t>
-        </is>
-      </c>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="H61" s="8" t="inlineStr"/>
       <c r="I61" s="8" t="inlineStr">
         <is>
-          <t>Year only, worked out from an age or school year – a real date would be better</t>
+          <t>Please add</t>
         </is>
       </c>
     </row>
@@ -2856,26 +2886,34 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>Rob Ellsworth</t>
+          <t>Mike Foster</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>2024–2025</t>
+          <t>2000–2023</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr"/>
       <c r="E62" s="7" t="n"/>
-      <c r="F62" s="5" t="inlineStr"/>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>50+</t>
+        </is>
+      </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="H62" s="8" t="inlineStr"/>
+          <t>Band only</t>
+        </is>
+      </c>
+      <c r="H62" s="8" t="inlineStr">
+        <is>
+          <t>Tommy Leech, Oct 2026</t>
+        </is>
+      </c>
       <c r="I62" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Only an age band is known – a year would be better</t>
         </is>
       </c>
     </row>
@@ -2887,28 +2925,38 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Mike Foster</t>
+          <t>Ben Fownes</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>2000–2023</t>
-        </is>
-      </c>
-      <c r="D63" s="6" t="inlineStr"/>
-      <c r="E63" s="7" t="n"/>
-      <c r="F63" s="5" t="inlineStr"/>
+          <t>2018–2022</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>4 Nov 1992</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="n">
+        <v>1992</v>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>30–39</t>
+        </is>
+      </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="H63" s="8" t="inlineStr"/>
-      <c r="I63" s="8" t="inlineStr">
-        <is>
-          <t>Please add</t>
-        </is>
-      </c>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H63" s="8" t="inlineStr">
+        <is>
+          <t>Fox Chapel age roster, Aug 2025</t>
+        </is>
+      </c>
+      <c r="I63" s="8" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
@@ -2918,38 +2966,42 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>Ben Fownes</t>
+          <t>Rob Franklin</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>2018–2022</t>
-        </is>
-      </c>
-      <c r="D64" s="5" t="inlineStr">
-        <is>
-          <t>4 Nov 1992</t>
+          <t>2013–2024</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>1974</t>
         </is>
       </c>
       <c r="E64" s="7" t="n">
-        <v>1992</v>
+        <v>1974</v>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>30–39</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Approximate</t>
         </is>
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>Fox Chapel age roster, Aug 2025</t>
-        </is>
-      </c>
-      <c r="I64" s="8" t="inlineStr"/>
+          <t>Fox Chapel age roster: 49 in Oct 2023</t>
+        </is>
+      </c>
+      <c r="I64" s="8" t="inlineStr">
+        <is>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
@@ -2959,42 +3011,38 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>Rob Franklin</t>
+          <t>David Fuhrer II</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>2013–2024</t>
-        </is>
-      </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t>1974</t>
+          <t>2021–2025</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>1 Mar 2006</t>
         </is>
       </c>
       <c r="E65" s="7" t="n">
-        <v>1974</v>
+        <v>2006</v>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Under 25</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>Approximate</t>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>Fox Chapel age roster: 49 in Oct 2023</t>
-        </is>
-      </c>
-      <c r="I65" s="8" t="inlineStr">
-        <is>
-          <t>Year only, worked out from an age or school year – a real date would be better</t>
-        </is>
-      </c>
+          <t>Fox Chapel age roster, Aug 2025</t>
+        </is>
+      </c>
+      <c r="I65" s="8" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
@@ -3004,25 +3052,25 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>David Fuhrer II</t>
+          <t>Todd Green</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>2021–2025</t>
+          <t>2020–2024</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>1 Mar 2006</t>
+          <t>31 Oct 1989</t>
         </is>
       </c>
       <c r="E66" s="7" t="n">
-        <v>2006</v>
+        <v>1989</v>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>Under 25</t>
+          <t>30–39</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
@@ -3045,38 +3093,42 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>Todd Green</t>
+          <t>Clint Guyaux</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>2020–2024</t>
-        </is>
-      </c>
-      <c r="D67" s="5" t="inlineStr">
-        <is>
-          <t>31 Oct 1989</t>
+          <t>2017–2022</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>1972</t>
         </is>
       </c>
       <c r="E67" s="7" t="n">
-        <v>1989</v>
+        <v>1972</v>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>30–39</t>
-        </is>
-      </c>
-      <c r="G67" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>Please confirm</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>Fox Chapel age roster, Aug 2025</t>
-        </is>
-      </c>
-      <c r="I67" s="8" t="inlineStr"/>
+          <t>Fox Chapel age roster, Aug 2025 shows 1972-12-15, identical to Tom Delaney (Oakmont) and probably pasted; year kept as approximate until Fox Chapel confirms</t>
+        </is>
+      </c>
+      <c r="I67" s="8" t="inlineStr">
+        <is>
+          <t>The roster gives this player the same full date as another player – please check which is right</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
@@ -3086,40 +3138,40 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>Clint Guyaux</t>
+          <t>Jon Halpern</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>2017–2022</t>
+          <t>2022–2024</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>1972</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="E68" s="7" t="n">
-        <v>1972</v>
+        <v>1991</v>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>50+</t>
-        </is>
-      </c>
-      <c r="G68" s="6" t="inlineStr">
-        <is>
-          <t>Please confirm</t>
+          <t>30–39</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>Approximate</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>Fox Chapel age roster, Aug 2025 shows 1972-12-15, identical to Tom Delaney (Oakmont) and probably pasted; year kept as approximate until Fox Chapel confirms</t>
+          <t>A year older than Tommy Leech (Tommy, Oct 2026)</t>
         </is>
       </c>
       <c r="I68" s="8" t="inlineStr">
         <is>
-          <t>The roster gives this player the same full date as another player – please check which is right</t>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
       </c>
     </row>
@@ -3131,26 +3183,40 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>Jon Halpern</t>
+          <t>Eric Hellberg</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>2022–2024</t>
-        </is>
-      </c>
-      <c r="D69" s="6" t="inlineStr"/>
-      <c r="E69" s="7" t="n"/>
-      <c r="F69" s="5" t="inlineStr"/>
-      <c r="G69" s="5" t="inlineStr">
-        <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="H69" s="8" t="inlineStr"/>
+          <t>2007–2023</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>1981</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="n">
+        <v>1981</v>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>40–49</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>Please confirm</t>
+        </is>
+      </c>
+      <c r="H69" s="8" t="inlineStr">
+        <is>
+          <t>Fox Chapel age roster, Aug 2025 shows 1981-07-06, identical to Michael Carlin; one of the two is probably a copy error, so both are approximate until Fox Chapel confirms</t>
+        </is>
+      </c>
       <c r="I69" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>The roster gives this player the same full date as another player – please check which is right</t>
         </is>
       </c>
     </row>
@@ -3162,42 +3228,38 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>Eric Hellberg</t>
+          <t>Scott Hellberg</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>2007–2023</t>
-        </is>
-      </c>
-      <c r="D70" s="6" t="inlineStr">
-        <is>
-          <t>1981</t>
+          <t>2017–2025</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>1 Oct 1988</t>
         </is>
       </c>
       <c r="E70" s="7" t="n">
-        <v>1981</v>
+        <v>1988</v>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>40–49</t>
-        </is>
-      </c>
-      <c r="G70" s="6" t="inlineStr">
-        <is>
-          <t>Please confirm</t>
+          <t>30–39</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="H70" s="8" t="inlineStr">
         <is>
-          <t>Fox Chapel age roster, Aug 2025 shows 1981-07-06, identical to Michael Carlin; one of the two is probably a copy error, so both are approximate until Fox Chapel confirms</t>
-        </is>
-      </c>
-      <c r="I70" s="8" t="inlineStr">
-        <is>
-          <t>The roster gives this player the same full date as another player – please check which is right</t>
-        </is>
-      </c>
+          <t>Fox Chapel age roster, Aug 2025</t>
+        </is>
+      </c>
+      <c r="I70" s="8" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
@@ -3207,21 +3269,21 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>Scott Hellberg</t>
+          <t>Adam Hofmann</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>2017–2025</t>
+          <t>2008–2025</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>1 Oct 1988</t>
+          <t>1 May 1989</t>
         </is>
       </c>
       <c r="E71" s="7" t="n">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
@@ -3248,25 +3310,25 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>Adam Hofmann</t>
+          <t>Dave Kassling</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>2008–2025</t>
+          <t>2008–2022</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>1 May 1989</t>
+          <t>10 Aug 1983</t>
         </is>
       </c>
       <c r="E72" s="7" t="n">
-        <v>1989</v>
+        <v>1983</v>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>30–39</t>
+          <t>40–49</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
@@ -3289,38 +3351,28 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>Dave Kassling</t>
+          <t>T. Kelly</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>2008–2022</t>
-        </is>
-      </c>
-      <c r="D73" s="5" t="inlineStr">
-        <is>
-          <t>10 Aug 1983</t>
-        </is>
-      </c>
-      <c r="E73" s="7" t="n">
-        <v>1983</v>
-      </c>
-      <c r="F73" s="5" t="inlineStr">
-        <is>
-          <t>40–49</t>
-        </is>
-      </c>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr"/>
+      <c r="E73" s="7" t="n"/>
+      <c r="F73" s="5" t="inlineStr"/>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="H73" s="8" t="inlineStr">
-        <is>
-          <t>Fox Chapel age roster, Aug 2025</t>
-        </is>
-      </c>
-      <c r="I73" s="8" t="inlineStr"/>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="H73" s="8" t="inlineStr"/>
+      <c r="I73" s="8" t="inlineStr">
+        <is>
+          <t>Please add</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
@@ -3330,26 +3382,40 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>T. Kelly</t>
+          <t>Adam Lauer</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="D74" s="6" t="inlineStr"/>
-      <c r="E74" s="7" t="n"/>
-      <c r="F74" s="5" t="inlineStr"/>
+          <t>2018–2023</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="n">
+        <v>2003</v>
+      </c>
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>Under 25</t>
+        </is>
+      </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="H74" s="8" t="inlineStr"/>
+          <t>Approximate</t>
+        </is>
+      </c>
+      <c r="H74" s="8" t="inlineStr">
+        <is>
+          <t>Shady Side Academy junior in fall 2019; WPIAL 3A runner-up 2020</t>
+        </is>
+      </c>
       <c r="I74" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
       </c>
     </row>
@@ -3361,42 +3427,38 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>Adam Lauer</t>
+          <t>Dave Lucas Jr.</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>2018–2023</t>
-        </is>
-      </c>
-      <c r="D75" s="6" t="inlineStr">
-        <is>
-          <t>2003</t>
+          <t>2000–2018</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>4 Apr 1960</t>
         </is>
       </c>
       <c r="E75" s="7" t="n">
-        <v>2003</v>
+        <v>1960</v>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>Under 25</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>Approximate</t>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="H75" s="8" t="inlineStr">
         <is>
-          <t>Shady Side Academy junior in fall 2019; WPIAL 3A runner-up 2020</t>
-        </is>
-      </c>
-      <c r="I75" s="8" t="inlineStr">
-        <is>
-          <t>Year only, worked out from an age or school year – a real date would be better</t>
-        </is>
-      </c>
+          <t>Fox Chapel age roster, Aug 2025</t>
+        </is>
+      </c>
+      <c r="I75" s="8" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
@@ -3406,21 +3468,21 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>Dave Lucas Jr.</t>
+          <t>John Mah</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>2000–2018</t>
+          <t>2014–2023</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>4 Apr 1960</t>
+          <t>20 Mar 1973</t>
         </is>
       </c>
       <c r="E76" s="7" t="n">
-        <v>1960</v>
+        <v>1973</v>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
@@ -3447,21 +3509,21 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>John Mah</t>
+          <t>Randy McCombs</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>2014–2023</t>
+          <t>2003–2019</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>20 Mar 1973</t>
+          <t>16 Jun 1962</t>
         </is>
       </c>
       <c r="E77" s="7" t="n">
-        <v>1973</v>
+        <v>1962</v>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
@@ -3488,38 +3550,28 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>Randy McCombs</t>
+          <t>Henry McCrady</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>2003–2019</t>
-        </is>
-      </c>
-      <c r="D78" s="5" t="inlineStr">
-        <is>
-          <t>16 Jun 1962</t>
-        </is>
-      </c>
-      <c r="E78" s="7" t="n">
-        <v>1962</v>
-      </c>
-      <c r="F78" s="5" t="inlineStr">
-        <is>
-          <t>50+</t>
-        </is>
-      </c>
+          <t>2023–2025</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr"/>
+      <c r="E78" s="7" t="n"/>
+      <c r="F78" s="5" t="inlineStr"/>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="H78" s="8" t="inlineStr">
-        <is>
-          <t>Fox Chapel age roster, Aug 2025</t>
-        </is>
-      </c>
-      <c r="I78" s="8" t="inlineStr"/>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="H78" s="8" t="inlineStr"/>
+      <c r="I78" s="8" t="inlineStr">
+        <is>
+          <t>Please add</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
@@ -3529,26 +3581,34 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>Henry McCrady</t>
+          <t>Dave Mengel</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>2023–2025</t>
+          <t>2001–2016</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr"/>
       <c r="E79" s="7" t="n"/>
-      <c r="F79" s="5" t="inlineStr"/>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>50+</t>
+        </is>
+      </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="H79" s="8" t="inlineStr"/>
+          <t>Band only</t>
+        </is>
+      </c>
+      <c r="H79" s="8" t="inlineStr">
+        <is>
+          <t>Tommy Leech, Oct 2026</t>
+        </is>
+      </c>
       <c r="I79" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Only an age band is known – a year would be better</t>
         </is>
       </c>
     </row>
@@ -3560,26 +3620,40 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>Dave Mengel</t>
+          <t>Jeremy Merich</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>2001–2016</t>
-        </is>
-      </c>
-      <c r="D80" s="6" t="inlineStr"/>
-      <c r="E80" s="7" t="n"/>
-      <c r="F80" s="5" t="inlineStr"/>
+          <t>2020–2023</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="n">
+        <v>1994</v>
+      </c>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>30–39</t>
+        </is>
+      </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="H80" s="8" t="inlineStr"/>
+          <t>Approximate</t>
+        </is>
+      </c>
+      <c r="H80" s="8" t="inlineStr">
+        <is>
+          <t>Peters Township class of 2012; Saint Francis golf 2012-16</t>
+        </is>
+      </c>
       <c r="I80" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
       </c>
     </row>
@@ -3591,40 +3665,26 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>Jeremy Merich</t>
+          <t>Sam Miclot</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>2020–2023</t>
-        </is>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
-        <is>
-          <t>1994</t>
-        </is>
-      </c>
-      <c r="E81" s="7" t="n">
-        <v>1994</v>
-      </c>
-      <c r="F81" s="5" t="inlineStr">
-        <is>
-          <t>30–39</t>
-        </is>
-      </c>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr"/>
+      <c r="E81" s="7" t="n"/>
+      <c r="F81" s="5" t="inlineStr"/>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Approximate</t>
-        </is>
-      </c>
-      <c r="H81" s="8" t="inlineStr">
-        <is>
-          <t>Peters Township class of 2012; Saint Francis golf 2012-16</t>
-        </is>
-      </c>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="H81" s="8" t="inlineStr"/>
       <c r="I81" s="8" t="inlineStr">
         <is>
-          <t>Year only, worked out from an age or school year – a real date would be better</t>
+          <t>Please add</t>
         </is>
       </c>
     </row>
@@ -3636,28 +3696,38 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>Sam Miclot</t>
+          <t>Greg Podufal</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D82" s="6" t="inlineStr"/>
-      <c r="E82" s="7" t="n"/>
-      <c r="F82" s="5" t="inlineStr"/>
+          <t>2016–2021</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>26 Jun 1992</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="n">
+        <v>1992</v>
+      </c>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>30–39</t>
+        </is>
+      </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="H82" s="8" t="inlineStr"/>
-      <c r="I82" s="8" t="inlineStr">
-        <is>
-          <t>Please add</t>
-        </is>
-      </c>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H82" s="8" t="inlineStr">
+        <is>
+          <t>Georgetown men's golf roster</t>
+        </is>
+      </c>
+      <c r="I82" s="8" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
@@ -3667,38 +3737,42 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>Greg Podufal</t>
+          <t>Tom Reading</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>2016–2021</t>
-        </is>
-      </c>
-      <c r="D83" s="5" t="inlineStr">
-        <is>
-          <t>26 Jun 1992</t>
+          <t>2008–2014</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>1963</t>
         </is>
       </c>
       <c r="E83" s="7" t="n">
-        <v>1992</v>
+        <v>1963</v>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>30–39</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Approximate</t>
         </is>
       </c>
       <c r="H83" s="8" t="inlineStr">
         <is>
-          <t>Georgetown men's golf roster</t>
-        </is>
-      </c>
-      <c r="I83" s="8" t="inlineStr"/>
+          <t>Fox Chapel age roster: 60 in Oct 2023</t>
+        </is>
+      </c>
+      <c r="I83" s="8" t="inlineStr">
+        <is>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
@@ -3708,40 +3782,26 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>Tom Reading</t>
+          <t>C. Rudolf</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>2008–2014</t>
-        </is>
-      </c>
-      <c r="D84" s="6" t="inlineStr">
-        <is>
-          <t>1963</t>
-        </is>
-      </c>
-      <c r="E84" s="7" t="n">
-        <v>1963</v>
-      </c>
-      <c r="F84" s="5" t="inlineStr">
-        <is>
-          <t>50+</t>
-        </is>
-      </c>
+          <t>2017–2021</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr"/>
+      <c r="E84" s="7" t="n"/>
+      <c r="F84" s="5" t="inlineStr"/>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>Approximate</t>
-        </is>
-      </c>
-      <c r="H84" s="8" t="inlineStr">
-        <is>
-          <t>Fox Chapel age roster: 60 in Oct 2023</t>
-        </is>
-      </c>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="H84" s="8" t="inlineStr"/>
       <c r="I84" s="8" t="inlineStr">
         <is>
-          <t>Year only, worked out from an age or school year – a real date would be better</t>
+          <t>Please add</t>
         </is>
       </c>
     </row>
@@ -3753,12 +3813,12 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>C. Rudolf</t>
+          <t>R. Russell</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>2017–2021</t>
+          <t>2016–2020</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr"/>
@@ -3784,26 +3844,40 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>R. Russell</t>
+          <t>Gus Schroeder</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>2016–2020</t>
-        </is>
-      </c>
-      <c r="D86" s="6" t="inlineStr"/>
-      <c r="E86" s="7" t="n"/>
-      <c r="F86" s="5" t="inlineStr"/>
+          <t>2007–2021</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>1970</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="n">
+        <v>1970</v>
+      </c>
+      <c r="F86" s="5" t="inlineStr">
+        <is>
+          <t>50+</t>
+        </is>
+      </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="H86" s="8" t="inlineStr"/>
+          <t>Approximate</t>
+        </is>
+      </c>
+      <c r="H86" s="8" t="inlineStr">
+        <is>
+          <t>Gus Schroeder Jr., Schroeder Industries president since 2005; rough estimate, father (also Gus, b. c. 1940) died c. 2000</t>
+        </is>
+      </c>
       <c r="I86" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
       </c>
     </row>
@@ -3815,25 +3889,25 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>Gus Schroeder</t>
+          <t>Ben Smith</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>2007–2021</t>
+          <t>2000–2013</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>1970</t>
+          <t>1981</t>
         </is>
       </c>
       <c r="E87" s="7" t="n">
-        <v>1970</v>
+        <v>1981</v>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>40–49</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
@@ -3843,7 +3917,7 @@
       </c>
       <c r="H87" s="8" t="inlineStr">
         <is>
-          <t>Gus Schroeder Jr., Schroeder Industries president since 2005; rough estimate, father (also Gus, b. c. 1940) died c. 2000</t>
+          <t>About 45 in Oct 2026 (Tommy Leech)</t>
         </is>
       </c>
       <c r="I87" s="8" t="inlineStr">
@@ -3860,28 +3934,38 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>Ben Smith</t>
+          <t>Bennett Smith</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>2000–2013</t>
-        </is>
-      </c>
-      <c r="D88" s="6" t="inlineStr"/>
-      <c r="E88" s="7" t="n"/>
-      <c r="F88" s="5" t="inlineStr"/>
+          <t>2003–2025</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>20 Apr 1984</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="n">
+        <v>1984</v>
+      </c>
+      <c r="F88" s="5" t="inlineStr">
+        <is>
+          <t>40–49</t>
+        </is>
+      </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="H88" s="8" t="inlineStr"/>
-      <c r="I88" s="8" t="inlineStr">
-        <is>
-          <t>Please add</t>
-        </is>
-      </c>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H88" s="8" t="inlineStr">
+        <is>
+          <t>Fox Chapel age roster, Aug 2025</t>
+        </is>
+      </c>
+      <c r="I88" s="8" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
@@ -3891,38 +3975,28 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>Bennett Smith</t>
+          <t>D. Smith</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>2003–2025</t>
-        </is>
-      </c>
-      <c r="D89" s="5" t="inlineStr">
-        <is>
-          <t>20 Apr 1984</t>
-        </is>
-      </c>
-      <c r="E89" s="7" t="n">
-        <v>1984</v>
-      </c>
-      <c r="F89" s="5" t="inlineStr">
-        <is>
-          <t>40–49</t>
-        </is>
-      </c>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr"/>
+      <c r="E89" s="7" t="n"/>
+      <c r="F89" s="5" t="inlineStr"/>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="H89" s="8" t="inlineStr">
-        <is>
-          <t>Fox Chapel age roster, Aug 2025</t>
-        </is>
-      </c>
-      <c r="I89" s="8" t="inlineStr"/>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="H89" s="8" t="inlineStr"/>
+      <c r="I89" s="8" t="inlineStr">
+        <is>
+          <t>Please add</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
@@ -3932,28 +4006,38 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>D. Smith</t>
+          <t>Vance Smith IV</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="D90" s="6" t="inlineStr"/>
-      <c r="E90" s="7" t="n"/>
-      <c r="F90" s="5" t="inlineStr"/>
+          <t>2000–2024</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>29 Dec 1979</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="n">
+        <v>1979</v>
+      </c>
+      <c r="F90" s="5" t="inlineStr">
+        <is>
+          <t>40–49</t>
+        </is>
+      </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="H90" s="8" t="inlineStr"/>
-      <c r="I90" s="8" t="inlineStr">
-        <is>
-          <t>Please add</t>
-        </is>
-      </c>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H90" s="8" t="inlineStr">
+        <is>
+          <t>Fox Chapel age roster, Aug 2025</t>
+        </is>
+      </c>
+      <c r="I90" s="8" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
@@ -3963,38 +4047,42 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>Vance Smith IV</t>
+          <t>Hunter Stanchak</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>2000–2024</t>
-        </is>
-      </c>
-      <c r="D91" s="5" t="inlineStr">
-        <is>
-          <t>29 Dec 1979</t>
+          <t>2022–2025</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>1994</t>
         </is>
       </c>
       <c r="E91" s="7" t="n">
-        <v>1979</v>
+        <v>1994</v>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>40–49</t>
+          <t>30–39</t>
         </is>
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Approximate</t>
         </is>
       </c>
       <c r="H91" s="8" t="inlineStr">
         <is>
-          <t>Fox Chapel age roster, Aug 2025</t>
-        </is>
-      </c>
-      <c r="I91" s="8" t="inlineStr"/>
+          <t>Peters Township HS golf 2010 alongside Tommy Nettles; uncertain, same name only</t>
+        </is>
+      </c>
+      <c r="I91" s="8" t="inlineStr">
+        <is>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
@@ -4004,25 +4092,25 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>Hunter Stanchak</t>
+          <t>Don Thomas</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>2022–2025</t>
+          <t>2024–2025</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>1994</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="E92" s="7" t="n">
-        <v>1994</v>
+        <v>1986</v>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>30–39</t>
+          <t>40–49</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr">
@@ -4032,7 +4120,7 @@
       </c>
       <c r="H92" s="8" t="inlineStr">
         <is>
-          <t>Peters Township HS golf 2010 alongside Tommy Nettles; uncertain, same name only</t>
+          <t>About 40 in Oct 2026 (Tommy Leech)</t>
         </is>
       </c>
       <c r="I92" s="8" t="inlineStr">
@@ -4049,12 +4137,12 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>Don Thomas</t>
+          <t>Jim Usher</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>2024–2025</t>
+          <t>2010–2015</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr"/>
@@ -4080,12 +4168,12 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>Jim Usher</t>
+          <t>JP Walsh</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>2010–2015</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr"/>
@@ -4111,12 +4199,12 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>JP Walsh</t>
+          <t>Patrick Walsh</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2018–2019</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr"/>
@@ -4142,12 +4230,12 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>Patrick Walsh</t>
+          <t>Ben Washburn</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>2018–2019</t>
+          <t>2023–2024</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr"/>
@@ -4173,56 +4261,66 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>Ben Washburn</t>
+          <t>Henry Watson</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>2023–2024</t>
-        </is>
-      </c>
-      <c r="D97" s="6" t="inlineStr"/>
-      <c r="E97" s="7" t="n"/>
-      <c r="F97" s="5" t="inlineStr"/>
+          <t>2000–2017</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>1 Jan 1984</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="n">
+        <v>1984</v>
+      </c>
+      <c r="F97" s="5" t="inlineStr">
+        <is>
+          <t>40–49</t>
+        </is>
+      </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="H97" s="8" t="inlineStr"/>
-      <c r="I97" s="8" t="inlineStr">
-        <is>
-          <t>Please add</t>
-        </is>
-      </c>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H97" s="8" t="inlineStr">
+        <is>
+          <t>Fox Chapel age roster, Aug 2025</t>
+        </is>
+      </c>
+      <c r="I97" s="8" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>Fox Chapel</t>
+          <t>Oakmont</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>Henry Watson</t>
+          <t>Amby Bauer</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>2000–2017</t>
+          <t>2012–2014</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>1 Jan 1984</t>
+          <t>21 Sep 1974</t>
         </is>
       </c>
       <c r="E98" s="7" t="n">
-        <v>1984</v>
+        <v>1974</v>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>40–49</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
@@ -4232,7 +4330,7 @@
       </c>
       <c r="H98" s="8" t="inlineStr">
         <is>
-          <t>Fox Chapel age roster, Aug 2025</t>
+          <t>Oakmont age roster, Aug 2025</t>
         </is>
       </c>
       <c r="I98" s="8" t="inlineStr"/>
@@ -4245,21 +4343,21 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>Amby Bauer</t>
+          <t>Rich Berglund</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>2012–2014</t>
+          <t>2001–2024</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 1974</t>
+          <t>16 Feb 1965</t>
         </is>
       </c>
       <c r="E99" s="7" t="n">
-        <v>1974</v>
+        <v>1965</v>
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
@@ -4286,38 +4384,42 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>Rich Berglund</t>
+          <t>Todd Berglund</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>2001–2024</t>
-        </is>
-      </c>
-      <c r="D100" s="5" t="inlineStr">
-        <is>
-          <t>16 Feb 1965</t>
+          <t>2024–2025</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>1991</t>
         </is>
       </c>
       <c r="E100" s="7" t="n">
-        <v>1965</v>
+        <v>1991</v>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>30–39</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Approximate</t>
         </is>
       </c>
       <c r="H100" s="8" t="inlineStr">
         <is>
-          <t>Oakmont age roster, Aug 2025</t>
-        </is>
-      </c>
-      <c r="I100" s="8" t="inlineStr"/>
+          <t>A year older than Tommy Leech (Tommy, Oct 2026)</t>
+        </is>
+      </c>
+      <c r="I100" s="8" t="inlineStr">
+        <is>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
@@ -4327,28 +4429,38 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>Todd Berglund</t>
+          <t>Brett Bergman</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>2024–2025</t>
-        </is>
-      </c>
-      <c r="D101" s="6" t="inlineStr"/>
-      <c r="E101" s="7" t="n"/>
-      <c r="F101" s="5" t="inlineStr"/>
+          <t>2007–2023</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>16 Jun 1986</t>
+        </is>
+      </c>
+      <c r="E101" s="7" t="n">
+        <v>1986</v>
+      </c>
+      <c r="F101" s="5" t="inlineStr">
+        <is>
+          <t>40–49</t>
+        </is>
+      </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="H101" s="8" t="inlineStr"/>
-      <c r="I101" s="8" t="inlineStr">
-        <is>
-          <t>Please add</t>
-        </is>
-      </c>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H101" s="8" t="inlineStr">
+        <is>
+          <t>Oakmont age roster, Aug 2025</t>
+        </is>
+      </c>
+      <c r="I101" s="8" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
@@ -4358,21 +4470,21 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>Brett Bergman</t>
+          <t>Brock Bergman</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>2007–2023</t>
+          <t>2007–2014</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>16 Jun 1986</t>
+          <t>26 May 1984</t>
         </is>
       </c>
       <c r="E102" s="7" t="n">
-        <v>1986</v>
+        <v>1984</v>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
@@ -4399,25 +4511,25 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>Brock Bergman</t>
+          <t>John Birmingham Jr.</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>2007–2014</t>
+          <t>2000–2017</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>26 May 1984</t>
+          <t>30 Jan 1967</t>
         </is>
       </c>
       <c r="E103" s="7" t="n">
-        <v>1984</v>
+        <v>1967</v>
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
-          <t>40–49</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
@@ -4440,21 +4552,21 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>John Birmingham Jr.</t>
+          <t>Mark Bope</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>2000–2017</t>
+          <t>2000–2013</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>30 Jan 1967</t>
+          <t>29 Mar 1954</t>
         </is>
       </c>
       <c r="E104" s="7" t="n">
-        <v>1967</v>
+        <v>1954</v>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
@@ -4481,21 +4593,21 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>Mark Bope</t>
+          <t>Jim Bulger</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>2000–2013</t>
+          <t>2014–2017</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>29 Mar 1954</t>
+          <t>25 Sep 1974</t>
         </is>
       </c>
       <c r="E105" s="7" t="n">
-        <v>1954</v>
+        <v>1974</v>
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
@@ -4522,25 +4634,25 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>Jim Bulger</t>
+          <t>Luke Bumgardner</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>2014–2017</t>
+          <t>2021–2023</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>25 Sep 1974</t>
+          <t>1 Dec 1987</t>
         </is>
       </c>
       <c r="E106" s="7" t="n">
-        <v>1974</v>
+        <v>1987</v>
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>30–39</t>
         </is>
       </c>
       <c r="G106" s="5" t="inlineStr">
@@ -4563,25 +4675,25 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>Luke Bumgardner</t>
+          <t>B. Burke</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>2021–2023</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>1 Dec 1987</t>
+          <t>23 Mar 1972</t>
         </is>
       </c>
       <c r="E107" s="7" t="n">
-        <v>1987</v>
+        <v>1972</v>
       </c>
       <c r="F107" s="5" t="inlineStr">
         <is>
-          <t>30–39</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
@@ -4604,25 +4716,25 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>B. Burke</t>
+          <t>Ryan Cameron</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2023–2024</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>23 Mar 1972</t>
+          <t>18 Jan 1987</t>
         </is>
       </c>
       <c r="E108" s="7" t="n">
-        <v>1972</v>
+        <v>1987</v>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>30–39</t>
         </is>
       </c>
       <c r="G108" s="5" t="inlineStr">
@@ -4645,25 +4757,25 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>Ryan Cameron</t>
+          <t>Curt Coulter</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>2023–2024</t>
+          <t>2000–2019</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>18 Jan 1987</t>
+          <t>21 Sep 1965</t>
         </is>
       </c>
       <c r="E109" s="7" t="n">
-        <v>1987</v>
+        <v>1965</v>
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
-          <t>30–39</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G109" s="5" t="inlineStr">
@@ -4686,21 +4798,21 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>Curt Coulter</t>
+          <t>Tom Delaney</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>2000–2019</t>
+          <t>2008–2016</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 1965</t>
+          <t>15 Dec 1972</t>
         </is>
       </c>
       <c r="E110" s="7" t="n">
-        <v>1965</v>
+        <v>1972</v>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
@@ -4714,7 +4826,7 @@
       </c>
       <c r="H110" s="8" t="inlineStr">
         <is>
-          <t>Oakmont age roster, Aug 2025</t>
+          <t>Oakmont age roster, Aug 2025; the roster's own age column (50 in Oct 2023) agrees. Clint Guyaux (Fox Chapel) carries the same date, probably pasted from this row</t>
         </is>
       </c>
       <c r="I110" s="8" t="inlineStr"/>
@@ -4727,25 +4839,25 @@
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>Tom Delaney</t>
+          <t>Robbie Denove</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>2008–2016</t>
+          <t>2017–2025</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>15 Dec 1972</t>
+          <t>23 Apr 1992</t>
         </is>
       </c>
       <c r="E111" s="7" t="n">
-        <v>1972</v>
+        <v>1992</v>
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>30–39</t>
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr">
@@ -4755,7 +4867,7 @@
       </c>
       <c r="H111" s="8" t="inlineStr">
         <is>
-          <t>Oakmont age roster, Aug 2025; the roster's own age column (50 in Oct 2023) agrees. Clint Guyaux (Fox Chapel) carries the same date, probably pasted from this row</t>
+          <t>Oakmont age roster, Aug 2025</t>
         </is>
       </c>
       <c r="I111" s="8" t="inlineStr"/>
@@ -4768,25 +4880,25 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>Robbie Denove</t>
+          <t>D. Donahue</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>2017–2025</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>23 Apr 1992</t>
+          <t>1 May 1979</t>
         </is>
       </c>
       <c r="E112" s="7" t="n">
-        <v>1992</v>
+        <v>1979</v>
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>30–39</t>
+          <t>40–49</t>
         </is>
       </c>
       <c r="G112" s="5" t="inlineStr">
@@ -4809,25 +4921,25 @@
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>D. Donahue</t>
+          <t>Ned Foster</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2000–2016</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>1 May 1979</t>
+          <t>23 Aug 1966</t>
         </is>
       </c>
       <c r="E113" s="7" t="n">
-        <v>1979</v>
+        <v>1966</v>
       </c>
       <c r="F113" s="5" t="inlineStr">
         <is>
-          <t>40–49</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G113" s="5" t="inlineStr">
@@ -4850,38 +4962,28 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>Ned Foster</t>
+          <t>Fricke</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>2000–2016</t>
-        </is>
-      </c>
-      <c r="D114" s="5" t="inlineStr">
-        <is>
-          <t>23 Aug 1966</t>
-        </is>
-      </c>
-      <c r="E114" s="7" t="n">
-        <v>1966</v>
-      </c>
-      <c r="F114" s="5" t="inlineStr">
-        <is>
-          <t>50+</t>
-        </is>
-      </c>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D114" s="6" t="inlineStr"/>
+      <c r="E114" s="7" t="n"/>
+      <c r="F114" s="5" t="inlineStr"/>
       <c r="G114" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="H114" s="8" t="inlineStr">
-        <is>
-          <t>Oakmont age roster, Aug 2025</t>
-        </is>
-      </c>
-      <c r="I114" s="8" t="inlineStr"/>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="H114" s="8" t="inlineStr"/>
+      <c r="I114" s="8" t="inlineStr">
+        <is>
+          <t>Please add</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
@@ -4891,28 +4993,38 @@
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>Fricke</t>
+          <t>Andrew Friend</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D115" s="6" t="inlineStr"/>
-      <c r="E115" s="7" t="n"/>
-      <c r="F115" s="5" t="inlineStr"/>
+          <t>2017–2025</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="inlineStr">
+        <is>
+          <t>12 Nov 1999</t>
+        </is>
+      </c>
+      <c r="E115" s="7" t="n">
+        <v>1999</v>
+      </c>
+      <c r="F115" s="5" t="inlineStr">
+        <is>
+          <t>25–29</t>
+        </is>
+      </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="H115" s="8" t="inlineStr"/>
-      <c r="I115" s="8" t="inlineStr">
-        <is>
-          <t>Please add</t>
-        </is>
-      </c>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="H115" s="8" t="inlineStr">
+        <is>
+          <t>Oakmont age roster, Aug 2025</t>
+        </is>
+      </c>
+      <c r="I115" s="8" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
@@ -4922,25 +5034,25 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>Andrew Friend</t>
+          <t>Steve Fuhrer</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>2017–2025</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>12 Nov 1999</t>
+          <t>10 Sep 1963</t>
         </is>
       </c>
       <c r="E116" s="7" t="n">
-        <v>1999</v>
+        <v>1963</v>
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>25–29</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G116" s="5" t="inlineStr">
@@ -4963,38 +5075,42 @@
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>Steve Fuhrer</t>
+          <t>Keenan Hickton</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="D117" s="5" t="inlineStr">
-        <is>
-          <t>10 Sep 1963</t>
+          <t>2013–2015</t>
+        </is>
+      </c>
+      <c r="D117" s="6" t="inlineStr">
+        <is>
+          <t>1995</t>
         </is>
       </c>
       <c r="E117" s="7" t="n">
-        <v>1963</v>
+        <v>1995</v>
       </c>
       <c r="F117" s="5" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>30–39</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Approximate</t>
         </is>
       </c>
       <c r="H117" s="8" t="inlineStr">
         <is>
-          <t>Oakmont age roster, Aug 2025</t>
-        </is>
-      </c>
-      <c r="I117" s="8" t="inlineStr"/>
+          <t>Oakmont age roster: 28 in Oct 2023; Emory golf 2014-18 agrees</t>
+        </is>
+      </c>
+      <c r="I117" s="8" t="inlineStr">
+        <is>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
@@ -5004,21 +5120,21 @@
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>Keenan Hickton</t>
+          <t>A. Hofmann</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>2013–2015</t>
-        </is>
-      </c>
-      <c r="D118" s="6" t="inlineStr">
-        <is>
-          <t>1995</t>
+          <t>2007–2022</t>
+        </is>
+      </c>
+      <c r="D118" s="5" t="inlineStr">
+        <is>
+          <t>8 May 1989</t>
         </is>
       </c>
       <c r="E118" s="7" t="n">
-        <v>1995</v>
+        <v>1989</v>
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
@@ -5027,19 +5143,15 @@
       </c>
       <c r="G118" s="5" t="inlineStr">
         <is>
-          <t>Approximate</t>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="H118" s="8" t="inlineStr">
         <is>
-          <t>Oakmont age roster: 28 in Oct 2023; Emory golf 2014-18 agrees</t>
-        </is>
-      </c>
-      <c r="I118" s="8" t="inlineStr">
-        <is>
-          <t>Year only, worked out from an age or school year – a real date would be better</t>
-        </is>
-      </c>
+          <t>Oakmont age roster, Aug 2025</t>
+        </is>
+      </c>
+      <c r="I118" s="8" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
@@ -5049,25 +5161,25 @@
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>A. Hofmann</t>
+          <t>B. Kittsley</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>2007–2022</t>
+          <t>2009–2020</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>8 May 1989</t>
+          <t>7 Dec 1974</t>
         </is>
       </c>
       <c r="E119" s="7" t="n">
-        <v>1989</v>
+        <v>1974</v>
       </c>
       <c r="F119" s="5" t="inlineStr">
         <is>
-          <t>30–39</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
@@ -5090,21 +5202,21 @@
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>B. Kittsley</t>
+          <t>Scott Lamond</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>2009–2020</t>
+          <t>2008–2015</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>7 Dec 1974</t>
+          <t>30 Jun 1969</t>
         </is>
       </c>
       <c r="E120" s="7" t="n">
-        <v>1974</v>
+        <v>1969</v>
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
@@ -5131,38 +5243,42 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>Scott Lamond</t>
+          <t>A. Lawson</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>2008–2015</t>
-        </is>
-      </c>
-      <c r="D121" s="5" t="inlineStr">
-        <is>
-          <t>30 Jun 1969</t>
+          <t>2017–2018</t>
+        </is>
+      </c>
+      <c r="D121" s="6" t="inlineStr">
+        <is>
+          <t>1993</t>
         </is>
       </c>
       <c r="E121" s="7" t="n">
-        <v>1969</v>
+        <v>1993</v>
       </c>
       <c r="F121" s="5" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>30–39</t>
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Approximate</t>
         </is>
       </c>
       <c r="H121" s="8" t="inlineStr">
         <is>
-          <t>Oakmont age roster, Aug 2025</t>
-        </is>
-      </c>
-      <c r="I121" s="8" t="inlineStr"/>
+          <t>Oakmont age roster: 30 in Oct 2023</t>
+        </is>
+      </c>
+      <c r="I121" s="8" t="inlineStr">
+        <is>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
@@ -5172,42 +5288,38 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>A. Lawson</t>
+          <t>Steve Leone</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>2017–2018</t>
-        </is>
-      </c>
-      <c r="D122" s="6" t="inlineStr">
-        <is>
-          <t>1993</t>
+          <t>2003–2024</t>
+        </is>
+      </c>
+      <c r="D122" s="5" t="inlineStr">
+        <is>
+          <t>24 May 1976</t>
         </is>
       </c>
       <c r="E122" s="7" t="n">
-        <v>1993</v>
+        <v>1976</v>
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>30–39</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G122" s="5" t="inlineStr">
         <is>
-          <t>Approximate</t>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="H122" s="8" t="inlineStr">
         <is>
-          <t>Oakmont age roster: 30 in Oct 2023</t>
-        </is>
-      </c>
-      <c r="I122" s="8" t="inlineStr">
-        <is>
-          <t>Year only, worked out from an age or school year – a real date would be better</t>
-        </is>
-      </c>
+          <t>Oakmont age roster, Aug 2025</t>
+        </is>
+      </c>
+      <c r="I122" s="8" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
@@ -5217,38 +5329,42 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>Steve Leone</t>
+          <t>W. Livingston</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>2003–2024</t>
-        </is>
-      </c>
-      <c r="D123" s="5" t="inlineStr">
-        <is>
-          <t>24 May 1976</t>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="D123" s="6" t="inlineStr">
+        <is>
+          <t>2003</t>
         </is>
       </c>
       <c r="E123" s="7" t="n">
-        <v>1976</v>
+        <v>2003</v>
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Under 25</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Approximate</t>
         </is>
       </c>
       <c r="H123" s="8" t="inlineStr">
         <is>
-          <t>Oakmont age roster, Aug 2025</t>
-        </is>
-      </c>
-      <c r="I123" s="8" t="inlineStr"/>
+          <t>Oakmont age roster: 20 in Oct 2023</t>
+        </is>
+      </c>
+      <c r="I123" s="8" t="inlineStr">
+        <is>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
@@ -5258,42 +5374,38 @@
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>W. Livingston</t>
+          <t>Paul Mazeski</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="D124" s="6" t="inlineStr">
-        <is>
-          <t>2003</t>
+          <t>2000–2021</t>
+        </is>
+      </c>
+      <c r="D124" s="5" t="inlineStr">
+        <is>
+          <t>29 Apr 1963</t>
         </is>
       </c>
       <c r="E124" s="7" t="n">
-        <v>2003</v>
+        <v>1963</v>
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t>Under 25</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G124" s="5" t="inlineStr">
         <is>
-          <t>Approximate</t>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="H124" s="8" t="inlineStr">
         <is>
-          <t>Oakmont age roster: 20 in Oct 2023</t>
-        </is>
-      </c>
-      <c r="I124" s="8" t="inlineStr">
-        <is>
-          <t>Year only, worked out from an age or school year – a real date would be better</t>
-        </is>
-      </c>
+          <t>Oakmont age roster, Aug 2025</t>
+        </is>
+      </c>
+      <c r="I124" s="8" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
@@ -5303,25 +5415,25 @@
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>Paul Mazeski</t>
+          <t>Robby Mazeski</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>2000–2021</t>
+          <t>2013–2016</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>29 Apr 1963</t>
+          <t>20 Nov 1993</t>
         </is>
       </c>
       <c r="E125" s="7" t="n">
-        <v>1963</v>
+        <v>1993</v>
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>30–39</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr">
@@ -5344,21 +5456,21 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>Robby Mazeski</t>
+          <t>Spencer Mellon</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>2013–2016</t>
+          <t>2009–2015</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>20 Nov 1993</t>
+          <t>23 Sep 1991</t>
         </is>
       </c>
       <c r="E126" s="7" t="n">
-        <v>1993</v>
+        <v>1991</v>
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
@@ -5385,21 +5497,21 @@
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>Spencer Mellon</t>
+          <t>Mitch Mercer</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>2009–2015</t>
+          <t>2020–2025</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 1991</t>
+          <t>21 Jul 1987</t>
         </is>
       </c>
       <c r="E127" s="7" t="n">
-        <v>1991</v>
+        <v>1987</v>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
@@ -5426,25 +5538,25 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>Mitch Mercer</t>
+          <t>Jimmy Meyers</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>2020–2025</t>
+          <t>2017–2024</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>21 Jul 1987</t>
+          <t>1 Jun 2000</t>
         </is>
       </c>
       <c r="E128" s="7" t="n">
-        <v>1987</v>
+        <v>2000</v>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>30–39</t>
+          <t>25–29</t>
         </is>
       </c>
       <c r="G128" s="5" t="inlineStr">
@@ -5467,25 +5579,25 @@
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>Jimmy Meyers</t>
+          <t>Justin Miller</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>2017–2024</t>
+          <t>2010–2024</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>1 Jun 2000</t>
+          <t>13 Jan 1993</t>
         </is>
       </c>
       <c r="E129" s="7" t="n">
-        <v>2000</v>
+        <v>1993</v>
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
-          <t>25–29</t>
+          <t>30–39</t>
         </is>
       </c>
       <c r="G129" s="5" t="inlineStr">
@@ -5508,21 +5620,21 @@
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>Justin Miller</t>
+          <t>Chuck Nettles</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>2010–2024</t>
+          <t>2016–2025</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>13 Jan 1993</t>
+          <t>11 Oct 1988</t>
         </is>
       </c>
       <c r="E130" s="7" t="n">
-        <v>1993</v>
+        <v>1988</v>
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
@@ -5549,21 +5661,21 @@
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>Chuck Nettles</t>
+          <t>Tommy Nettles</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>2016–2025</t>
+          <t>2024–2025</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>11 Oct 1988</t>
+          <t>17 Nov 1994</t>
         </is>
       </c>
       <c r="E131" s="7" t="n">
-        <v>1988</v>
+        <v>1994</v>
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
@@ -5577,7 +5689,7 @@
       </c>
       <c r="H131" s="8" t="inlineStr">
         <is>
-          <t>Oakmont age roster, Aug 2025</t>
+          <t>PGA Tour player bio (Tom Nettles, McMurray PA)</t>
         </is>
       </c>
       <c r="I131" s="8" t="inlineStr"/>
@@ -5590,25 +5702,25 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>Tommy Nettles</t>
+          <t>Nathan Piatt</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>2024–2025</t>
+          <t>2022–2025</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>17 Nov 1994</t>
+          <t>12 Mar 2002</t>
         </is>
       </c>
       <c r="E132" s="7" t="n">
-        <v>1994</v>
+        <v>2002</v>
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>30–39</t>
+          <t>Under 25</t>
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr">
@@ -5618,7 +5730,7 @@
       </c>
       <c r="H132" s="8" t="inlineStr">
         <is>
-          <t>PGA Tour player bio (Tom Nettles, McMurray PA)</t>
+          <t>Oakmont age roster, Aug 2025</t>
         </is>
       </c>
       <c r="I132" s="8" t="inlineStr"/>
@@ -5631,21 +5743,21 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>Nathan Piatt</t>
+          <t>Carter Pitcairn</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>2022–2025</t>
+          <t>2021–2025</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>12 Mar 2002</t>
+          <t>11 Jul 2003</t>
         </is>
       </c>
       <c r="E133" s="7" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
@@ -5659,7 +5771,7 @@
       </c>
       <c r="H133" s="8" t="inlineStr">
         <is>
-          <t>Oakmont age roster, Aug 2025</t>
+          <t>High Point University men's golf roster</t>
         </is>
       </c>
       <c r="I133" s="8" t="inlineStr"/>
@@ -5672,21 +5784,21 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>Carter Pitcairn</t>
+          <t>Rocco Salvitti</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>2021–2025</t>
-        </is>
-      </c>
-      <c r="D134" s="5" t="inlineStr">
-        <is>
-          <t>11 Jul 2003</t>
+          <t>2022–2025</t>
+        </is>
+      </c>
+      <c r="D134" s="6" t="inlineStr">
+        <is>
+          <t>2005</t>
         </is>
       </c>
       <c r="E134" s="7" t="n">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
@@ -5695,15 +5807,19 @@
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Approximate</t>
         </is>
       </c>
       <c r="H134" s="8" t="inlineStr">
         <is>
-          <t>High Point University men's golf roster</t>
-        </is>
-      </c>
-      <c r="I134" s="8" t="inlineStr"/>
+          <t>Central Catholic class of 2023, Notre Dame class of 2027; 18 on the Oakmont roster in Oct 2023</t>
+        </is>
+      </c>
+      <c r="I134" s="8" t="inlineStr">
+        <is>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
@@ -5713,12 +5829,12 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>Rocco Salvitti</t>
+          <t>Nolan Shilling</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>2022–2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D135" s="6" t="inlineStr">
@@ -5741,7 +5857,7 @@
       </c>
       <c r="H135" s="8" t="inlineStr">
         <is>
-          <t>Central Catholic class of 2023, Notre Dame class of 2027; 18 on the Oakmont roster in Oct 2023</t>
+          <t>Franklin Regional class of 2023; signed with Youngstown State for 2023-24</t>
         </is>
       </c>
       <c r="I135" s="8" t="inlineStr">
@@ -5758,42 +5874,38 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>Nolan Shilling</t>
+          <t>Marty Slovonic</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D136" s="6" t="inlineStr">
-        <is>
-          <t>2005</t>
+          <t>2009–2017</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 1961</t>
         </is>
       </c>
       <c r="E136" s="7" t="n">
-        <v>2005</v>
+        <v>1961</v>
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
-          <t>Under 25</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G136" s="5" t="inlineStr">
         <is>
-          <t>Approximate</t>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="H136" s="8" t="inlineStr">
         <is>
-          <t>Franklin Regional class of 2023; signed with Youngstown State for 2023-24</t>
-        </is>
-      </c>
-      <c r="I136" s="8" t="inlineStr">
-        <is>
-          <t>Year only, worked out from an age or school year – a real date would be better</t>
-        </is>
-      </c>
+          <t>Oakmont age roster, Aug 2025</t>
+        </is>
+      </c>
+      <c r="I136" s="8" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
@@ -5803,21 +5915,21 @@
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>Marty Slovonic</t>
+          <t>Win Smathers</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>2009–2017</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 1961</t>
+          <t>9 Mar 1968</t>
         </is>
       </c>
       <c r="E137" s="7" t="n">
-        <v>1961</v>
+        <v>1968</v>
       </c>
       <c r="F137" s="5" t="inlineStr">
         <is>
@@ -5844,25 +5956,25 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>Win Smathers</t>
+          <t>Malcolm Spatz</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2000–2025</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>9 Mar 1968</t>
+          <t>21 Jul 1981</t>
         </is>
       </c>
       <c r="E138" s="7" t="n">
-        <v>1968</v>
+        <v>1981</v>
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>40–49</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr">
@@ -5885,38 +5997,42 @@
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>Malcolm Spatz</t>
+          <t>Jim Sullivan Jr.</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>2000–2025</t>
-        </is>
-      </c>
-      <c r="D139" s="5" t="inlineStr">
-        <is>
-          <t>21 Jul 1981</t>
+          <t>2000–2020</t>
+        </is>
+      </c>
+      <c r="D139" s="6" t="inlineStr">
+        <is>
+          <t>1967</t>
         </is>
       </c>
       <c r="E139" s="7" t="n">
-        <v>1981</v>
+        <v>1967</v>
       </c>
       <c r="F139" s="5" t="inlineStr">
         <is>
-          <t>40–49</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Approximate</t>
         </is>
       </c>
       <c r="H139" s="8" t="inlineStr">
         <is>
-          <t>Oakmont age roster, Aug 2025</t>
-        </is>
-      </c>
-      <c r="I139" s="8" t="inlineStr"/>
+          <t>Oakmont age roster: 56 in Oct 2023</t>
+        </is>
+      </c>
+      <c r="I139" s="8" t="inlineStr">
+        <is>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
@@ -5926,42 +6042,38 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>Jim Sullivan Jr.</t>
+          <t>Tom Summers</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>2000–2020</t>
-        </is>
-      </c>
-      <c r="D140" s="6" t="inlineStr">
-        <is>
-          <t>1967</t>
+          <t>2018–2025</t>
+        </is>
+      </c>
+      <c r="D140" s="5" t="inlineStr">
+        <is>
+          <t>26 Sep 1989</t>
         </is>
       </c>
       <c r="E140" s="7" t="n">
-        <v>1967</v>
+        <v>1989</v>
       </c>
       <c r="F140" s="5" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>30–39</t>
         </is>
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>Approximate</t>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="H140" s="8" t="inlineStr">
         <is>
-          <t>Oakmont age roster: 56 in Oct 2023</t>
-        </is>
-      </c>
-      <c r="I140" s="8" t="inlineStr">
-        <is>
-          <t>Year only, worked out from an age or school year – a real date would be better</t>
-        </is>
-      </c>
+          <t>Oakmont age roster, Aug 2025</t>
+        </is>
+      </c>
+      <c r="I140" s="8" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
@@ -5971,17 +6083,17 @@
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>Tom Summers</t>
+          <t>Nathan Sutherland</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>2018–2025</t>
+          <t>2000–2025</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>26 Sep 1989</t>
+          <t>22 Jun 1989</t>
         </is>
       </c>
       <c r="E141" s="7" t="n">
@@ -6012,25 +6124,25 @@
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>Nathan Sutherland</t>
+          <t>Arne Thomas</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>2000–2025</t>
+          <t>2015–2017</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>22 Jun 1989</t>
+          <t>2 Apr 1966</t>
         </is>
       </c>
       <c r="E142" s="7" t="n">
-        <v>1989</v>
+        <v>1966</v>
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
-          <t>30–39</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G142" s="5" t="inlineStr">
@@ -6053,21 +6165,21 @@
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>Arne Thomas</t>
+          <t>S. Thomas</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>2015–2017</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>2 Apr 1966</t>
+          <t>13 Jun 1967</t>
         </is>
       </c>
       <c r="E143" s="7" t="n">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="F143" s="5" t="inlineStr">
         <is>
@@ -6094,21 +6206,21 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>S. Thomas</t>
+          <t>Chick Wagner</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2000–2014</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>13 Jun 1967</t>
+          <t>1 Mar 1954</t>
         </is>
       </c>
       <c r="E144" s="7" t="n">
-        <v>1967</v>
+        <v>1954</v>
       </c>
       <c r="F144" s="5" t="inlineStr">
         <is>
@@ -6135,38 +6247,42 @@
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>Chick Wagner</t>
+          <t>Corey Wagner</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>2000–2014</t>
-        </is>
-      </c>
-      <c r="D145" s="5" t="inlineStr">
-        <is>
-          <t>1 Mar 1954</t>
+          <t>2010–2014</t>
+        </is>
+      </c>
+      <c r="D145" s="6" t="inlineStr">
+        <is>
+          <t>1993</t>
         </is>
       </c>
       <c r="E145" s="7" t="n">
-        <v>1954</v>
+        <v>1993</v>
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>30–39</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Approximate</t>
         </is>
       </c>
       <c r="H145" s="8" t="inlineStr">
         <is>
-          <t>Oakmont age roster, Aug 2025</t>
-        </is>
-      </c>
-      <c r="I145" s="8" t="inlineStr"/>
+          <t>Oakmont age roster: 30 in Oct 2023</t>
+        </is>
+      </c>
+      <c r="I145" s="8" t="inlineStr">
+        <is>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
@@ -6176,21 +6292,21 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>Corey Wagner</t>
+          <t>Chad Warmbein</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>2010–2014</t>
-        </is>
-      </c>
-      <c r="D146" s="6" t="inlineStr">
-        <is>
-          <t>1993</t>
+          <t>2023–2025</t>
+        </is>
+      </c>
+      <c r="D146" s="5" t="inlineStr">
+        <is>
+          <t>29 Jun 1988</t>
         </is>
       </c>
       <c r="E146" s="7" t="n">
-        <v>1993</v>
+        <v>1988</v>
       </c>
       <c r="F146" s="5" t="inlineStr">
         <is>
@@ -6199,60 +6315,54 @@
       </c>
       <c r="G146" s="5" t="inlineStr">
         <is>
-          <t>Approximate</t>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="H146" s="8" t="inlineStr">
         <is>
-          <t>Oakmont age roster: 30 in Oct 2023</t>
-        </is>
-      </c>
-      <c r="I146" s="8" t="inlineStr">
-        <is>
-          <t>Year only, worked out from an age or school year – a real date would be better</t>
-        </is>
-      </c>
+          <t>Oakmont age roster, Aug 2025</t>
+        </is>
+      </c>
+      <c r="I146" s="8" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>Oakmont</t>
+          <t>Longue Vue</t>
         </is>
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>Chad Warmbein</t>
+          <t>Al Beeken</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>2023–2025</t>
-        </is>
-      </c>
-      <c r="D147" s="5" t="inlineStr">
-        <is>
-          <t>29 Jun 1988</t>
-        </is>
-      </c>
-      <c r="E147" s="7" t="n">
-        <v>1988</v>
-      </c>
+          <t>2000–2013</t>
+        </is>
+      </c>
+      <c r="D147" s="6" t="inlineStr"/>
+      <c r="E147" s="7" t="n"/>
       <c r="F147" s="5" t="inlineStr">
         <is>
-          <t>30–39</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Band only</t>
         </is>
       </c>
       <c r="H147" s="8" t="inlineStr">
         <is>
-          <t>Oakmont age roster, Aug 2025</t>
-        </is>
-      </c>
-      <c r="I147" s="8" t="inlineStr"/>
+          <t>60+ per Tommy Leech, Oct 2026 (bands stop at 50+)</t>
+        </is>
+      </c>
+      <c r="I147" s="8" t="inlineStr">
+        <is>
+          <t>Only an age band is known – a year would be better</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
@@ -6262,12 +6372,12 @@
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>Al Beeken</t>
+          <t>Joe Bertucci</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>2000–2013</t>
+          <t>2008–2013</t>
         </is>
       </c>
       <c r="D148" s="6" t="inlineStr"/>
@@ -6293,26 +6403,40 @@
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>Joe Bertucci</t>
+          <t>Will Betts</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>2008–2013</t>
-        </is>
-      </c>
-      <c r="D149" s="6" t="inlineStr"/>
-      <c r="E149" s="7" t="n"/>
-      <c r="F149" s="5" t="inlineStr"/>
+          <t>2008–2025</t>
+        </is>
+      </c>
+      <c r="D149" s="6" t="inlineStr">
+        <is>
+          <t>1993</t>
+        </is>
+      </c>
+      <c r="E149" s="7" t="n">
+        <v>1993</v>
+      </c>
+      <c r="F149" s="5" t="inlineStr">
+        <is>
+          <t>30–39</t>
+        </is>
+      </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="H149" s="8" t="inlineStr"/>
+          <t>Approximate</t>
+        </is>
+      </c>
+      <c r="H149" s="8" t="inlineStr">
+        <is>
+          <t>Fox Chapel HS freshman in 2007, then prep school, class of 2011/12 (Tommy Leech); Hartford golf senior 2015-16</t>
+        </is>
+      </c>
       <c r="I149" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
       </c>
     </row>
@@ -6324,21 +6448,21 @@
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>Will Betts</t>
+          <t>Will Bloss</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>2008–2025</t>
+          <t>2009–2018</t>
         </is>
       </c>
       <c r="D150" s="6" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="E150" s="7" t="n">
-        <v>1993</v>
+        <v>1991</v>
       </c>
       <c r="F150" s="5" t="inlineStr">
         <is>
@@ -6352,7 +6476,7 @@
       </c>
       <c r="H150" s="8" t="inlineStr">
         <is>
-          <t>Fox Chapel HS freshman in 2007, then prep school, class of 2011/12 (Tommy Leech); Hartford golf senior 2015-16</t>
+          <t>A year older than Tommy Leech (Tommy, Oct 2026)</t>
         </is>
       </c>
       <c r="I150" s="8" t="inlineStr">
@@ -6369,26 +6493,40 @@
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>W. Bloss</t>
+          <t>JJ Bush Jr.</t>
         </is>
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>2009–2018</t>
-        </is>
-      </c>
-      <c r="D151" s="6" t="inlineStr"/>
-      <c r="E151" s="7" t="n"/>
-      <c r="F151" s="5" t="inlineStr"/>
+          <t>2018–2025</t>
+        </is>
+      </c>
+      <c r="D151" s="6" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="E151" s="7" t="n">
+        <v>1992</v>
+      </c>
+      <c r="F151" s="5" t="inlineStr">
+        <is>
+          <t>30–39</t>
+        </is>
+      </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="H151" s="8" t="inlineStr"/>
+          <t>Approximate</t>
+        </is>
+      </c>
+      <c r="H151" s="8" t="inlineStr">
+        <is>
+          <t>Same age as Tommy Leech; Central Catholic (Tommy, Oct 2026)</t>
+        </is>
+      </c>
       <c r="I151" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
       </c>
     </row>
@@ -6400,26 +6538,34 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>JJ Bush Jr.</t>
+          <t>Mike Colville</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>2018–2025</t>
+          <t>2000–2019</t>
         </is>
       </c>
       <c r="D152" s="6" t="inlineStr"/>
       <c r="E152" s="7" t="n"/>
-      <c r="F152" s="5" t="inlineStr"/>
+      <c r="F152" s="5" t="inlineStr">
+        <is>
+          <t>50+</t>
+        </is>
+      </c>
       <c r="G152" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="H152" s="8" t="inlineStr"/>
+          <t>Band only</t>
+        </is>
+      </c>
+      <c r="H152" s="8" t="inlineStr">
+        <is>
+          <t>Tommy Leech, Oct 2026</t>
+        </is>
+      </c>
       <c r="I152" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Only an age band is known – a year would be better</t>
         </is>
       </c>
     </row>
@@ -6431,34 +6577,26 @@
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>Mike Colville</t>
+          <t>P. Compeau</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>2000–2019</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="D153" s="6" t="inlineStr"/>
       <c r="E153" s="7" t="n"/>
-      <c r="F153" s="5" t="inlineStr">
-        <is>
-          <t>50+</t>
-        </is>
-      </c>
+      <c r="F153" s="5" t="inlineStr"/>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>Band only</t>
-        </is>
-      </c>
-      <c r="H153" s="8" t="inlineStr">
-        <is>
-          <t>Tommy Leech, Oct 2026</t>
-        </is>
-      </c>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="H153" s="8" t="inlineStr"/>
       <c r="I153" s="8" t="inlineStr">
         <is>
-          <t>Only an age band is known – a year would be better</t>
+          <t>Please add</t>
         </is>
       </c>
     </row>
@@ -6470,26 +6608,40 @@
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>P. Compeau</t>
+          <t>Anthony Cordaro</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="D154" s="6" t="inlineStr"/>
-      <c r="E154" s="7" t="n"/>
-      <c r="F154" s="5" t="inlineStr"/>
+          <t>2013–2018</t>
+        </is>
+      </c>
+      <c r="D154" s="6" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="E154" s="7" t="n">
+        <v>1997</v>
+      </c>
+      <c r="F154" s="5" t="inlineStr">
+        <is>
+          <t>25–29</t>
+        </is>
+      </c>
       <c r="G154" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="H154" s="8" t="inlineStr"/>
+          <t>Approximate</t>
+        </is>
+      </c>
+      <c r="H154" s="8" t="inlineStr">
+        <is>
+          <t>Pittsburgh entrant in 2014 U.S. Junior Amateur qualifying (under 19); uncertain by a year or two</t>
+        </is>
+      </c>
       <c r="I154" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
       </c>
     </row>
@@ -6501,40 +6653,34 @@
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>Anthony Cordaro</t>
+          <t>Joe Cordaro</t>
         </is>
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>2013–2018</t>
-        </is>
-      </c>
-      <c r="D155" s="6" t="inlineStr">
-        <is>
-          <t>1997</t>
-        </is>
-      </c>
-      <c r="E155" s="7" t="n">
-        <v>1997</v>
-      </c>
+          <t>2007–2016</t>
+        </is>
+      </c>
+      <c r="D155" s="6" t="inlineStr"/>
+      <c r="E155" s="7" t="n"/>
       <c r="F155" s="5" t="inlineStr">
         <is>
-          <t>25–29</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>Approximate</t>
+          <t>Band only</t>
         </is>
       </c>
       <c r="H155" s="8" t="inlineStr">
         <is>
-          <t>Pittsburgh entrant in 2014 U.S. Junior Amateur qualifying (under 19); uncertain by a year or two</t>
+          <t>Tommy Leech, Oct 2026</t>
         </is>
       </c>
       <c r="I155" s="8" t="inlineStr">
         <is>
-          <t>Year only, worked out from an age or school year – a real date would be better</t>
+          <t>Only an age band is known – a year would be better</t>
         </is>
       </c>
     </row>
@@ -6546,26 +6692,34 @@
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>Joe Cordaro</t>
+          <t>Jim Crawford</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>2007–2016</t>
+          <t>2007–2018</t>
         </is>
       </c>
       <c r="D156" s="6" t="inlineStr"/>
       <c r="E156" s="7" t="n"/>
-      <c r="F156" s="5" t="inlineStr"/>
+      <c r="F156" s="5" t="inlineStr">
+        <is>
+          <t>50+</t>
+        </is>
+      </c>
       <c r="G156" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="H156" s="8" t="inlineStr"/>
+          <t>Band only</t>
+        </is>
+      </c>
+      <c r="H156" s="8" t="inlineStr">
+        <is>
+          <t>Tommy Leech, Oct 2026</t>
+        </is>
+      </c>
       <c r="I156" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Only an age band is known – a year would be better</t>
         </is>
       </c>
     </row>
@@ -6577,34 +6731,40 @@
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>Jim Crawford</t>
+          <t>Amani D'Ambrosio</t>
         </is>
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>2007–2018</t>
-        </is>
-      </c>
-      <c r="D157" s="6" t="inlineStr"/>
-      <c r="E157" s="7" t="n"/>
+          <t>2024–2025</t>
+        </is>
+      </c>
+      <c r="D157" s="6" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="E157" s="7" t="n">
+        <v>2002</v>
+      </c>
       <c r="F157" s="5" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Under 25</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>Band only</t>
+          <t>Approximate</t>
         </is>
       </c>
       <c r="H157" s="8" t="inlineStr">
         <is>
-          <t>Tommy Leech, Oct 2026</t>
+          <t>Fox Chapel HS, 2020 High School Golf National Invitational; Barry University golf, senior 2023-24</t>
         </is>
       </c>
       <c r="I157" s="8" t="inlineStr">
         <is>
-          <t>Only an age band is known – a year would be better</t>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
       </c>
     </row>
@@ -6616,26 +6776,40 @@
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>Amani D'Ambrosio</t>
+          <t>Tim Derdenger</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>2024–2025</t>
-        </is>
-      </c>
-      <c r="D158" s="6" t="inlineStr"/>
-      <c r="E158" s="7" t="n"/>
-      <c r="F158" s="5" t="inlineStr"/>
+          <t>2015–2016</t>
+        </is>
+      </c>
+      <c r="D158" s="6" t="inlineStr">
+        <is>
+          <t>1980</t>
+        </is>
+      </c>
+      <c r="E158" s="7" t="n">
+        <v>1980</v>
+      </c>
+      <c r="F158" s="5" t="inlineStr">
+        <is>
+          <t>40–49</t>
+        </is>
+      </c>
       <c r="G158" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="H158" s="8" t="inlineStr"/>
+          <t>Approximate</t>
+        </is>
+      </c>
+      <c r="H158" s="8" t="inlineStr">
+        <is>
+          <t>Age 45 in Poets &amp; Quants profile, 2025</t>
+        </is>
+      </c>
       <c r="I158" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
       </c>
     </row>
@@ -6647,21 +6821,21 @@
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>Tim Derdenger</t>
+          <t>Sam Duerr</t>
         </is>
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>2015–2016</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D159" s="6" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="E159" s="7" t="n">
-        <v>1980</v>
+        <v>1986</v>
       </c>
       <c r="F159" s="5" t="inlineStr">
         <is>
@@ -6675,7 +6849,7 @@
       </c>
       <c r="H159" s="8" t="inlineStr">
         <is>
-          <t>Age 45 in Poets &amp; Quants profile, 2025</t>
+          <t>About 40 in Oct 2026 (Tommy Leech)</t>
         </is>
       </c>
       <c r="I159" s="8" t="inlineStr">
@@ -6692,26 +6866,40 @@
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>Duerr</t>
+          <t>Derek Evans</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D160" s="6" t="inlineStr"/>
-      <c r="E160" s="7" t="n"/>
-      <c r="F160" s="5" t="inlineStr"/>
+          <t>2021–2025</t>
+        </is>
+      </c>
+      <c r="D160" s="6" t="inlineStr">
+        <is>
+          <t>1986</t>
+        </is>
+      </c>
+      <c r="E160" s="7" t="n">
+        <v>1986</v>
+      </c>
+      <c r="F160" s="5" t="inlineStr">
+        <is>
+          <t>40–49</t>
+        </is>
+      </c>
       <c r="G160" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="H160" s="8" t="inlineStr"/>
+          <t>Approximate</t>
+        </is>
+      </c>
+      <c r="H160" s="8" t="inlineStr">
+        <is>
+          <t>About 40 in Oct 2026 (Tommy Leech)</t>
+        </is>
+      </c>
       <c r="I160" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
       </c>
     </row>
@@ -6723,12 +6911,12 @@
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>Derek Evans</t>
+          <t>F. Fisch</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>2021–2025</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D161" s="6" t="inlineStr"/>
@@ -6754,12 +6942,12 @@
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>F. Fisch</t>
+          <t>Matt Fisch</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2014–2021</t>
         </is>
       </c>
       <c r="D162" s="6" t="inlineStr"/>
@@ -6785,12 +6973,12 @@
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>Matt Fisch</t>
+          <t>Mike Gielarowski</t>
         </is>
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>2014–2021</t>
+          <t>2021–2025</t>
         </is>
       </c>
       <c r="D163" s="6" t="inlineStr"/>
@@ -6816,26 +7004,40 @@
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>Mike Gielarowski</t>
+          <t>Nick Gordon</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>2021–2025</t>
-        </is>
-      </c>
-      <c r="D164" s="6" t="inlineStr"/>
-      <c r="E164" s="7" t="n"/>
-      <c r="F164" s="5" t="inlineStr"/>
+          <t>2019–2024</t>
+        </is>
+      </c>
+      <c r="D164" s="6" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="E164" s="7" t="n">
+        <v>1991</v>
+      </c>
+      <c r="F164" s="5" t="inlineStr">
+        <is>
+          <t>30–39</t>
+        </is>
+      </c>
       <c r="G164" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="H164" s="8" t="inlineStr"/>
+          <t>Approximate</t>
+        </is>
+      </c>
+      <c r="H164" s="8" t="inlineStr">
+        <is>
+          <t>About 35 in Oct 2026 (Tommy Leech)</t>
+        </is>
+      </c>
       <c r="I164" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
       </c>
     </row>
@@ -6847,26 +7049,40 @@
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>Nick Gordon</t>
+          <t>Brendan Gramley</t>
         </is>
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>2019–2024</t>
-        </is>
-      </c>
-      <c r="D165" s="6" t="inlineStr"/>
-      <c r="E165" s="7" t="n"/>
-      <c r="F165" s="5" t="inlineStr"/>
+          <t>2014–2015</t>
+        </is>
+      </c>
+      <c r="D165" s="6" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="E165" s="7" t="n">
+        <v>1994</v>
+      </c>
+      <c r="F165" s="5" t="inlineStr">
+        <is>
+          <t>30–39</t>
+        </is>
+      </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="H165" s="8" t="inlineStr"/>
+          <t>Approximate</t>
+        </is>
+      </c>
+      <c r="H165" s="8" t="inlineStr">
+        <is>
+          <t>Shady Side Academy; senior on the South Carolina golf roster 2015-16</t>
+        </is>
+      </c>
       <c r="I165" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
       </c>
     </row>
@@ -6878,25 +7094,25 @@
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>Brendan Gramley</t>
+          <t>Tanner Grzegorczyk</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>2014–2015</t>
+          <t>2022–2023</t>
         </is>
       </c>
       <c r="D166" s="6" t="inlineStr">
         <is>
-          <t>1994</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="E166" s="7" t="n">
-        <v>1994</v>
+        <v>2000</v>
       </c>
       <c r="F166" s="5" t="inlineStr">
         <is>
-          <t>30–39</t>
+          <t>25–29</t>
         </is>
       </c>
       <c r="G166" s="5" t="inlineStr">
@@ -6906,7 +7122,7 @@
       </c>
       <c r="H166" s="8" t="inlineStr">
         <is>
-          <t>Shady Side Academy; senior on the South Carolina golf roster 2015-16</t>
+          <t>Shaler graduate; Findlay golf, senior in 2023; uncertain by a year or two</t>
         </is>
       </c>
       <c r="I166" s="8" t="inlineStr">
@@ -6923,25 +7139,25 @@
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>Tanner Grzegorczyk</t>
+          <t>Kevin Heher</t>
         </is>
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>2022–2023</t>
+          <t>2012–2023</t>
         </is>
       </c>
       <c r="D167" s="6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="E167" s="7" t="n">
-        <v>2000</v>
+        <v>1984</v>
       </c>
       <c r="F167" s="5" t="inlineStr">
         <is>
-          <t>25–29</t>
+          <t>40–49</t>
         </is>
       </c>
       <c r="G167" s="5" t="inlineStr">
@@ -6951,7 +7167,7 @@
       </c>
       <c r="H167" s="8" t="inlineStr">
         <is>
-          <t>Shaler graduate; Findlay golf, senior in 2023; uncertain by a year or two</t>
+          <t>About 42 in Oct 2026 (Tommy Leech)</t>
         </is>
       </c>
       <c r="I167" s="8" t="inlineStr">
@@ -6968,25 +7184,25 @@
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>Kevin Heher</t>
+          <t>Andrew Hodge</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>2012–2023</t>
+          <t>2015–2025</t>
         </is>
       </c>
       <c r="D168" s="6" t="inlineStr">
         <is>
-          <t>1984</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="E168" s="7" t="n">
-        <v>1984</v>
+        <v>1990</v>
       </c>
       <c r="F168" s="5" t="inlineStr">
         <is>
-          <t>40–49</t>
+          <t>30–39</t>
         </is>
       </c>
       <c r="G168" s="5" t="inlineStr">
@@ -6996,7 +7212,7 @@
       </c>
       <c r="H168" s="8" t="inlineStr">
         <is>
-          <t>About 42 in Oct 2026 (Tommy Leech)</t>
+          <t>About 36 in Oct 2026 (Tommy Leech)</t>
         </is>
       </c>
       <c r="I168" s="8" t="inlineStr">
@@ -7013,12 +7229,12 @@
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>Andrew Hodge</t>
+          <t>Kevin Koerbel</t>
         </is>
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>2015–2025</t>
+          <t>2021–2025</t>
         </is>
       </c>
       <c r="D169" s="6" t="inlineStr">
@@ -7041,7 +7257,7 @@
       </c>
       <c r="H169" s="8" t="inlineStr">
         <is>
-          <t>About 36 in Oct 2026 (Tommy Leech)</t>
+          <t>Deer Lakes; Penn State Behrend golf 2009-11</t>
         </is>
       </c>
       <c r="I169" s="8" t="inlineStr">
@@ -7058,40 +7274,26 @@
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>Kevin Koerbel</t>
+          <t>David Koi</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>2021–2025</t>
-        </is>
-      </c>
-      <c r="D170" s="6" t="inlineStr">
-        <is>
-          <t>1990</t>
-        </is>
-      </c>
-      <c r="E170" s="7" t="n">
-        <v>1990</v>
-      </c>
-      <c r="F170" s="5" t="inlineStr">
-        <is>
-          <t>30–39</t>
-        </is>
-      </c>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="D170" s="6" t="inlineStr"/>
+      <c r="E170" s="7" t="n"/>
+      <c r="F170" s="5" t="inlineStr"/>
       <c r="G170" s="5" t="inlineStr">
         <is>
-          <t>Approximate</t>
-        </is>
-      </c>
-      <c r="H170" s="8" t="inlineStr">
-        <is>
-          <t>Deer Lakes; Penn State Behrend golf 2009-11</t>
-        </is>
-      </c>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="H170" s="8" t="inlineStr"/>
       <c r="I170" s="8" t="inlineStr">
         <is>
-          <t>Year only, worked out from an age or school year – a real date would be better</t>
+          <t>Please add</t>
         </is>
       </c>
     </row>
@@ -7103,7 +7305,7 @@
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>David Koi</t>
+          <t>Stu Lotz</t>
         </is>
       </c>
       <c r="C171" s="5" t="inlineStr">
@@ -7111,18 +7313,32 @@
           <t>2015</t>
         </is>
       </c>
-      <c r="D171" s="6" t="inlineStr"/>
-      <c r="E171" s="7" t="n"/>
-      <c r="F171" s="5" t="inlineStr"/>
+      <c r="D171" s="6" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="E171" s="7" t="n">
+        <v>1992</v>
+      </c>
+      <c r="F171" s="5" t="inlineStr">
+        <is>
+          <t>30–39</t>
+        </is>
+      </c>
       <c r="G171" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="H171" s="8" t="inlineStr"/>
+          <t>Approximate</t>
+        </is>
+      </c>
+      <c r="H171" s="8" t="inlineStr">
+        <is>
+          <t>Same age as Tommy Leech (Tommy, Oct 2026)</t>
+        </is>
+      </c>
       <c r="I171" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
       </c>
     </row>
@@ -7134,26 +7350,34 @@
       </c>
       <c r="B172" s="5" t="inlineStr">
         <is>
-          <t>Stu Lotz</t>
+          <t>Jim McBride</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2007–2020</t>
         </is>
       </c>
       <c r="D172" s="6" t="inlineStr"/>
       <c r="E172" s="7" t="n"/>
-      <c r="F172" s="5" t="inlineStr"/>
+      <c r="F172" s="5" t="inlineStr">
+        <is>
+          <t>50+</t>
+        </is>
+      </c>
       <c r="G172" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="H172" s="8" t="inlineStr"/>
+          <t>Band only</t>
+        </is>
+      </c>
+      <c r="H172" s="8" t="inlineStr">
+        <is>
+          <t>Tommy Leech, Oct 2026</t>
+        </is>
+      </c>
       <c r="I172" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Only an age band is known – a year would be better</t>
         </is>
       </c>
     </row>
@@ -7165,34 +7389,40 @@
       </c>
       <c r="B173" s="5" t="inlineStr">
         <is>
-          <t>Jim McBride</t>
+          <t>Aidan Oehrle</t>
         </is>
       </c>
       <c r="C173" s="5" t="inlineStr">
         <is>
-          <t>2007–2020</t>
-        </is>
-      </c>
-      <c r="D173" s="6" t="inlineStr"/>
-      <c r="E173" s="7" t="n"/>
+          <t>2019–2025</t>
+        </is>
+      </c>
+      <c r="D173" s="6" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="E173" s="7" t="n">
+        <v>2003</v>
+      </c>
       <c r="F173" s="5" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Under 25</t>
         </is>
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>Band only</t>
+          <t>Approximate</t>
         </is>
       </c>
       <c r="H173" s="8" t="inlineStr">
         <is>
-          <t>Tommy Leech, Oct 2026</t>
+          <t>Fox Chapel HS junior in fall 2019 (WPIAL 3A, T3)</t>
         </is>
       </c>
       <c r="I173" s="8" t="inlineStr">
         <is>
-          <t>Only an age band is known – a year would be better</t>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
       </c>
     </row>
@@ -7204,40 +7434,34 @@
       </c>
       <c r="B174" s="5" t="inlineStr">
         <is>
-          <t>Aidan Oehrle</t>
+          <t>Chris Osborne</t>
         </is>
       </c>
       <c r="C174" s="5" t="inlineStr">
         <is>
-          <t>2019–2025</t>
-        </is>
-      </c>
-      <c r="D174" s="6" t="inlineStr">
-        <is>
-          <t>2003</t>
-        </is>
-      </c>
-      <c r="E174" s="7" t="n">
-        <v>2003</v>
-      </c>
+          <t>2016–2020</t>
+        </is>
+      </c>
+      <c r="D174" s="6" t="inlineStr"/>
+      <c r="E174" s="7" t="n"/>
       <c r="F174" s="5" t="inlineStr">
         <is>
-          <t>Under 25</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G174" s="5" t="inlineStr">
         <is>
-          <t>Approximate</t>
+          <t>Band only</t>
         </is>
       </c>
       <c r="H174" s="8" t="inlineStr">
         <is>
-          <t>Fox Chapel HS junior in fall 2019 (WPIAL 3A, T3)</t>
+          <t>Tommy Leech, Oct 2026</t>
         </is>
       </c>
       <c r="I174" s="8" t="inlineStr">
         <is>
-          <t>Year only, worked out from an age or school year – a real date would be better</t>
+          <t>Only an age band is known – a year would be better</t>
         </is>
       </c>
     </row>
@@ -7249,26 +7473,40 @@
       </c>
       <c r="B175" s="5" t="inlineStr">
         <is>
-          <t>Chris Osborne</t>
+          <t>Jonathan Pepe</t>
         </is>
       </c>
       <c r="C175" s="5" t="inlineStr">
         <is>
-          <t>2016–2020</t>
-        </is>
-      </c>
-      <c r="D175" s="6" t="inlineStr"/>
-      <c r="E175" s="7" t="n"/>
-      <c r="F175" s="5" t="inlineStr"/>
+          <t>2009–2013</t>
+        </is>
+      </c>
+      <c r="D175" s="6" t="inlineStr">
+        <is>
+          <t>1986</t>
+        </is>
+      </c>
+      <c r="E175" s="7" t="n">
+        <v>1986</v>
+      </c>
+      <c r="F175" s="5" t="inlineStr">
+        <is>
+          <t>40–49</t>
+        </is>
+      </c>
       <c r="G175" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="H175" s="8" t="inlineStr"/>
+          <t>Approximate</t>
+        </is>
+      </c>
+      <c r="H175" s="8" t="inlineStr">
+        <is>
+          <t>Serra Catholic; senior on the Marshall golf roster 2007-08</t>
+        </is>
+      </c>
       <c r="I175" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
       </c>
     </row>
@@ -7280,21 +7518,21 @@
       </c>
       <c r="B176" s="5" t="inlineStr">
         <is>
-          <t>Jonathan Pepe</t>
+          <t>Ben Rathfon</t>
         </is>
       </c>
       <c r="C176" s="5" t="inlineStr">
         <is>
-          <t>2009–2013</t>
+          <t>2009–2014</t>
         </is>
       </c>
       <c r="D176" s="6" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>1983</t>
         </is>
       </c>
       <c r="E176" s="7" t="n">
-        <v>1986</v>
+        <v>1983</v>
       </c>
       <c r="F176" s="5" t="inlineStr">
         <is>
@@ -7308,7 +7546,7 @@
       </c>
       <c r="H176" s="8" t="inlineStr">
         <is>
-          <t>Serra Catholic; senior on the Marshall golf roster 2007-08</t>
+          <t>Allegheny College class of 2005 (athletics hall of fame)</t>
         </is>
       </c>
       <c r="I176" s="8" t="inlineStr">
@@ -7325,25 +7563,25 @@
       </c>
       <c r="B177" s="5" t="inlineStr">
         <is>
-          <t>Ben Rathfon</t>
+          <t>Evan Ruhling</t>
         </is>
       </c>
       <c r="C177" s="5" t="inlineStr">
         <is>
-          <t>2009–2014</t>
+          <t>2016–2025</t>
         </is>
       </c>
       <c r="D177" s="6" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="E177" s="7" t="n">
-        <v>1983</v>
+        <v>1993</v>
       </c>
       <c r="F177" s="5" t="inlineStr">
         <is>
-          <t>40–49</t>
+          <t>30–39</t>
         </is>
       </c>
       <c r="G177" s="5" t="inlineStr">
@@ -7353,7 +7591,7 @@
       </c>
       <c r="H177" s="8" t="inlineStr">
         <is>
-          <t>Allegheny College class of 2005 (athletics hall of fame)</t>
+          <t>A year younger than Tommy Leech (Tommy, Oct 2026)</t>
         </is>
       </c>
       <c r="I177" s="8" t="inlineStr">
@@ -7370,12 +7608,12 @@
       </c>
       <c r="B178" s="5" t="inlineStr">
         <is>
-          <t>Evan Ruhling</t>
+          <t>B. Sera</t>
         </is>
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>2016–2025</t>
+          <t>2017–2022</t>
         </is>
       </c>
       <c r="D178" s="6" t="inlineStr"/>
@@ -7401,26 +7639,40 @@
       </c>
       <c r="B179" s="5" t="inlineStr">
         <is>
-          <t>B. Sera</t>
+          <t>Charlie Troutman</t>
         </is>
       </c>
       <c r="C179" s="5" t="inlineStr">
         <is>
-          <t>2017–2022</t>
-        </is>
-      </c>
-      <c r="D179" s="6" t="inlineStr"/>
-      <c r="E179" s="7" t="n"/>
-      <c r="F179" s="5" t="inlineStr"/>
+          <t>2020–2025</t>
+        </is>
+      </c>
+      <c r="D179" s="6" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="E179" s="7" t="n">
+        <v>2003</v>
+      </c>
+      <c r="F179" s="5" t="inlineStr">
+        <is>
+          <t>Under 25</t>
+        </is>
+      </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="H179" s="8" t="inlineStr"/>
+          <t>Approximate</t>
+        </is>
+      </c>
+      <c r="H179" s="8" t="inlineStr">
+        <is>
+          <t>Shady Side Academy sophomore in fall 2018 (IPSL medalist)</t>
+        </is>
+      </c>
       <c r="I179" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
       </c>
     </row>
@@ -7432,40 +7684,34 @@
       </c>
       <c r="B180" s="5" t="inlineStr">
         <is>
-          <t>Charlie Troutman</t>
+          <t>Jeff Troutman</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>2020–2025</t>
-        </is>
-      </c>
-      <c r="D180" s="6" t="inlineStr">
-        <is>
-          <t>2003</t>
-        </is>
-      </c>
-      <c r="E180" s="7" t="n">
-        <v>2003</v>
-      </c>
+          <t>2000–2016</t>
+        </is>
+      </c>
+      <c r="D180" s="6" t="inlineStr"/>
+      <c r="E180" s="7" t="n"/>
       <c r="F180" s="5" t="inlineStr">
         <is>
-          <t>Under 25</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>Approximate</t>
+          <t>Band only</t>
         </is>
       </c>
       <c r="H180" s="8" t="inlineStr">
         <is>
-          <t>Shady Side Academy sophomore in fall 2018 (IPSL medalist)</t>
+          <t>Tommy Leech, Oct 2026</t>
         </is>
       </c>
       <c r="I180" s="8" t="inlineStr">
         <is>
-          <t>Year only, worked out from an age or school year – a real date would be better</t>
+          <t>Only an age band is known – a year would be better</t>
         </is>
       </c>
     </row>
@@ -7477,26 +7723,34 @@
       </c>
       <c r="B181" s="5" t="inlineStr">
         <is>
-          <t>Jeff Troutman</t>
+          <t>Scott Troutman</t>
         </is>
       </c>
       <c r="C181" s="5" t="inlineStr">
         <is>
-          <t>2000–2016</t>
+          <t>2010–2015</t>
         </is>
       </c>
       <c r="D181" s="6" t="inlineStr"/>
       <c r="E181" s="7" t="n"/>
-      <c r="F181" s="5" t="inlineStr"/>
+      <c r="F181" s="5" t="inlineStr">
+        <is>
+          <t>50+</t>
+        </is>
+      </c>
       <c r="G181" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="H181" s="8" t="inlineStr"/>
+          <t>Band only</t>
+        </is>
+      </c>
+      <c r="H181" s="8" t="inlineStr">
+        <is>
+          <t>Tommy Leech, Oct 2026</t>
+        </is>
+      </c>
       <c r="I181" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Only an age band is known – a year would be better</t>
         </is>
       </c>
     </row>
@@ -7508,26 +7762,40 @@
       </c>
       <c r="B182" s="5" t="inlineStr">
         <is>
-          <t>Scott Troutman</t>
+          <t>Mark Vernallis</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>2010–2015</t>
-        </is>
-      </c>
-      <c r="D182" s="6" t="inlineStr"/>
-      <c r="E182" s="7" t="n"/>
-      <c r="F182" s="5" t="inlineStr"/>
+          <t>2015–2020</t>
+        </is>
+      </c>
+      <c r="D182" s="6" t="inlineStr">
+        <is>
+          <t>1989</t>
+        </is>
+      </c>
+      <c r="E182" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="F182" s="5" t="inlineStr">
+        <is>
+          <t>30–39</t>
+        </is>
+      </c>
       <c r="G182" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="H182" s="8" t="inlineStr"/>
+          <t>Approximate</t>
+        </is>
+      </c>
+      <c r="H182" s="8" t="inlineStr">
+        <is>
+          <t>About 37 in Oct 2026 (Tommy Leech)</t>
+        </is>
+      </c>
       <c r="I182" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
       </c>
     </row>
@@ -7539,12 +7807,12 @@
       </c>
       <c r="B183" s="5" t="inlineStr">
         <is>
-          <t>Mark Vernallis</t>
+          <t>B. Weinbaum</t>
         </is>
       </c>
       <c r="C183" s="5" t="inlineStr">
         <is>
-          <t>2015–2020</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D183" s="6" t="inlineStr"/>
@@ -7570,26 +7838,40 @@
       </c>
       <c r="B184" s="5" t="inlineStr">
         <is>
-          <t>B. Weinbaum</t>
+          <t>Shawn Will</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="D184" s="6" t="inlineStr"/>
-      <c r="E184" s="7" t="n"/>
-      <c r="F184" s="5" t="inlineStr"/>
+          <t>2001–2021</t>
+        </is>
+      </c>
+      <c r="D184" s="6" t="inlineStr">
+        <is>
+          <t>1976</t>
+        </is>
+      </c>
+      <c r="E184" s="7" t="n">
+        <v>1976</v>
+      </c>
+      <c r="F184" s="5" t="inlineStr">
+        <is>
+          <t>50+</t>
+        </is>
+      </c>
       <c r="G184" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="H184" s="8" t="inlineStr"/>
+          <t>Approximate</t>
+        </is>
+      </c>
+      <c r="H184" s="8" t="inlineStr">
+        <is>
+          <t>About 50 in Oct 2026 (Tommy Leech)</t>
+        </is>
+      </c>
       <c r="I184" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
       </c>
     </row>
@@ -7601,26 +7883,40 @@
       </c>
       <c r="B185" s="5" t="inlineStr">
         <is>
-          <t>Shawn Will</t>
+          <t>Jack Wymard</t>
         </is>
       </c>
       <c r="C185" s="5" t="inlineStr">
         <is>
-          <t>2001–2021</t>
-        </is>
-      </c>
-      <c r="D185" s="6" t="inlineStr"/>
-      <c r="E185" s="7" t="n"/>
-      <c r="F185" s="5" t="inlineStr"/>
+          <t>2023–2025</t>
+        </is>
+      </c>
+      <c r="D185" s="6" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="E185" s="7" t="n">
+        <v>2001</v>
+      </c>
+      <c r="F185" s="5" t="inlineStr">
+        <is>
+          <t>25–29</t>
+        </is>
+      </c>
       <c r="G185" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="H185" s="8" t="inlineStr"/>
+          <t>Approximate</t>
+        </is>
+      </c>
+      <c r="H185" s="8" t="inlineStr">
+        <is>
+          <t>Pine-Richland golfer at the 2018 PIAA championship; class year not found, uncertain</t>
+        </is>
+      </c>
       <c r="I185" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
       </c>
     </row>
@@ -7632,25 +7928,25 @@
       </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
-          <t>Jack Wymard</t>
+          <t>Eli Yofan</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
         <is>
-          <t>2023–2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D186" s="6" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="E186" s="7" t="n">
-        <v>2001</v>
+        <v>2004</v>
       </c>
       <c r="F186" s="5" t="inlineStr">
         <is>
-          <t>25–29</t>
+          <t>Under 25</t>
         </is>
       </c>
       <c r="G186" s="5" t="inlineStr">
@@ -7660,7 +7956,7 @@
       </c>
       <c r="H186" s="8" t="inlineStr">
         <is>
-          <t>Pine-Richland golfer at the 2018 PIAA championship; class year not found, uncertain</t>
+          <t>Fox Chapel HS junior in fall 2020</t>
         </is>
       </c>
       <c r="I186" s="8" t="inlineStr">
@@ -7669,53 +7965,8 @@
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="5" t="inlineStr">
-        <is>
-          <t>Longue Vue</t>
-        </is>
-      </c>
-      <c r="B187" s="5" t="inlineStr">
-        <is>
-          <t>Eli Yofan</t>
-        </is>
-      </c>
-      <c r="C187" s="5" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D187" s="6" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
-      </c>
-      <c r="E187" s="7" t="n">
-        <v>2004</v>
-      </c>
-      <c r="F187" s="5" t="inlineStr">
-        <is>
-          <t>Under 25</t>
-        </is>
-      </c>
-      <c r="G187" s="5" t="inlineStr">
-        <is>
-          <t>Approximate</t>
-        </is>
-      </c>
-      <c r="H187" s="8" t="inlineStr">
-        <is>
-          <t>Fox Chapel HS junior in fall 2020</t>
-        </is>
-      </c>
-      <c r="I187" s="8" t="inlineStr">
-        <is>
-          <t>Year only, worked out from an age or school year – a real date would be better</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A5:I187"/>
+  <autoFilter ref="A5:I186"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7789,7 +8040,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C4" s="11" t="n">
         <v>36</v>
@@ -7804,7 +8055,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -7820,16 +8071,16 @@
         <v>16</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E5" s="11" t="n">
         <v>3</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
@@ -7845,7 +8096,7 @@
         <v>40</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6" s="11" t="n">
         <v>0</v>
@@ -7854,7 +8105,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -7870,16 +8121,16 @@
         <v>0</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E7" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -7889,22 +8140,22 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C8" s="12" t="n">
         <v>92</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>3</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>48</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" ht="45" customHeight="1">

--- a/reports/diebold-birth-dates.xlsx
+++ b/reports/diebold-birth-dates.xlsx
@@ -2246,7 +2246,7 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>L. Astorino</t>
+          <t>Lou Astorino</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
@@ -2254,18 +2254,32 @@
           <t>2017</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr"/>
-      <c r="E46" s="7" t="n"/>
-      <c r="F46" s="5" t="inlineStr"/>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>1975</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="n">
+        <v>1975</v>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>50+</t>
+        </is>
+      </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="H46" s="8" t="inlineStr"/>
+          <t>Approximate</t>
+        </is>
+      </c>
+      <c r="H46" s="8" t="inlineStr">
+        <is>
+          <t>Graduated college 1997 (Tommy Leech)</t>
+        </is>
+      </c>
       <c r="I46" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
       </c>
     </row>
@@ -2277,7 +2291,7 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>W. Barker</t>
+          <t>Watson Barker</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -2285,18 +2299,32 @@
           <t>2018–2019</t>
         </is>
       </c>
-      <c r="D47" s="6" t="inlineStr"/>
-      <c r="E47" s="7" t="n"/>
-      <c r="F47" s="5" t="inlineStr"/>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>1977</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="n">
+        <v>1977</v>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>40–49</t>
+        </is>
+      </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="H47" s="8" t="inlineStr"/>
+          <t>Approximate</t>
+        </is>
+      </c>
+      <c r="H47" s="8" t="inlineStr">
+        <is>
+          <t>Graduated college 1999 (Tommy Leech)</t>
+        </is>
+      </c>
       <c r="I47" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3379,7 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>T. Kelly</t>
+          <t>Trey Kelly</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
@@ -3359,18 +3387,32 @@
           <t>2017</t>
         </is>
       </c>
-      <c r="D73" s="6" t="inlineStr"/>
-      <c r="E73" s="7" t="n"/>
-      <c r="F73" s="5" t="inlineStr"/>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="n">
+        <v>1999</v>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>25–29</t>
+        </is>
+      </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="H73" s="8" t="inlineStr"/>
+          <t>Approximate</t>
+        </is>
+      </c>
+      <c r="H73" s="8" t="inlineStr">
+        <is>
+          <t>Graduated college 2021 (Tommy Leech)</t>
+        </is>
+      </c>
       <c r="I73" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3824,7 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>C. Rudolf</t>
+          <t>Chris Rudolf</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
@@ -3790,18 +3832,32 @@
           <t>2017–2021</t>
         </is>
       </c>
-      <c r="D84" s="6" t="inlineStr"/>
-      <c r="E84" s="7" t="n"/>
-      <c r="F84" s="5" t="inlineStr"/>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>1988</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="n">
+        <v>1988</v>
+      </c>
+      <c r="F84" s="5" t="inlineStr">
+        <is>
+          <t>30–39</t>
+        </is>
+      </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="H84" s="8" t="inlineStr"/>
+          <t>Approximate</t>
+        </is>
+      </c>
+      <c r="H84" s="8" t="inlineStr">
+        <is>
+          <t>Graduated college 2010 (Tommy Leech)</t>
+        </is>
+      </c>
       <c r="I84" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
       </c>
     </row>
@@ -3813,7 +3869,7 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>R. Russell</t>
+          <t>Randy Russell</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
@@ -3821,18 +3877,32 @@
           <t>2016–2020</t>
         </is>
       </c>
-      <c r="D85" s="6" t="inlineStr"/>
-      <c r="E85" s="7" t="n"/>
-      <c r="F85" s="5" t="inlineStr"/>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>1969</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="n">
+        <v>1969</v>
+      </c>
+      <c r="F85" s="5" t="inlineStr">
+        <is>
+          <t>50+</t>
+        </is>
+      </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="H85" s="8" t="inlineStr"/>
+          <t>Approximate</t>
+        </is>
+      </c>
+      <c r="H85" s="8" t="inlineStr">
+        <is>
+          <t>Graduated college 1991 (Tommy Leech)</t>
+        </is>
+      </c>
       <c r="I85" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
       </c>
     </row>
@@ -3975,7 +4045,7 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>D. Smith</t>
+          <t>Don Smith</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
@@ -4962,7 +5032,7 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>Fricke</t>
+          <t>Jackson Fricke</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
@@ -4970,18 +5040,32 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D114" s="6" t="inlineStr"/>
-      <c r="E114" s="7" t="n"/>
-      <c r="F114" s="5" t="inlineStr"/>
+      <c r="D114" s="6" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="E114" s="7" t="n">
+        <v>2003</v>
+      </c>
+      <c r="F114" s="5" t="inlineStr">
+        <is>
+          <t>Under 25</t>
+        </is>
+      </c>
       <c r="G114" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="H114" s="8" t="inlineStr"/>
+          <t>Approximate</t>
+        </is>
+      </c>
+      <c r="H114" s="8" t="inlineStr">
+        <is>
+          <t>Graduated college 2025 (Tommy Leech)</t>
+        </is>
+      </c>
       <c r="I114" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
       </c>
     </row>
@@ -8071,7 +8155,7 @@
         <v>16</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E5" s="11" t="n">
         <v>3</v>
@@ -8080,7 +8164,7 @@
         <v>4</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -8096,7 +8180,7 @@
         <v>40</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6" s="11" t="n">
         <v>0</v>
@@ -8105,7 +8189,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -8146,7 +8230,7 @@
         <v>92</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>3</v>
@@ -8155,7 +8239,7 @@
         <v>12</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" ht="45" customHeight="1">

--- a/reports/diebold-birth-dates.xlsx
+++ b/reports/diebold-birth-dates.xlsx
@@ -3600,18 +3600,32 @@
           <t>2023–2025</t>
         </is>
       </c>
-      <c r="D78" s="6" t="inlineStr"/>
-      <c r="E78" s="7" t="n"/>
-      <c r="F78" s="5" t="inlineStr"/>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="n">
+        <v>2007</v>
+      </c>
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>Under 25</t>
+        </is>
+      </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="H78" s="8" t="inlineStr"/>
+          <t>Approximate</t>
+        </is>
+      </c>
+      <c r="H78" s="8" t="inlineStr">
+        <is>
+          <t>High school class of 2025 (Tommy Leech)</t>
+        </is>
+      </c>
       <c r="I78" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
       </c>
     </row>
@@ -8155,7 +8169,7 @@
         <v>16</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E5" s="11" t="n">
         <v>3</v>
@@ -8164,7 +8178,7 @@
         <v>4</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -8230,7 +8244,7 @@
         <v>92</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>3</v>
@@ -8239,7 +8253,7 @@
         <v>12</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" ht="45" customHeight="1">

--- a/reports/diebold-birth-dates.xlsx
+++ b/reports/diebold-birth-dates.xlsx
@@ -6675,7 +6675,7 @@
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>P. Compeau</t>
+          <t>Phil Compeau</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
@@ -6683,18 +6683,32 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="D153" s="6" t="inlineStr"/>
-      <c r="E153" s="7" t="n"/>
-      <c r="F153" s="5" t="inlineStr"/>
+      <c r="D153" s="6" t="inlineStr">
+        <is>
+          <t>1986</t>
+        </is>
+      </c>
+      <c r="E153" s="7" t="n">
+        <v>1986</v>
+      </c>
+      <c r="F153" s="5" t="inlineStr">
+        <is>
+          <t>40–49</t>
+        </is>
+      </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="H153" s="8" t="inlineStr"/>
+          <t>Approximate</t>
+        </is>
+      </c>
+      <c r="H153" s="8" t="inlineStr">
+        <is>
+          <t>Graduated college 2008 (Tommy Leech)</t>
+        </is>
+      </c>
       <c r="I153" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
       </c>
     </row>
@@ -8219,7 +8233,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E7" s="11" t="n">
         <v>0</v>
@@ -8228,7 +8242,7 @@
         <v>8</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -8244,7 +8258,7 @@
         <v>92</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>3</v>
@@ -8253,7 +8267,7 @@
         <v>12</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" ht="45" customHeight="1">

--- a/reports/diebold-birth-dates.xlsx
+++ b/reports/diebold-birth-dates.xlsx
@@ -7062,18 +7062,32 @@
           <t>2014–2021</t>
         </is>
       </c>
-      <c r="D162" s="6" t="inlineStr"/>
-      <c r="E162" s="7" t="n"/>
-      <c r="F162" s="5" t="inlineStr"/>
+      <c r="D162" s="6" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="E162" s="7" t="n">
+        <v>1996</v>
+      </c>
+      <c r="F162" s="5" t="inlineStr">
+        <is>
+          <t>30–39</t>
+        </is>
+      </c>
       <c r="G162" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="H162" s="8" t="inlineStr"/>
+          <t>Approximate</t>
+        </is>
+      </c>
+      <c r="H162" s="8" t="inlineStr">
+        <is>
+          <t>Graduated college 2018 (Tommy Leech); older brother of Pitt's Aidan Fisch (b. 2000)</t>
+        </is>
+      </c>
       <c r="I162" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
       </c>
     </row>
@@ -8233,7 +8247,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E7" s="11" t="n">
         <v>0</v>
@@ -8242,7 +8256,7 @@
         <v>8</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -8258,7 +8272,7 @@
         <v>92</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>3</v>
@@ -8267,7 +8281,7 @@
         <v>12</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" ht="45" customHeight="1">

--- a/reports/diebold-birth-dates.xlsx
+++ b/reports/diebold-birth-dates.xlsx
@@ -7107,18 +7107,32 @@
           <t>2021–2025</t>
         </is>
       </c>
-      <c r="D163" s="6" t="inlineStr"/>
-      <c r="E163" s="7" t="n"/>
-      <c r="F163" s="5" t="inlineStr"/>
+      <c r="D163" s="6" t="inlineStr">
+        <is>
+          <t>1988</t>
+        </is>
+      </c>
+      <c r="E163" s="7" t="n">
+        <v>1988</v>
+      </c>
+      <c r="F163" s="5" t="inlineStr">
+        <is>
+          <t>30–39</t>
+        </is>
+      </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="H163" s="8" t="inlineStr"/>
+          <t>Approximate</t>
+        </is>
+      </c>
+      <c r="H163" s="8" t="inlineStr">
+        <is>
+          <t>Graduated college 2010 (Tommy Leech)</t>
+        </is>
+      </c>
       <c r="I163" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
       </c>
     </row>
@@ -8247,7 +8261,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E7" s="11" t="n">
         <v>0</v>
@@ -8256,7 +8270,7 @@
         <v>8</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -8272,7 +8286,7 @@
         <v>92</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>3</v>
@@ -8281,7 +8295,7 @@
         <v>12</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" ht="45" customHeight="1">

--- a/reports/diebold-birth-dates.xlsx
+++ b/reports/diebold-birth-dates.xlsx
@@ -7424,16 +7424,24 @@
       </c>
       <c r="D170" s="6" t="inlineStr"/>
       <c r="E170" s="7" t="n"/>
-      <c r="F170" s="5" t="inlineStr"/>
+      <c r="F170" s="5" t="inlineStr">
+        <is>
+          <t>50+</t>
+        </is>
+      </c>
       <c r="G170" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="H170" s="8" t="inlineStr"/>
+          <t>Band only</t>
+        </is>
+      </c>
+      <c r="H170" s="8" t="inlineStr">
+        <is>
+          <t>60+ per Tommy Leech, Oct 2026 (bands stop at 50+)</t>
+        </is>
+      </c>
       <c r="I170" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Only an age band is known – a year would be better</t>
         </is>
       </c>
     </row>
@@ -7748,7 +7756,7 @@
       </c>
       <c r="B178" s="5" t="inlineStr">
         <is>
-          <t>B. Sera</t>
+          <t>Ben Sera</t>
         </is>
       </c>
       <c r="C178" s="5" t="inlineStr">
@@ -7756,18 +7764,32 @@
           <t>2017–2022</t>
         </is>
       </c>
-      <c r="D178" s="6" t="inlineStr"/>
-      <c r="E178" s="7" t="n"/>
-      <c r="F178" s="5" t="inlineStr"/>
+      <c r="D178" s="6" t="inlineStr">
+        <is>
+          <t>1988</t>
+        </is>
+      </c>
+      <c r="E178" s="7" t="n">
+        <v>1988</v>
+      </c>
+      <c r="F178" s="5" t="inlineStr">
+        <is>
+          <t>30–39</t>
+        </is>
+      </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="H178" s="8" t="inlineStr"/>
+          <t>Approximate</t>
+        </is>
+      </c>
+      <c r="H178" s="8" t="inlineStr">
+        <is>
+          <t>Graduated college 2010 (Tommy Leech)</t>
+        </is>
+      </c>
       <c r="I178" s="8" t="inlineStr">
         <is>
-          <t>Please add</t>
+          <t>Year only, worked out from an age or school year – a real date would be better</t>
         </is>
       </c>
     </row>
@@ -8261,16 +8283,16 @@
         <v>0</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E7" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -8286,16 +8308,16 @@
         <v>92</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>3</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" ht="45" customHeight="1">
